--- a/ready-for-annotation/de/bbc.242497.xlsx
+++ b/ready-for-annotation/de/bbc.242497.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="375">
   <si>
     <t>ID</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Brücke</t>
   </si>
   <si>
-    <t>Queensferry Crossing : Brücke nun mit Fife verbunden Das £ 1,35 Mrd .</t>
+    <t>Queensferry Crossing : Brücke nun mit Fife verbunden</t>
   </si>
   <si>
     <t>file://conllu/de/bbc.242497.conllu#s1_0</t>
@@ -68,19 +68,46 @@
     <t>2</t>
   </si>
   <si>
+    <t>Mrd</t>
+  </si>
+  <si>
+    <t>Das £ 1,35 Mrd .</t>
+  </si>
+  <si>
+    <t>file://conllu/de/bbc.242497.conllu#s2_0</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
     <t>fertigstellen</t>
   </si>
   <si>
-    <t>teure Projekt soll bis Mai 2017 fertiggestellt werden Ingenieure haben das Norddeck des Queensferry Crossings mit dem Viadukt verbunden was bedeutet , dass die Brücke jetzt mit Fife verbunden ist .</t>
-  </si>
-  <si>
-    <t>file://conllu/de/bbc.242497.conllu#s2_0</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>teure Projekt soll bis Mai 2017 fertiggestellt werden</t>
+  </si>
+  <si>
+    <t>file://conllu/de/bbc.242497.conllu#s3_0</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Was?</t>
+  </si>
+  <si>
+    <t>verbunden</t>
+  </si>
+  <si>
+    <t>Ingenieure haben das Norddeck des Queensferry Crossings mit dem Viadukt verbunden was bedeutet , dass die Brücke jetzt mit Fife verbunden ist .</t>
+  </si>
+  <si>
+    <t>file://conllu/de/bbc.242497.conllu#s4_0</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>sein (sein erst)</t>
@@ -89,10 +116,10 @@
     <t>Es ist das erste von vier Verschließungen der &amp;quot; Deckgebläse &amp;quot; , die sich der Fertigstellung um jeden der drei Türme der Brücke nähern .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s3_0</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>file://conllu/de/bbc.242497.conllu#s5_0</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>sein (sein lang)</t>
@@ -101,7 +128,7 @@
     <t>Der Brückenabschnitt von Fife ist jetzt 600 Meter lang und wiegt 30.000 Tonnen .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s4_0</t>
+    <t>file://conllu/de/bbc.242497.conllu#s6_0</t>
   </si>
   <si>
     <t>verfügen</t>
@@ -110,19 +137,19 @@
     <t>Er verfügt über 10.000 Tonnen Stahl und 20.000 Tonnen Beton sowie 46 Schrägseile .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s5_0</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>file://conllu/de/bbc.242497.conllu#s7_0</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>Das £ 1,35 Mrd. teure Projekt soll bis Mai 2017 fertiggestellt werden .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s6_0</t>
+    <t>file://conllu/de/bbc.242497.conllu#s8_0</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>statten</t>
@@ -131,10 +158,10 @@
     <t>Wirtschaftsminister Keith Brown stattete der Baustelle heute einen Besuch ab und war einer der Ersten , die vom von dem Land auf die Brücke gingen .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s7_0</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>file://conllu/de/bbc.242497.conllu#s9_0</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>sagen</t>
@@ -143,10 +170,7 @@
     <t>Er sagte : &amp;quot; Das ist ein historischer und symbolischer Moment beim bei dem Bau des Queensferry Crossings .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s8_0</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>file://conllu/de/bbc.242497.conllu#s10_0</t>
   </si>
   <si>
     <t>sein (sein Zeuge)</t>
@@ -155,10 +179,10 @@
     <t>Wir sind alle Zeugen einer Ingenieurskunst von einem wahrlich epischen Maße bei diesem Projekt mit über 30.000 Tonnen Beton und Stahl , die alleine für diesen Teil der Brücke verwendet wurden .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s9_0</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>file://conllu/de/bbc.242497.conllu#s11_0</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>sein (sein Tätigkeit)</t>
@@ -167,34 +191,34 @@
     <t>Trotz der massiven Größe und Gewichts des Brücke , ist die Fertigstellung des Verschlusses zwischen dem Viadukt und dem Brückendeck eine heikle Tätigkeit , die extrem präzise Toleranzen für die Passung erfordern .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s10_0</t>
+    <t>file://conllu/de/bbc.242497.conllu#s12_0</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>Was?</t>
-  </si>
-  <si>
     <t>bekommen</t>
   </si>
   <si>
     <t>Insgesamt sind fast 79 % der gesamten Brückendecks an ihrem Platz und der letzte Abschnitt des Decks bekommt heute in Rosyth einen Betonguss für das Deck , was bedeutet , dass das gesamte Deck bereit ist , auf der Brücke an seinen Platz gehoben zu werden .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s11_0</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>file://conllu/de/bbc.242497.conllu#s13_0</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>Michael Martin , Projektleiter von Forth Crossing Bridge Constructors sagte : &amp;quot; Der erste Verschluss stellt bei jedem Brückenprojekt einen erheblichen Meilenstein dar .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s12_0</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>file://conllu/de/bbc.242497.conllu#s14_0</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>stellen</t>
@@ -203,10 +227,10 @@
     <t>Bei diesem fantastischen Projekt stellt der Verschluss zukunftsweisenden Hoch und Tiefbau dar .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s13_0</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>file://conllu/de/bbc.242497.conllu#s15_0</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>31</t>
@@ -218,10 +242,10 @@
     <t>Nach der Installation des letzten Straßendeckabschnitts und dessen Verbindung mit dem im in dem Ausbau befindlichen Nordturmdeck , mussten wir sodann die noch bestehende Lücke auf der Nord oder Landseite schließen .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s14_0</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>file://conllu/de/bbc.242497.conllu#s16_0</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>Durch?</t>
@@ -233,19 +257,16 @@
     <t>Dies wurde durch Ziehen der nördlichen Zubringerbrücke 700 Millimeter südlich erreicht .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s15_0</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>file://conllu/de/bbc.242497.conllu#s17_0</t>
   </si>
   <si>
     <t>Dies war eine massive und gleichzeitig sehr heikle Tätigkeit .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s16_0</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>file://conllu/de/bbc.242497.conllu#s18_0</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>27</t>
@@ -257,7 +278,10 @@
     <t>Massiv , da das Viadukt 222 Meter lang ist , ca . 6.000 Tonnen wiegt und bei einer Steigung von ca . 3 % nach oben gezogen werden musste .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s17_0</t>
+    <t>file://conllu/de/bbc.242497.conllu#s19_0</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>sein (sein betragen)</t>
@@ -266,10 +290,10 @@
     <t>Heikel , da die Toleranzen , auf die das Team hinarbeitet , winzig waren auf jeder Seite betrugen sie nur einige Millimeter .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s18_0</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>file://conllu/de/bbc.242497.conllu#s20_0</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>verlaufen</t>
@@ -278,7 +302,7 @@
     <t>Glücklicherweise verlief alles sehr gut .</t>
   </si>
   <si>
-    <t>file://conllu/de/bbc.242497.conllu#s19_0</t>
+    <t>file://conllu/de/bbc.242497.conllu#s21_0</t>
   </si>
   <si>
     <t>WORD</t>
@@ -314,7 +338,7 @@
     <t>REF_DIST_ANTE</t>
   </si>
   <si>
-    <t># text = Queensferry Crossing: Brücke nun mit Fife verbunden Das £ 1,35 Mrd.</t>
+    <t># text = Queensferry Crossing: Brücke nun mit Fife verbunden</t>
   </si>
   <si>
     <t>Queensferry</t>
@@ -350,7 +374,7 @@
     <t>indef-np.bare</t>
   </si>
   <si>
-    <t>verbunden</t>
+    <t># text = Das £ 1,35 Mrd.</t>
   </si>
   <si>
     <t>Das</t>
@@ -359,166 +383,166 @@
     <t>£</t>
   </si>
   <si>
+    <t>SBJ</t>
+  </si>
+  <si>
+    <t>def-np.the</t>
+  </si>
+  <si>
+    <t>1,35</t>
+  </si>
+  <si>
+    <t>pron.pper</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t># text = teure Projekt soll bis Mai 2017 fertiggestellt werden</t>
+  </si>
+  <si>
+    <t>teure</t>
+  </si>
+  <si>
+    <t>Projekt</t>
+  </si>
+  <si>
+    <t>indef-np</t>
+  </si>
+  <si>
+    <t>soll</t>
+  </si>
+  <si>
+    <t>bis</t>
+  </si>
+  <si>
+    <t>Mai</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>fertiggestellt</t>
+  </si>
+  <si>
+    <t>werden</t>
+  </si>
+  <si>
+    <t># text = Ingenieure haben das Norddeck des Queensferry Crossings mit dem Viadukt verbunden - was bedeutet, dass die Brücke jetzt mit Fife verbunden ist.</t>
+  </si>
+  <si>
+    <t>Ingenieure</t>
+  </si>
+  <si>
+    <t>haben</t>
+  </si>
+  <si>
+    <t>das</t>
+  </si>
+  <si>
+    <t>Norddeck</t>
+  </si>
+  <si>
+    <t>def-np.poss</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>Crossings</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>Viadukt</t>
+  </si>
+  <si>
+    <t>was</t>
+  </si>
+  <si>
+    <t>SBJ_2</t>
+  </si>
+  <si>
+    <t>pron</t>
+  </si>
+  <si>
+    <t>bedeutet</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>dass</t>
+  </si>
+  <si>
+    <t>die</t>
+  </si>
+  <si>
+    <t>SBJ_3</t>
+  </si>
+  <si>
+    <t>jetzt</t>
+  </si>
+  <si>
+    <t>other_3</t>
+  </si>
+  <si>
+    <t>ist</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t># text = Es ist das erste von vier Verschließungen der "Deckgebläse", die sich der Fertigstellung um jeden der drei Türme der Brücke nähern.</t>
+  </si>
+  <si>
+    <t>Es</t>
+  </si>
+  <si>
+    <t>erste</t>
+  </si>
+  <si>
+    <t>von</t>
+  </si>
+  <si>
+    <t>vier</t>
+  </si>
+  <si>
+    <t>Verschließungen</t>
+  </si>
+  <si>
+    <t>indef-np.quant</t>
+  </si>
+  <si>
+    <t>der</t>
+  </si>
+  <si>
+    <t>&amp;quot;</t>
+  </si>
+  <si>
+    <t>Deckgebläse</t>
+  </si>
+  <si>
     <t>SBJ_4</t>
   </si>
   <si>
-    <t>def-np.the</t>
-  </si>
-  <si>
-    <t>1,35</t>
-  </si>
-  <si>
-    <t>Mrd</t>
-  </si>
-  <si>
-    <t>other_3</t>
-  </si>
-  <si>
-    <t>pron.pper</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t># text = teure Projekt soll bis Mai 2017 fertiggestellt werden Ingenieure haben das Norddeck des Queensferry Crossings mit dem Viadukt verbunden - was bedeutet, dass die Brücke jetzt mit Fife verbunden ist.</t>
-  </si>
-  <si>
-    <t>teure</t>
-  </si>
-  <si>
-    <t>Projekt</t>
-  </si>
-  <si>
-    <t>SBJ</t>
-  </si>
-  <si>
-    <t>indef-np</t>
-  </si>
-  <si>
-    <t>soll</t>
-  </si>
-  <si>
-    <t>bis</t>
-  </si>
-  <si>
-    <t>Mai</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>fertiggestellt</t>
-  </si>
-  <si>
-    <t>werden</t>
-  </si>
-  <si>
-    <t>Ingenieure</t>
-  </si>
-  <si>
-    <t>SBJ_2</t>
-  </si>
-  <si>
-    <t>haben</t>
-  </si>
-  <si>
-    <t>das</t>
-  </si>
-  <si>
-    <t>Norddeck</t>
-  </si>
-  <si>
-    <t>def-np.poss</t>
-  </si>
-  <si>
-    <t>des</t>
-  </si>
-  <si>
-    <t>Crossings</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>Viadukt</t>
-  </si>
-  <si>
-    <t>was</t>
-  </si>
-  <si>
-    <t>SBJ_3</t>
-  </si>
-  <si>
-    <t>pron</t>
-  </si>
-  <si>
-    <t>bedeutet</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>dass</t>
-  </si>
-  <si>
-    <t>die</t>
-  </si>
-  <si>
-    <t>jetzt</t>
+    <t>sich</t>
+  </si>
+  <si>
+    <t>OBJ_4</t>
+  </si>
+  <si>
+    <t>Fertigstellung</t>
+  </si>
+  <si>
+    <t>um</t>
+  </si>
+  <si>
+    <t>jeden</t>
   </si>
   <si>
     <t>other_4</t>
-  </si>
-  <si>
-    <t>ist</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t># text = Es ist das erste von vier Verschließungen der "Deckgebläse", die sich der Fertigstellung um jeden der drei Türme der Brücke nähern.</t>
-  </si>
-  <si>
-    <t>Es</t>
-  </si>
-  <si>
-    <t>erste</t>
-  </si>
-  <si>
-    <t>von</t>
-  </si>
-  <si>
-    <t>vier</t>
-  </si>
-  <si>
-    <t>Verschließungen</t>
-  </si>
-  <si>
-    <t>indef-np.quant</t>
-  </si>
-  <si>
-    <t>der</t>
-  </si>
-  <si>
-    <t>&amp;quot;</t>
-  </si>
-  <si>
-    <t>Deckgebläse</t>
-  </si>
-  <si>
-    <t>sich</t>
-  </si>
-  <si>
-    <t>OBJ_4</t>
-  </si>
-  <si>
-    <t>Fertigstellung</t>
-  </si>
-  <si>
-    <t>um</t>
-  </si>
-  <si>
-    <t>jeden</t>
   </si>
   <si>
     <t>pron.pind</t>
@@ -1591,7 +1615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="2" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1671,19 +1695,19 @@
         <v>16</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="9">
         <f>IF(A3=1,"_",IF(C3="_","???",C3))</f>
@@ -1699,10 +1723,10 @@
     </row>
     <row r="4" spans="1:10" ht="60" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
@@ -1736,16 +1760,16 @@
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="9">
         <f>IF(A5=1,"_",IF(C5="_","???",C5))</f>
@@ -1761,7 +1785,7 @@
     </row>
     <row r="6" spans="1:10" ht="60" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>16</v>
@@ -1770,13 +1794,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" s="9">
         <f>IF(A6=1,"_",IF(C6="_","???",C6))</f>
@@ -1792,22 +1816,22 @@
     </row>
     <row r="7" spans="1:10" ht="60" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" s="9">
         <f>IF(A7=1,"_",IF(C7="_","???",C7))</f>
@@ -1823,22 +1847,22 @@
     </row>
     <row r="8" spans="1:10" ht="60" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G8" s="9">
         <f>IF(A8=1,"_",IF(C8="_","???",C8))</f>
@@ -1854,22 +1878,22 @@
     </row>
     <row r="9" spans="1:10" ht="60" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" s="9">
         <f>IF(A9=1,"_",IF(C9="_","???",C9))</f>
@@ -1885,22 +1909,22 @@
     </row>
     <row r="10" spans="1:10" ht="60" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="9">
         <f>IF(A10=1,"_",IF(C10="_","???",C10))</f>
@@ -1916,22 +1940,22 @@
     </row>
     <row r="11" spans="1:10" ht="60" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G11" s="9">
         <f>IF(A11=1,"_",IF(C11="_","???",C11))</f>
@@ -1947,22 +1971,22 @@
     </row>
     <row r="12" spans="1:10" ht="60" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="G12" s="9">
         <f>IF(A12=1,"_",IF(C12="_","???",C12))</f>
@@ -1978,16 +2002,16 @@
     </row>
     <row r="13" spans="1:10" ht="60" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>57</v>
@@ -2012,19 +2036,19 @@
         <v>59</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14" s="9">
         <f>IF(A14=1,"_",IF(C14="_","???",C14))</f>
@@ -2040,22 +2064,22 @@
     </row>
     <row r="15" spans="1:10" ht="60" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="G15" s="9">
         <f>IF(A15=1,"_",IF(C15="_","???",C15))</f>
@@ -2071,22 +2095,22 @@
     </row>
     <row r="16" spans="1:10" ht="60" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="E16" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="G16" s="9">
         <f>IF(A16=1,"_",IF(C16="_","???",C16))</f>
@@ -2102,16 +2126,16 @@
     </row>
     <row r="17" spans="1:10" ht="60" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>74</v>
@@ -2136,10 +2160,10 @@
         <v>76</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>78</v>
@@ -2164,22 +2188,22 @@
     </row>
     <row r="19" spans="1:10" ht="60" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="G19" s="9">
         <f>IF(A19=1,"_",IF(C19="_","???",C19))</f>
@@ -2195,10 +2219,10 @@
     </row>
     <row r="20" spans="1:10" ht="60" customHeight="1">
       <c r="A20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>12</v>
@@ -2223,6 +2247,68 @@
         <v>12</v>
       </c>
       <c r="J20" s="12"/>
+    </row>
+    <row r="21" spans="1:10" ht="60" customHeight="1">
+      <c r="A21" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="9">
+        <f>IF(A21=1,"_",IF(C21="_","???",C21))</f>
+        <v/>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="12"/>
+    </row>
+    <row r="22" spans="1:10" ht="60" customHeight="1">
+      <c r="A22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="9">
+        <f>IF(A22=1,"_",IF(C22="_","???",C22))</f>
+        <v/>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="12"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -2232,7 +2318,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L460"/>
+  <dimension ref="A1:L464"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2244,37 +2330,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="13" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>9</v>
@@ -2282,12 +2368,12 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="20" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21">
         <f>IF(D3="?OLD","!!!","")</f>
@@ -2321,7 +2407,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="20" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E4" s="21">
         <f>IF(D4="?OLD","!!!","")</f>
@@ -2355,7 +2441,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="20" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E5" s="21">
         <f>IF(D5="?OLD","!!!","")</f>
@@ -2392,13 +2478,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E6" s="21">
         <f>IF(D6="?OLD","!!!","")</f>
@@ -2432,7 +2518,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="20" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E7" s="21">
         <f>IF(D7="?OLD","!!!","")</f>
@@ -2466,7 +2552,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="20" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E8" s="21">
         <f>IF(D8="?OLD","!!!","")</f>
@@ -2500,13 +2586,13 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="20" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E9" s="21">
         <f>IF(D9="?OLD","!!!","")</f>
@@ -2540,7 +2626,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="20" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="E10" s="21">
         <f>IF(D10="?OLD","!!!","")</f>
@@ -2573,85 +2659,16 @@
       <c r="L10" s="26"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" s="21">
-        <f>IF(D11="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F11" s="22" t="str">
-        <f>IF(OR(E11="",E11="!!!"),"",IF(NOT(ISNA(VLOOKUP(E11,E$1:E10,1,FALSE()))),"OLD",IF(AND(E11&lt;&gt;"",E11&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G11" s="23" t="str">
-        <f>IF(OR(E11="",E11="!!!"),"",IF(OR(J11=0,AND(J11=1,K11=1),AND(J11=1,I11="SBJ"),AND(J11=1,I11=0)),"?IN_FOCUS",IF(J11&lt;=2,"?ACTIVATED",IF(J11&lt;&gt;"","?FAMILIAR",IF(F11="NEW",IF(ISNA(VLOOKUP(E11,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H11" s="24" t="str">
-        <f>IF(J11&lt;&gt;1,"",IF(I11="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I11" s="25" t="str">
-        <f>IF(OR(E11="",E11="!!!",F11="NEW"),"",INDEX(B10:B$2,-1+SUMPRODUCT(MAX(ROW(E10:E$2)*(E11=E10:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J11" s="25" t="str">
-        <f>IF(OR(E11="",E11="!!!",F11="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E11)*(E11=E$2:E11)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E10)*(E2=E$1:E10))))))</f>
-        <v> </v>
-      </c>
-      <c r="K11" s="25" t="str">
-        <f>IF(OR(E11="",E11="!!!",F11="NEW"),"",INDEX(J$1:J10,SUMPRODUCT(MAX(ROW(E$1:E10)*(E11=E$1:E10)))))</f>
-        <v> </v>
-      </c>
-      <c r="L11" s="26"/>
+      <c r="A11" s="20"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="21">
-        <f>IF(D12="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F12" s="22" t="str">
-        <f>IF(OR(E12="",E12="!!!"),"",IF(NOT(ISNA(VLOOKUP(E12,E$1:E11,1,FALSE()))),"OLD",IF(AND(E12&lt;&gt;"",E12&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G12" s="23" t="str">
-        <f>IF(OR(E12="",E12="!!!"),"",IF(OR(J12=0,AND(J12=1,K12=1),AND(J12=1,I12="SBJ"),AND(J12=1,I12=0)),"?IN_FOCUS",IF(J12&lt;=2,"?ACTIVATED",IF(J12&lt;&gt;"","?FAMILIAR",IF(F12="NEW",IF(ISNA(VLOOKUP(E12,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H12" s="24" t="str">
-        <f>IF(J12&lt;&gt;1,"",IF(I12="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I12" s="25" t="str">
-        <f>IF(OR(E12="",E12="!!!",F12="NEW"),"",INDEX(B11:B$2,-1+SUMPRODUCT(MAX(ROW(E11:E$2)*(E12=E11:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J12" s="25" t="str">
-        <f>IF(OR(E12="",E12="!!!",F12="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E12)*(E12=E$2:E12)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E11)*(E2=E$1:E11))))))</f>
-        <v> </v>
-      </c>
-      <c r="K12" s="25" t="str">
-        <f>IF(OR(E12="",E12="!!!",F12="NEW"),"",INDEX(J$1:J11,SUMPRODUCT(MAX(ROW(E$1:E11)*(E12=E$1:E11)))))</f>
-        <v> </v>
-      </c>
-      <c r="L12" s="26"/>
+        <v>119</v>
+      </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="20" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E13" s="21">
         <f>IF(D13="?OLD","!!!","")</f>
@@ -2685,16 +2702,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E14" s="21">
         <f>IF(D14="?OLD","!!!","")</f>
@@ -2728,7 +2745,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="20" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E15" s="21">
         <f>IF(D15="?OLD","!!!","")</f>
@@ -2761,90 +2778,93 @@
       <c r="L15" s="26"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="20"/>
+      <c r="A16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="21">
+        <f>IF(D16="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F16" s="22" t="str">
+        <f>IF(OR(E16="",E16="!!!"),"",IF(NOT(ISNA(VLOOKUP(E16,E$1:E15,1,FALSE()))),"OLD",IF(AND(E16&lt;&gt;"",E16&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G16" s="23" t="str">
+        <f>IF(OR(E16="",E16="!!!"),"",IF(OR(J16=0,AND(J16=1,K16=1),AND(J16=1,I16="SBJ"),AND(J16=1,I16=0)),"?IN_FOCUS",IF(J16&lt;=2,"?ACTIVATED",IF(J16&lt;&gt;"","?FAMILIAR",IF(F16="NEW",IF(ISNA(VLOOKUP(E16,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H16" s="24" t="str">
+        <f>IF(J16&lt;&gt;1,"",IF(I16="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I16" s="25" t="str">
+        <f>IF(OR(E16="",E16="!!!",F16="NEW"),"",INDEX(B15:B$2,-1+SUMPRODUCT(MAX(ROW(E15:E$2)*(E16=E15:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J16" s="25" t="str">
+        <f>IF(OR(E16="",E16="!!!",F16="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E16)*(E16=E$2:E16)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E15)*(E2=E$1:E15))))))</f>
+        <v> </v>
+      </c>
+      <c r="K16" s="25" t="str">
+        <f>IF(OR(E16="",E16="!!!",F16="NEW"),"",INDEX(J$1:J15,SUMPRODUCT(MAX(ROW(E$1:E15)*(E16=E$1:E15)))))</f>
+        <v> </v>
+      </c>
+      <c r="L16" s="26"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="20" t="s">
-        <v>121</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E17" s="21">
+        <f>IF(D17="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F17" s="22" t="str">
+        <f>IF(OR(E17="",E17="!!!"),"",IF(NOT(ISNA(VLOOKUP(E17,E$1:E16,1,FALSE()))),"OLD",IF(AND(E17&lt;&gt;"",E17&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G17" s="23" t="str">
+        <f>IF(OR(E17="",E17="!!!"),"",IF(OR(J17=0,AND(J17=1,K17=1),AND(J17=1,I17="SBJ"),AND(J17=1,I17=0)),"?IN_FOCUS",IF(J17&lt;=2,"?ACTIVATED",IF(J17&lt;&gt;"","?FAMILIAR",IF(F17="NEW",IF(ISNA(VLOOKUP(E17,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H17" s="24" t="str">
+        <f>IF(J17&lt;&gt;1,"",IF(I17="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I17" s="25" t="str">
+        <f>IF(OR(E17="",E17="!!!",F17="NEW"),"",INDEX(B16:B$2,-1+SUMPRODUCT(MAX(ROW(E16:E$2)*(E17=E16:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J17" s="25" t="str">
+        <f>IF(OR(E17="",E17="!!!",F17="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E17)*(E17=E$2:E17)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E16)*(E2=E$1:E16))))))</f>
+        <v> </v>
+      </c>
+      <c r="K17" s="25" t="str">
+        <f>IF(OR(E17="",E17="!!!",F17="NEW"),"",INDEX(J$1:J16,SUMPRODUCT(MAX(ROW(E$1:E16)*(E17=E$1:E16)))))</f>
+        <v> </v>
+      </c>
+      <c r="L17" s="26"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" s="21">
-        <f>IF(D18="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F18" s="22" t="str">
-        <f>IF(OR(E18="",E18="!!!"),"",IF(NOT(ISNA(VLOOKUP(E18,E$1:E17,1,FALSE()))),"OLD",IF(AND(E18&lt;&gt;"",E18&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G18" s="23" t="str">
-        <f>IF(OR(E18="",E18="!!!"),"",IF(OR(J18=0,AND(J18=1,K18=1),AND(J18=1,I18="SBJ"),AND(J18=1,I18=0)),"?IN_FOCUS",IF(J18&lt;=2,"?ACTIVATED",IF(J18&lt;&gt;"","?FAMILIAR",IF(F18="NEW",IF(ISNA(VLOOKUP(E18,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H18" s="24" t="str">
-        <f>IF(J18&lt;&gt;1,"",IF(I18="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I18" s="25" t="str">
-        <f>IF(OR(E18="",E18="!!!",F18="NEW"),"",INDEX(B17:B$2,-1+SUMPRODUCT(MAX(ROW(E17:E$2)*(E18=E17:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J18" s="25" t="str">
-        <f>IF(OR(E18="",E18="!!!",F18="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E18)*(E18=E$2:E18)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E17)*(E2=E$1:E17))))))</f>
-        <v> </v>
-      </c>
-      <c r="K18" s="25" t="str">
-        <f>IF(OR(E18="",E18="!!!",F18="NEW"),"",INDEX(J$1:J17,SUMPRODUCT(MAX(ROW(E$1:E17)*(E18=E$1:E17)))))</f>
-        <v> </v>
-      </c>
-      <c r="L18" s="26"/>
+      <c r="A18" s="20"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" s="21">
-        <f>IF(D19="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F19" s="22" t="str">
-        <f>IF(OR(E19="",E19="!!!"),"",IF(NOT(ISNA(VLOOKUP(E19,E$1:E18,1,FALSE()))),"OLD",IF(AND(E19&lt;&gt;"",E19&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G19" s="23" t="str">
-        <f>IF(OR(E19="",E19="!!!"),"",IF(OR(J19=0,AND(J19=1,K19=1),AND(J19=1,I19="SBJ"),AND(J19=1,I19=0)),"?IN_FOCUS",IF(J19&lt;=2,"?ACTIVATED",IF(J19&lt;&gt;"","?FAMILIAR",IF(F19="NEW",IF(ISNA(VLOOKUP(E19,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H19" s="24" t="str">
-        <f>IF(J19&lt;&gt;1,"",IF(I19="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I19" s="25" t="str">
-        <f>IF(OR(E19="",E19="!!!",F19="NEW"),"",INDEX(B18:B$2,-1+SUMPRODUCT(MAX(ROW(E18:E$2)*(E19=E18:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J19" s="25" t="str">
-        <f>IF(OR(E19="",E19="!!!",F19="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E19)*(E19=E$2:E19)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E18)*(E2=E$1:E18))))))</f>
-        <v> </v>
-      </c>
-      <c r="K19" s="25" t="str">
-        <f>IF(OR(E19="",E19="!!!",F19="NEW"),"",INDEX(J$1:J18,SUMPRODUCT(MAX(ROW(E$1:E18)*(E19=E$1:E18)))))</f>
-        <v> </v>
-      </c>
-      <c r="L19" s="26"/>
+        <v>127</v>
+      </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E20" s="21">
         <f>IF(D20="?OLD","!!!","")</f>
@@ -2878,7 +2898,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="20" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>130</v>
       </c>
       <c r="E21" s="21">
         <f>IF(D21="?OLD","!!!","")</f>
@@ -2912,16 +2938,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="E22" s="21">
         <f>IF(D22="?OLD","!!!","")</f>
@@ -2955,7 +2972,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="20" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E23" s="21">
         <f>IF(D23="?OLD","!!!","")</f>
@@ -2989,7 +3006,16 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="20" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E24" s="21">
         <f>IF(D24="?OLD","!!!","")</f>
@@ -3023,7 +3049,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E25" s="21">
         <f>IF(D25="?OLD","!!!","")</f>
@@ -3057,13 +3083,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="E26" s="21">
         <f>IF(D26="?OLD","!!!","")</f>
@@ -3097,7 +3117,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E27" s="21">
         <f>IF(D27="?OLD","!!!","")</f>
@@ -3130,86 +3150,23 @@
       <c r="L27" s="26"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" s="21">
-        <f>IF(D28="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F28" s="22" t="str">
-        <f>IF(OR(E28="",E28="!!!"),"",IF(NOT(ISNA(VLOOKUP(E28,E$1:E27,1,FALSE()))),"OLD",IF(AND(E28&lt;&gt;"",E28&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G28" s="23" t="str">
-        <f>IF(OR(E28="",E28="!!!"),"",IF(OR(J28=0,AND(J28=1,K28=1),AND(J28=1,I28="SBJ"),AND(J28=1,I28=0)),"?IN_FOCUS",IF(J28&lt;=2,"?ACTIVATED",IF(J28&lt;&gt;"","?FAMILIAR",IF(F28="NEW",IF(ISNA(VLOOKUP(E28,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H28" s="24" t="str">
-        <f>IF(J28&lt;&gt;1,"",IF(I28="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I28" s="25" t="str">
-        <f>IF(OR(E28="",E28="!!!",F28="NEW"),"",INDEX(B27:B$2,-1+SUMPRODUCT(MAX(ROW(E27:E$2)*(E28=E27:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J28" s="25" t="str">
-        <f>IF(OR(E28="",E28="!!!",F28="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E28)*(E28=E$2:E28)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E27)*(E2=E$1:E27))))))</f>
-        <v> </v>
-      </c>
-      <c r="K28" s="25" t="str">
-        <f>IF(OR(E28="",E28="!!!",F28="NEW"),"",INDEX(J$1:J27,SUMPRODUCT(MAX(ROW(E$1:E27)*(E28=E$1:E27)))))</f>
-        <v> </v>
-      </c>
-      <c r="L28" s="26"/>
+      <c r="A28" s="20"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C29" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" s="21">
-        <f>IF(D29="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F29" s="22" t="str">
-        <f>IF(OR(E29="",E29="!!!"),"",IF(NOT(ISNA(VLOOKUP(E29,E$1:E28,1,FALSE()))),"OLD",IF(AND(E29&lt;&gt;"",E29&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G29" s="23" t="str">
-        <f>IF(OR(E29="",E29="!!!"),"",IF(OR(J29=0,AND(J29=1,K29=1),AND(J29=1,I29="SBJ"),AND(J29=1,I29=0)),"?IN_FOCUS",IF(J29&lt;=2,"?ACTIVATED",IF(J29&lt;&gt;"","?FAMILIAR",IF(F29="NEW",IF(ISNA(VLOOKUP(E29,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H29" s="24" t="str">
-        <f>IF(J29&lt;&gt;1,"",IF(I29="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I29" s="25" t="str">
-        <f>IF(OR(E29="",E29="!!!",F29="NEW"),"",INDEX(B28:B$2,-1+SUMPRODUCT(MAX(ROW(E28:E$2)*(E29=E28:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J29" s="25" t="str">
-        <f>IF(OR(E29="",E29="!!!",F29="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E29)*(E29=E$2:E29)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E28)*(E2=E$1:E28))))))</f>
-        <v> </v>
-      </c>
-      <c r="K29" s="25" t="str">
-        <f>IF(OR(E29="",E29="!!!",F29="NEW"),"",INDEX(J$1:J28,SUMPRODUCT(MAX(ROW(E$1:E28)*(E29=E$1:E28)))))</f>
-        <v> </v>
-      </c>
-      <c r="L29" s="26"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="20" t="s">
         <v>138</v>
       </c>
+      <c r="B30" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>118</v>
+      </c>
       <c r="E30" s="21">
         <f>IF(D30="?OLD","!!!","")</f>
         <v/>
@@ -3242,16 +3199,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="E31" s="21">
         <f>IF(D31="?OLD","!!!","")</f>
@@ -3285,7 +3233,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E32" s="21">
         <f>IF(D32="?OLD","!!!","")</f>
@@ -3319,7 +3267,16 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="20" t="s">
-        <v>107</v>
+        <v>141</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E33" s="21">
         <f>IF(D33="?OLD","!!!","")</f>
@@ -3353,7 +3310,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E34" s="21">
         <f>IF(D34="?OLD","!!!","")</f>
@@ -3387,16 +3344,16 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="20" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E35" s="21">
         <f>IF(D35="?OLD","!!!","")</f>
@@ -3430,7 +3387,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="20" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="E36" s="21">
         <f>IF(D36="?OLD","!!!","")</f>
@@ -3464,7 +3421,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="20" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="E37" s="21">
         <f>IF(D37="?OLD","!!!","")</f>
@@ -3498,16 +3455,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="D38" s="27" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="E38" s="21">
         <f>IF(D38="?OLD","!!!","")</f>
@@ -3541,7 +3489,16 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E39" s="21">
         <f>IF(D39="?OLD","!!!","")</f>
@@ -3575,7 +3532,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="20" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="E40" s="21">
         <f>IF(D40="?OLD","!!!","")</f>
@@ -3609,7 +3566,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="20" t="s">
-        <v>147</v>
+        <v>12</v>
       </c>
       <c r="E41" s="21">
         <f>IF(D41="?OLD","!!!","")</f>
@@ -3643,7 +3600,16 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" s="27" t="s">
         <v>148</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E42" s="21">
         <f>IF(D42="?OLD","!!!","")</f>
@@ -3677,16 +3643,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B43" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" s="27" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="E43" s="21">
         <f>IF(D43="?OLD","!!!","")</f>
@@ -3720,7 +3677,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E44" s="21">
         <f>IF(D44="?OLD","!!!","")</f>
@@ -3754,7 +3711,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="20" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="E45" s="21">
         <f>IF(D45="?OLD","!!!","")</f>
@@ -3788,13 +3745,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C46" s="27" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="E46" s="21">
         <f>IF(D46="?OLD","!!!","")</f>
@@ -3828,7 +3779,16 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="20" t="s">
-        <v>111</v>
+        <v>13</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E47" s="21">
         <f>IF(D47="?OLD","!!!","")</f>
@@ -3862,7 +3822,7 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="20" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E48" s="21">
         <f>IF(D48="?OLD","!!!","")</f>
@@ -3896,7 +3856,7 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="20" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E49" s="21">
         <f>IF(D49="?OLD","!!!","")</f>
@@ -3929,11 +3889,48 @@
       <c r="L49" s="26"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="20"/>
+      <c r="A50" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" s="21">
+        <f>IF(D50="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F50" s="22" t="str">
+        <f>IF(OR(E50="",E50="!!!"),"",IF(NOT(ISNA(VLOOKUP(E50,E$1:E49,1,FALSE()))),"OLD",IF(AND(E50&lt;&gt;"",E50&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G50" s="23" t="str">
+        <f>IF(OR(E50="",E50="!!!"),"",IF(OR(J50=0,AND(J50=1,K50=1),AND(J50=1,I50="SBJ"),AND(J50=1,I50=0)),"?IN_FOCUS",IF(J50&lt;=2,"?ACTIVATED",IF(J50&lt;&gt;"","?FAMILIAR",IF(F50="NEW",IF(ISNA(VLOOKUP(E50,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H50" s="24" t="str">
+        <f>IF(J50&lt;&gt;1,"",IF(I50="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I50" s="25" t="str">
+        <f>IF(OR(E50="",E50="!!!",F50="NEW"),"",INDEX(B49:B$2,-1+SUMPRODUCT(MAX(ROW(E49:E$2)*(E50=E49:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J50" s="25" t="str">
+        <f>IF(OR(E50="",E50="!!!",F50="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E50)*(E50=E$2:E50)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E49)*(E2=E$1:E49))))))</f>
+        <v> </v>
+      </c>
+      <c r="K50" s="25" t="str">
+        <f>IF(OR(E50="",E50="!!!",F50="NEW"),"",INDEX(J$1:J49,SUMPRODUCT(MAX(ROW(E$1:E49)*(E50=E$1:E49)))))</f>
+        <v> </v>
+      </c>
+      <c r="L50" s="26"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="20" t="s">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="E51" s="21">
         <f>IF(D51="?OLD","!!!","")</f>
@@ -3967,21 +3964,41 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="20" t="s">
-        <v>153</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="E52" s="21">
+        <f>IF(D52="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F52" s="22" t="str">
+        <f>IF(OR(E52="",E52="!!!"),"",IF(NOT(ISNA(VLOOKUP(E52,E$1:E51,1,FALSE()))),"OLD",IF(AND(E52&lt;&gt;"",E52&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G52" s="23" t="str">
+        <f>IF(OR(E52="",E52="!!!"),"",IF(OR(J52=0,AND(J52=1,K52=1),AND(J52=1,I52="SBJ"),AND(J52=1,I52=0)),"?IN_FOCUS",IF(J52&lt;=2,"?ACTIVATED",IF(J52&lt;&gt;"","?FAMILIAR",IF(F52="NEW",IF(ISNA(VLOOKUP(E52,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H52" s="24" t="str">
+        <f>IF(J52&lt;&gt;1,"",IF(I52="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I52" s="25" t="str">
+        <f>IF(OR(E52="",E52="!!!",F52="NEW"),"",INDEX(B51:B$2,-1+SUMPRODUCT(MAX(ROW(E51:E$2)*(E52=E51:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J52" s="25" t="str">
+        <f>IF(OR(E52="",E52="!!!",F52="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E52)*(E52=E$2:E52)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E51)*(E2=E$1:E51))))))</f>
+        <v> </v>
+      </c>
+      <c r="K52" s="25" t="str">
+        <f>IF(OR(E52="",E52="!!!",F52="NEW"),"",INDEX(J$1:J51,SUMPRODUCT(MAX(ROW(E$1:E51)*(E52=E$1:E51)))))</f>
+        <v> </v>
+      </c>
+      <c r="L52" s="26"/>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D53" s="27" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E53" s="21">
         <f>IF(D53="?OLD","!!!","")</f>
@@ -4014,42 +4031,11 @@
       <c r="L53" s="26"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="E54" s="21">
-        <f>IF(D54="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F54" s="22" t="str">
-        <f>IF(OR(E54="",E54="!!!"),"",IF(NOT(ISNA(VLOOKUP(E54,E$1:E53,1,FALSE()))),"OLD",IF(AND(E54&lt;&gt;"",E54&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G54" s="23" t="str">
-        <f>IF(OR(E54="",E54="!!!"),"",IF(OR(J54=0,AND(J54=1,K54=1),AND(J54=1,I54="SBJ"),AND(J54=1,I54=0)),"?IN_FOCUS",IF(J54&lt;=2,"?ACTIVATED",IF(J54&lt;&gt;"","?FAMILIAR",IF(F54="NEW",IF(ISNA(VLOOKUP(E54,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H54" s="24" t="str">
-        <f>IF(J54&lt;&gt;1,"",IF(I54="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I54" s="25" t="str">
-        <f>IF(OR(E54="",E54="!!!",F54="NEW"),"",INDEX(B53:B$2,-1+SUMPRODUCT(MAX(ROW(E53:E$2)*(E54=E53:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J54" s="25" t="str">
-        <f>IF(OR(E54="",E54="!!!",F54="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E54)*(E54=E$2:E54)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E53)*(E2=E$1:E53))))))</f>
-        <v> </v>
-      </c>
-      <c r="K54" s="25" t="str">
-        <f>IF(OR(E54="",E54="!!!",F54="NEW"),"",INDEX(J$1:J53,SUMPRODUCT(MAX(ROW(E$1:E53)*(E54=E$1:E53)))))</f>
-        <v> </v>
-      </c>
-      <c r="L54" s="26"/>
+      <c r="A54" s="20"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="20" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="E55" s="21">
         <f>IF(D55="?OLD","!!!","")</f>
@@ -4083,50 +4069,21 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B56" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C56" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D56" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E56" s="21">
-        <f>IF(D56="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F56" s="22" t="str">
-        <f>IF(OR(E56="",E56="!!!"),"",IF(NOT(ISNA(VLOOKUP(E56,E$1:E55,1,FALSE()))),"OLD",IF(AND(E56&lt;&gt;"",E56&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G56" s="23" t="str">
-        <f>IF(OR(E56="",E56="!!!"),"",IF(OR(J56=0,AND(J56=1,K56=1),AND(J56=1,I56="SBJ"),AND(J56=1,I56=0)),"?IN_FOCUS",IF(J56&lt;=2,"?ACTIVATED",IF(J56&lt;&gt;"","?FAMILIAR",IF(F56="NEW",IF(ISNA(VLOOKUP(E56,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H56" s="24" t="str">
-        <f>IF(J56&lt;&gt;1,"",IF(I56="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I56" s="25" t="str">
-        <f>IF(OR(E56="",E56="!!!",F56="NEW"),"",INDEX(B55:B$2,-1+SUMPRODUCT(MAX(ROW(E55:E$2)*(E56=E55:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J56" s="25" t="str">
-        <f>IF(OR(E56="",E56="!!!",F56="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E56)*(E56=E$2:E56)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E55)*(E2=E$1:E55))))))</f>
-        <v> </v>
-      </c>
-      <c r="K56" s="25" t="str">
-        <f>IF(OR(E56="",E56="!!!",F56="NEW"),"",INDEX(J$1:J55,SUMPRODUCT(MAX(ROW(E$1:E55)*(E56=E$1:E55)))))</f>
-        <v> </v>
-      </c>
-      <c r="L56" s="26"/>
+        <v>159</v>
+      </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="20" t="s">
-        <v>156</v>
+        <v>160</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E57" s="21">
         <f>IF(D57="?OLD","!!!","")</f>
@@ -4194,13 +4151,7 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C59" s="27" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="E59" s="21">
         <f>IF(D59="?OLD","!!!","")</f>
@@ -4234,7 +4185,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="20" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E60" s="21">
         <f>IF(D60="?OLD","!!!","")</f>
@@ -4268,7 +4228,7 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E61" s="21">
         <f>IF(D61="?OLD","!!!","")</f>
@@ -4302,16 +4262,7 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C62" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D62" s="27" t="s">
-        <v>105</v>
+        <v>163</v>
       </c>
       <c r="E62" s="21">
         <f>IF(D62="?OLD","!!!","")</f>
@@ -4345,7 +4296,13 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="20" t="s">
-        <v>161</v>
+        <v>164</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C63" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E63" s="21">
         <f>IF(D63="?OLD","!!!","")</f>
@@ -4379,7 +4336,7 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="20" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="E64" s="21">
         <f>IF(D64="?OLD","!!!","")</f>
@@ -4413,10 +4370,7 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B65" s="27" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="E65" s="21">
         <f>IF(D65="?OLD","!!!","")</f>
@@ -4450,10 +4404,16 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="20" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>164</v>
+        <v>117</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E66" s="21">
         <f>IF(D66="?OLD","!!!","")</f>
@@ -4487,7 +4447,7 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="20" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E67" s="21">
         <f>IF(D67="?OLD","!!!","")</f>
@@ -4521,16 +4481,7 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="B68" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C68" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D68" s="27" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="E68" s="21">
         <f>IF(D68="?OLD","!!!","")</f>
@@ -4564,7 +4515,10 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" s="20" t="s">
-        <v>166</v>
+        <v>153</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>169</v>
       </c>
       <c r="E69" s="21">
         <f>IF(D69="?OLD","!!!","")</f>
@@ -4598,13 +4552,10 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" s="20" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C70" s="27" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E70" s="21">
         <f>IF(D70="?OLD","!!!","")</f>
@@ -4638,7 +4589,7 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="20" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E71" s="21">
         <f>IF(D71="?OLD","!!!","")</f>
@@ -4672,7 +4623,16 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="B72" s="27" t="s">
         <v>169</v>
+      </c>
+      <c r="C72" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D72" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E72" s="21">
         <f>IF(D72="?OLD","!!!","")</f>
@@ -4706,16 +4666,7 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="B73" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="E73" s="21">
         <f>IF(D73="?OLD","!!!","")</f>
@@ -4749,7 +4700,13 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="20" t="s">
-        <v>160</v>
+        <v>174</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C74" s="27" t="s">
+        <v>176</v>
       </c>
       <c r="E74" s="21">
         <f>IF(D74="?OLD","!!!","")</f>
@@ -4783,16 +4740,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C75" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D75" s="27" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="E75" s="21">
         <f>IF(D75="?OLD","!!!","")</f>
@@ -4826,7 +4774,7 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E76" s="21">
         <f>IF(D76="?OLD","!!!","")</f>
@@ -4860,7 +4808,16 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="20" t="s">
-        <v>120</v>
+        <v>178</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C77" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="D77" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E77" s="21">
         <f>IF(D77="?OLD","!!!","")</f>
@@ -4893,16 +4850,85 @@
       <c r="L77" s="26"/>
     </row>
     <row r="78" spans="1:12">
-      <c r="A78" s="20"/>
+      <c r="A78" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="E78" s="21">
+        <f>IF(D78="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F78" s="22" t="str">
+        <f>IF(OR(E78="",E78="!!!"),"",IF(NOT(ISNA(VLOOKUP(E78,E$1:E77,1,FALSE()))),"OLD",IF(AND(E78&lt;&gt;"",E78&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G78" s="23" t="str">
+        <f>IF(OR(E78="",E78="!!!"),"",IF(OR(J78=0,AND(J78=1,K78=1),AND(J78=1,I78="SBJ"),AND(J78=1,I78=0)),"?IN_FOCUS",IF(J78&lt;=2,"?ACTIVATED",IF(J78&lt;&gt;"","?FAMILIAR",IF(F78="NEW",IF(ISNA(VLOOKUP(E78,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H78" s="24" t="str">
+        <f>IF(J78&lt;&gt;1,"",IF(I78="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I78" s="25" t="str">
+        <f>IF(OR(E78="",E78="!!!",F78="NEW"),"",INDEX(B77:B$2,-1+SUMPRODUCT(MAX(ROW(E77:E$2)*(E78=E77:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J78" s="25" t="str">
+        <f>IF(OR(E78="",E78="!!!",F78="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E78)*(E78=E$2:E78)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E77)*(E2=E$1:E77))))))</f>
+        <v> </v>
+      </c>
+      <c r="K78" s="25" t="str">
+        <f>IF(OR(E78="",E78="!!!",F78="NEW"),"",INDEX(J$1:J77,SUMPRODUCT(MAX(ROW(E$1:E77)*(E78=E$1:E77)))))</f>
+        <v> </v>
+      </c>
+      <c r="L78" s="26"/>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="20" t="s">
-        <v>175</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C79" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D79" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" s="21">
+        <f>IF(D79="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F79" s="22" t="str">
+        <f>IF(OR(E79="",E79="!!!"),"",IF(NOT(ISNA(VLOOKUP(E79,E$1:E78,1,FALSE()))),"OLD",IF(AND(E79&lt;&gt;"",E79&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G79" s="23" t="str">
+        <f>IF(OR(E79="",E79="!!!"),"",IF(OR(J79=0,AND(J79=1,K79=1),AND(J79=1,I79="SBJ"),AND(J79=1,I79=0)),"?IN_FOCUS",IF(J79&lt;=2,"?ACTIVATED",IF(J79&lt;&gt;"","?FAMILIAR",IF(F79="NEW",IF(ISNA(VLOOKUP(E79,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H79" s="24" t="str">
+        <f>IF(J79&lt;&gt;1,"",IF(I79="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I79" s="25" t="str">
+        <f>IF(OR(E79="",E79="!!!",F79="NEW"),"",INDEX(B78:B$2,-1+SUMPRODUCT(MAX(ROW(E78:E$2)*(E79=E78:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J79" s="25" t="str">
+        <f>IF(OR(E79="",E79="!!!",F79="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E79)*(E79=E$2:E79)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E78)*(E2=E$1:E78))))))</f>
+        <v> </v>
+      </c>
+      <c r="K79" s="25" t="str">
+        <f>IF(OR(E79="",E79="!!!",F79="NEW"),"",INDEX(J$1:J78,SUMPRODUCT(MAX(ROW(E$1:E78)*(E79=E$1:E78)))))</f>
+        <v> </v>
+      </c>
+      <c r="L79" s="26"/>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="20" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E80" s="21">
         <f>IF(D80="?OLD","!!!","")</f>
@@ -4936,16 +4962,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="B81" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C81" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D81" s="27" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E81" s="21">
         <f>IF(D81="?OLD","!!!","")</f>
@@ -4978,85 +4995,16 @@
       <c r="L81" s="26"/>
     </row>
     <row r="82" spans="1:12">
-      <c r="A82" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="E82" s="21">
-        <f>IF(D82="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F82" s="22" t="str">
-        <f>IF(OR(E82="",E82="!!!"),"",IF(NOT(ISNA(VLOOKUP(E82,E$1:E81,1,FALSE()))),"OLD",IF(AND(E82&lt;&gt;"",E82&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G82" s="23" t="str">
-        <f>IF(OR(E82="",E82="!!!"),"",IF(OR(J82=0,AND(J82=1,K82=1),AND(J82=1,I82="SBJ"),AND(J82=1,I82=0)),"?IN_FOCUS",IF(J82&lt;=2,"?ACTIVATED",IF(J82&lt;&gt;"","?FAMILIAR",IF(F82="NEW",IF(ISNA(VLOOKUP(E82,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H82" s="24" t="str">
-        <f>IF(J82&lt;&gt;1,"",IF(I82="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I82" s="25" t="str">
-        <f>IF(OR(E82="",E82="!!!",F82="NEW"),"",INDEX(B81:B$2,-1+SUMPRODUCT(MAX(ROW(E81:E$2)*(E82=E81:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J82" s="25" t="str">
-        <f>IF(OR(E82="",E82="!!!",F82="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E82)*(E82=E$2:E82)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E81)*(E2=E$1:E81))))))</f>
-        <v> </v>
-      </c>
-      <c r="K82" s="25" t="str">
-        <f>IF(OR(E82="",E82="!!!",F82="NEW"),"",INDEX(J$1:J81,SUMPRODUCT(MAX(ROW(E$1:E81)*(E82=E$1:E81)))))</f>
-        <v> </v>
-      </c>
-      <c r="L82" s="26"/>
+      <c r="A82" s="20"/>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B83" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C83" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D83" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E83" s="21">
-        <f>IF(D83="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F83" s="22" t="str">
-        <f>IF(OR(E83="",E83="!!!"),"",IF(NOT(ISNA(VLOOKUP(E83,E$1:E82,1,FALSE()))),"OLD",IF(AND(E83&lt;&gt;"",E83&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G83" s="23" t="str">
-        <f>IF(OR(E83="",E83="!!!"),"",IF(OR(J83=0,AND(J83=1,K83=1),AND(J83=1,I83="SBJ"),AND(J83=1,I83=0)),"?IN_FOCUS",IF(J83&lt;=2,"?ACTIVATED",IF(J83&lt;&gt;"","?FAMILIAR",IF(F83="NEW",IF(ISNA(VLOOKUP(E83,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H83" s="24" t="str">
-        <f>IF(J83&lt;&gt;1,"",IF(I83="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I83" s="25" t="str">
-        <f>IF(OR(E83="",E83="!!!",F83="NEW"),"",INDEX(B82:B$2,-1+SUMPRODUCT(MAX(ROW(E82:E$2)*(E83=E82:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J83" s="25" t="str">
-        <f>IF(OR(E83="",E83="!!!",F83="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E83)*(E83=E$2:E83)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E82)*(E2=E$1:E82))))))</f>
-        <v> </v>
-      </c>
-      <c r="K83" s="25" t="str">
-        <f>IF(OR(E83="",E83="!!!",F83="NEW"),"",INDEX(J$1:J82,SUMPRODUCT(MAX(ROW(E$1:E82)*(E83=E$1:E82)))))</f>
-        <v> </v>
-      </c>
-      <c r="L83" s="26"/>
+        <v>183</v>
+      </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="20" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="E84" s="21">
         <f>IF(D84="?OLD","!!!","")</f>
@@ -5090,7 +5038,16 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="20" t="s">
-        <v>149</v>
+        <v>185</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C85" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D85" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E85" s="21">
         <f>IF(D85="?OLD","!!!","")</f>
@@ -5124,7 +5081,7 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="20" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="E86" s="21">
         <f>IF(D86="?OLD","!!!","")</f>
@@ -5158,13 +5115,16 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="20" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C87" s="27" t="s">
-        <v>159</v>
+        <v>112</v>
+      </c>
+      <c r="D87" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E87" s="21">
         <f>IF(D87="?OLD","!!!","")</f>
@@ -5198,7 +5158,7 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="20" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="E88" s="21">
         <f>IF(D88="?OLD","!!!","")</f>
@@ -5232,7 +5192,7 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" s="20" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="E89" s="21">
         <f>IF(D89="?OLD","!!!","")</f>
@@ -5266,7 +5226,7 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="20" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E90" s="21">
         <f>IF(D90="?OLD","!!!","")</f>
@@ -5300,7 +5260,13 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="20" t="s">
-        <v>183</v>
+        <v>187</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C91" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E91" s="21">
         <f>IF(D91="?OLD","!!!","")</f>
@@ -5334,13 +5300,7 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="B92" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="C92" s="27" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="E92" s="21">
         <f>IF(D92="?OLD","!!!","")</f>
@@ -5374,7 +5334,7 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="20" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="E93" s="21">
         <f>IF(D93="?OLD","!!!","")</f>
@@ -5407,25 +5367,82 @@
       <c r="L93" s="26"/>
     </row>
     <row r="94" spans="1:12">
-      <c r="A94" s="20"/>
+      <c r="A94" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E94" s="21">
+        <f>IF(D94="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F94" s="22" t="str">
+        <f>IF(OR(E94="",E94="!!!"),"",IF(NOT(ISNA(VLOOKUP(E94,E$1:E93,1,FALSE()))),"OLD",IF(AND(E94&lt;&gt;"",E94&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G94" s="23" t="str">
+        <f>IF(OR(E94="",E94="!!!"),"",IF(OR(J94=0,AND(J94=1,K94=1),AND(J94=1,I94="SBJ"),AND(J94=1,I94=0)),"?IN_FOCUS",IF(J94&lt;=2,"?ACTIVATED",IF(J94&lt;&gt;"","?FAMILIAR",IF(F94="NEW",IF(ISNA(VLOOKUP(E94,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H94" s="24" t="str">
+        <f>IF(J94&lt;&gt;1,"",IF(I94="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I94" s="25" t="str">
+        <f>IF(OR(E94="",E94="!!!",F94="NEW"),"",INDEX(B93:B$2,-1+SUMPRODUCT(MAX(ROW(E93:E$2)*(E94=E93:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J94" s="25" t="str">
+        <f>IF(OR(E94="",E94="!!!",F94="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E94)*(E94=E$2:E94)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E93)*(E2=E$1:E93))))))</f>
+        <v> </v>
+      </c>
+      <c r="K94" s="25" t="str">
+        <f>IF(OR(E94="",E94="!!!",F94="NEW"),"",INDEX(J$1:J93,SUMPRODUCT(MAX(ROW(E$1:E93)*(E94=E$1:E93)))))</f>
+        <v> </v>
+      </c>
+      <c r="L94" s="26"/>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="20" t="s">
-        <v>186</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="E95" s="21">
+        <f>IF(D95="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F95" s="22" t="str">
+        <f>IF(OR(E95="",E95="!!!"),"",IF(NOT(ISNA(VLOOKUP(E95,E$1:E94,1,FALSE()))),"OLD",IF(AND(E95&lt;&gt;"",E95&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G95" s="23" t="str">
+        <f>IF(OR(E95="",E95="!!!"),"",IF(OR(J95=0,AND(J95=1,K95=1),AND(J95=1,I95="SBJ"),AND(J95=1,I95=0)),"?IN_FOCUS",IF(J95&lt;=2,"?ACTIVATED",IF(J95&lt;&gt;"","?FAMILIAR",IF(F95="NEW",IF(ISNA(VLOOKUP(E95,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H95" s="24" t="str">
+        <f>IF(J95&lt;&gt;1,"",IF(I95="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I95" s="25" t="str">
+        <f>IF(OR(E95="",E95="!!!",F95="NEW"),"",INDEX(B94:B$2,-1+SUMPRODUCT(MAX(ROW(E94:E$2)*(E95=E94:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J95" s="25" t="str">
+        <f>IF(OR(E95="",E95="!!!",F95="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E95)*(E95=E$2:E95)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E94)*(E2=E$1:E94))))))</f>
+        <v> </v>
+      </c>
+      <c r="K95" s="25" t="str">
+        <f>IF(OR(E95="",E95="!!!",F95="NEW"),"",INDEX(J$1:J94,SUMPRODUCT(MAX(ROW(E$1:E94)*(E95=E$1:E94)))))</f>
+        <v> </v>
+      </c>
+      <c r="L95" s="26"/>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="20" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>124</v>
+        <v>193</v>
       </c>
       <c r="C96" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D96" s="27" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="E96" s="21">
         <f>IF(D96="?OLD","!!!","")</f>
@@ -5459,7 +5476,7 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="20" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="E97" s="21">
         <f>IF(D97="?OLD","!!!","")</f>
@@ -5492,76 +5509,25 @@
       <c r="L97" s="26"/>
     </row>
     <row r="98" spans="1:12">
-      <c r="A98" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="E98" s="21">
-        <f>IF(D98="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F98" s="22" t="str">
-        <f>IF(OR(E98="",E98="!!!"),"",IF(NOT(ISNA(VLOOKUP(E98,E$1:E97,1,FALSE()))),"OLD",IF(AND(E98&lt;&gt;"",E98&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G98" s="23" t="str">
-        <f>IF(OR(E98="",E98="!!!"),"",IF(OR(J98=0,AND(J98=1,K98=1),AND(J98=1,I98="SBJ"),AND(J98=1,I98=0)),"?IN_FOCUS",IF(J98&lt;=2,"?ACTIVATED",IF(J98&lt;&gt;"","?FAMILIAR",IF(F98="NEW",IF(ISNA(VLOOKUP(E98,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H98" s="24" t="str">
-        <f>IF(J98&lt;&gt;1,"",IF(I98="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I98" s="25" t="str">
-        <f>IF(OR(E98="",E98="!!!",F98="NEW"),"",INDEX(B97:B$2,-1+SUMPRODUCT(MAX(ROW(E97:E$2)*(E98=E97:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J98" s="25" t="str">
-        <f>IF(OR(E98="",E98="!!!",F98="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E98)*(E98=E$2:E98)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E97)*(E2=E$1:E97))))))</f>
-        <v> </v>
-      </c>
-      <c r="K98" s="25" t="str">
-        <f>IF(OR(E98="",E98="!!!",F98="NEW"),"",INDEX(J$1:J97,SUMPRODUCT(MAX(ROW(E$1:E97)*(E98=E$1:E97)))))</f>
-        <v> </v>
-      </c>
-      <c r="L98" s="26"/>
+      <c r="A98" s="20"/>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E99" s="21">
-        <f>IF(D99="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F99" s="22" t="str">
-        <f>IF(OR(E99="",E99="!!!"),"",IF(NOT(ISNA(VLOOKUP(E99,E$1:E98,1,FALSE()))),"OLD",IF(AND(E99&lt;&gt;"",E99&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G99" s="23" t="str">
-        <f>IF(OR(E99="",E99="!!!"),"",IF(OR(J99=0,AND(J99=1,K99=1),AND(J99=1,I99="SBJ"),AND(J99=1,I99=0)),"?IN_FOCUS",IF(J99&lt;=2,"?ACTIVATED",IF(J99&lt;&gt;"","?FAMILIAR",IF(F99="NEW",IF(ISNA(VLOOKUP(E99,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H99" s="24" t="str">
-        <f>IF(J99&lt;&gt;1,"",IF(I99="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I99" s="25" t="str">
-        <f>IF(OR(E99="",E99="!!!",F99="NEW"),"",INDEX(B98:B$2,-1+SUMPRODUCT(MAX(ROW(E98:E$2)*(E99=E98:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J99" s="25" t="str">
-        <f>IF(OR(E99="",E99="!!!",F99="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E99)*(E99=E$2:E99)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E98)*(E2=E$1:E98))))))</f>
-        <v> </v>
-      </c>
-      <c r="K99" s="25" t="str">
-        <f>IF(OR(E99="",E99="!!!",F99="NEW"),"",INDEX(J$1:J98,SUMPRODUCT(MAX(ROW(E$1:E98)*(E99=E$1:E98)))))</f>
-        <v> </v>
-      </c>
-      <c r="L99" s="26"/>
+        <v>194</v>
+      </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="20" t="s">
-        <v>184</v>
+        <v>195</v>
+      </c>
+      <c r="B100" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C100" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D100" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E100" s="21">
         <f>IF(D100="?OLD","!!!","")</f>
@@ -5595,13 +5561,7 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="B101" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C101" s="27" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="E101" s="21">
         <f>IF(D101="?OLD","!!!","")</f>
@@ -5635,7 +5595,7 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" s="20" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="E102" s="21">
         <f>IF(D102="?OLD","!!!","")</f>
@@ -5669,7 +5629,7 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" s="20" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E103" s="21">
         <f>IF(D103="?OLD","!!!","")</f>
@@ -5703,7 +5663,7 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" s="20" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E104" s="21">
         <f>IF(D104="?OLD","!!!","")</f>
@@ -5737,13 +5697,13 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" s="20" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C105" s="27" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E105" s="21">
         <f>IF(D105="?OLD","!!!","")</f>
@@ -5777,7 +5737,7 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E106" s="21">
         <f>IF(D106="?OLD","!!!","")</f>
@@ -5811,7 +5771,7 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="20" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E107" s="21">
         <f>IF(D107="?OLD","!!!","")</f>
@@ -5845,13 +5805,7 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B108" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C108" s="27" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="E108" s="21">
         <f>IF(D108="?OLD","!!!","")</f>
@@ -5885,7 +5839,13 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" s="20" t="s">
-        <v>120</v>
+        <v>201</v>
+      </c>
+      <c r="B109" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C109" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="E109" s="21">
         <f>IF(D109="?OLD","!!!","")</f>
@@ -5918,16 +5878,82 @@
       <c r="L109" s="26"/>
     </row>
     <row r="110" spans="1:12">
-      <c r="A110" s="20"/>
+      <c r="A110" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="E110" s="21">
+        <f>IF(D110="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F110" s="22" t="str">
+        <f>IF(OR(E110="",E110="!!!"),"",IF(NOT(ISNA(VLOOKUP(E110,E$1:E109,1,FALSE()))),"OLD",IF(AND(E110&lt;&gt;"",E110&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G110" s="23" t="str">
+        <f>IF(OR(E110="",E110="!!!"),"",IF(OR(J110=0,AND(J110=1,K110=1),AND(J110=1,I110="SBJ"),AND(J110=1,I110=0)),"?IN_FOCUS",IF(J110&lt;=2,"?ACTIVATED",IF(J110&lt;&gt;"","?FAMILIAR",IF(F110="NEW",IF(ISNA(VLOOKUP(E110,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H110" s="24" t="str">
+        <f>IF(J110&lt;&gt;1,"",IF(I110="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I110" s="25" t="str">
+        <f>IF(OR(E110="",E110="!!!",F110="NEW"),"",INDEX(B109:B$2,-1+SUMPRODUCT(MAX(ROW(E109:E$2)*(E110=E109:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J110" s="25" t="str">
+        <f>IF(OR(E110="",E110="!!!",F110="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E110)*(E110=E$2:E110)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E109)*(E2=E$1:E109))))))</f>
+        <v> </v>
+      </c>
+      <c r="K110" s="25" t="str">
+        <f>IF(OR(E110="",E110="!!!",F110="NEW"),"",INDEX(J$1:J109,SUMPRODUCT(MAX(ROW(E$1:E109)*(E110=E$1:E109)))))</f>
+        <v> </v>
+      </c>
+      <c r="L110" s="26"/>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" s="20" t="s">
-        <v>197</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="E111" s="21">
+        <f>IF(D111="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F111" s="22" t="str">
+        <f>IF(OR(E111="",E111="!!!"),"",IF(NOT(ISNA(VLOOKUP(E111,E$1:E110,1,FALSE()))),"OLD",IF(AND(E111&lt;&gt;"",E111&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G111" s="23" t="str">
+        <f>IF(OR(E111="",E111="!!!"),"",IF(OR(J111=0,AND(J111=1,K111=1),AND(J111=1,I111="SBJ"),AND(J111=1,I111=0)),"?IN_FOCUS",IF(J111&lt;=2,"?ACTIVATED",IF(J111&lt;&gt;"","?FAMILIAR",IF(F111="NEW",IF(ISNA(VLOOKUP(E111,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H111" s="24" t="str">
+        <f>IF(J111&lt;&gt;1,"",IF(I111="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I111" s="25" t="str">
+        <f>IF(OR(E111="",E111="!!!",F111="NEW"),"",INDEX(B110:B$2,-1+SUMPRODUCT(MAX(ROW(E110:E$2)*(E111=E110:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J111" s="25" t="str">
+        <f>IF(OR(E111="",E111="!!!",F111="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E111)*(E111=E$2:E111)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E110)*(E2=E$1:E110))))))</f>
+        <v> </v>
+      </c>
+      <c r="K111" s="25" t="str">
+        <f>IF(OR(E111="",E111="!!!",F111="NEW"),"",INDEX(J$1:J110,SUMPRODUCT(MAX(ROW(E$1:E110)*(E111=E$1:E110)))))</f>
+        <v> </v>
+      </c>
+      <c r="L111" s="26"/>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" s="20" t="s">
-        <v>112</v>
+        <v>204</v>
+      </c>
+      <c r="B112" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C112" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E112" s="21">
         <f>IF(D112="?OLD","!!!","")</f>
@@ -5961,16 +5987,7 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B113" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C113" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D113" s="27" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E113" s="21">
         <f>IF(D113="?OLD","!!!","")</f>
@@ -6003,82 +6020,16 @@
       <c r="L113" s="26"/>
     </row>
     <row r="114" spans="1:12">
-      <c r="A114" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E114" s="21">
-        <f>IF(D114="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F114" s="22" t="str">
-        <f>IF(OR(E114="",E114="!!!"),"",IF(NOT(ISNA(VLOOKUP(E114,E$1:E113,1,FALSE()))),"OLD",IF(AND(E114&lt;&gt;"",E114&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G114" s="23" t="str">
-        <f>IF(OR(E114="",E114="!!!"),"",IF(OR(J114=0,AND(J114=1,K114=1),AND(J114=1,I114="SBJ"),AND(J114=1,I114=0)),"?IN_FOCUS",IF(J114&lt;=2,"?ACTIVATED",IF(J114&lt;&gt;"","?FAMILIAR",IF(F114="NEW",IF(ISNA(VLOOKUP(E114,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H114" s="24" t="str">
-        <f>IF(J114&lt;&gt;1,"",IF(I114="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I114" s="25" t="str">
-        <f>IF(OR(E114="",E114="!!!",F114="NEW"),"",INDEX(B113:B$2,-1+SUMPRODUCT(MAX(ROW(E113:E$2)*(E114=E113:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J114" s="25" t="str">
-        <f>IF(OR(E114="",E114="!!!",F114="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E114)*(E114=E$2:E114)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E113)*(E2=E$1:E113))))))</f>
-        <v> </v>
-      </c>
-      <c r="K114" s="25" t="str">
-        <f>IF(OR(E114="",E114="!!!",F114="NEW"),"",INDEX(J$1:J113,SUMPRODUCT(MAX(ROW(E$1:E113)*(E114=E$1:E113)))))</f>
-        <v> </v>
-      </c>
-      <c r="L114" s="26"/>
+      <c r="A114" s="20"/>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="B115" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C115" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E115" s="21">
-        <f>IF(D115="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F115" s="22" t="str">
-        <f>IF(OR(E115="",E115="!!!"),"",IF(NOT(ISNA(VLOOKUP(E115,E$1:E114,1,FALSE()))),"OLD",IF(AND(E115&lt;&gt;"",E115&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G115" s="23" t="str">
-        <f>IF(OR(E115="",E115="!!!"),"",IF(OR(J115=0,AND(J115=1,K115=1),AND(J115=1,I115="SBJ"),AND(J115=1,I115=0)),"?IN_FOCUS",IF(J115&lt;=2,"?ACTIVATED",IF(J115&lt;&gt;"","?FAMILIAR",IF(F115="NEW",IF(ISNA(VLOOKUP(E115,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H115" s="24" t="str">
-        <f>IF(J115&lt;&gt;1,"",IF(I115="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I115" s="25" t="str">
-        <f>IF(OR(E115="",E115="!!!",F115="NEW"),"",INDEX(B114:B$2,-1+SUMPRODUCT(MAX(ROW(E114:E$2)*(E115=E114:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J115" s="25" t="str">
-        <f>IF(OR(E115="",E115="!!!",F115="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E115)*(E115=E$2:E115)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E114)*(E2=E$1:E114))))))</f>
-        <v> </v>
-      </c>
-      <c r="K115" s="25" t="str">
-        <f>IF(OR(E115="",E115="!!!",F115="NEW"),"",INDEX(J$1:J114,SUMPRODUCT(MAX(ROW(E$1:E114)*(E115=E$1:E114)))))</f>
-        <v> </v>
-      </c>
-      <c r="L115" s="26"/>
+        <v>205</v>
+      </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E116" s="21">
         <f>IF(D116="?OLD","!!!","")</f>
@@ -6112,13 +6063,16 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C117" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="B117" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C117" s="27" t="s">
-        <v>110</v>
+      <c r="D117" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E117" s="21">
         <f>IF(D117="?OLD","!!!","")</f>
@@ -6152,7 +6106,7 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" s="20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E118" s="21">
         <f>IF(D118="?OLD","!!!","")</f>
@@ -6186,7 +6140,13 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" s="20" t="s">
-        <v>127</v>
+        <v>206</v>
+      </c>
+      <c r="B119" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E119" s="21">
         <f>IF(D119="?OLD","!!!","")</f>
@@ -6222,15 +6182,6 @@
       <c r="A120" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B120" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C120" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D120" s="27" t="s">
-        <v>105</v>
-      </c>
       <c r="E120" s="21">
         <f>IF(D120="?OLD","!!!","")</f>
         <v/>
@@ -6265,6 +6216,12 @@
       <c r="A121" s="20" t="s">
         <v>129</v>
       </c>
+      <c r="B121" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C121" s="27" t="s">
+        <v>118</v>
+      </c>
       <c r="E121" s="21">
         <f>IF(D121="?OLD","!!!","")</f>
         <v/>
@@ -6297,7 +6254,7 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E122" s="21">
         <f>IF(D122="?OLD","!!!","")</f>
@@ -6331,7 +6288,7 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" s="20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E123" s="21">
         <f>IF(D123="?OLD","!!!","")</f>
@@ -6365,7 +6322,16 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" s="20" t="s">
-        <v>120</v>
+        <v>133</v>
+      </c>
+      <c r="B124" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C124" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D124" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E124" s="21">
         <f>IF(D124="?OLD","!!!","")</f>
@@ -6398,22 +6364,76 @@
       <c r="L124" s="26"/>
     </row>
     <row r="125" spans="1:12">
-      <c r="A125" s="20"/>
+      <c r="A125" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E125" s="21">
+        <f>IF(D125="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F125" s="22" t="str">
+        <f>IF(OR(E125="",E125="!!!"),"",IF(NOT(ISNA(VLOOKUP(E125,E$1:E124,1,FALSE()))),"OLD",IF(AND(E125&lt;&gt;"",E125&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G125" s="23" t="str">
+        <f>IF(OR(E125="",E125="!!!"),"",IF(OR(J125=0,AND(J125=1,K125=1),AND(J125=1,I125="SBJ"),AND(J125=1,I125=0)),"?IN_FOCUS",IF(J125&lt;=2,"?ACTIVATED",IF(J125&lt;&gt;"","?FAMILIAR",IF(F125="NEW",IF(ISNA(VLOOKUP(E125,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H125" s="24" t="str">
+        <f>IF(J125&lt;&gt;1,"",IF(I125="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I125" s="25" t="str">
+        <f>IF(OR(E125="",E125="!!!",F125="NEW"),"",INDEX(B124:B$2,-1+SUMPRODUCT(MAX(ROW(E124:E$2)*(E125=E124:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J125" s="25" t="str">
+        <f>IF(OR(E125="",E125="!!!",F125="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E125)*(E125=E$2:E125)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E124)*(E2=E$1:E124))))))</f>
+        <v> </v>
+      </c>
+      <c r="K125" s="25" t="str">
+        <f>IF(OR(E125="",E125="!!!",F125="NEW"),"",INDEX(J$1:J124,SUMPRODUCT(MAX(ROW(E$1:E124)*(E125=E$1:E124)))))</f>
+        <v> </v>
+      </c>
+      <c r="L125" s="26"/>
     </row>
     <row r="126" spans="1:12">
       <c r="A126" s="20" t="s">
-        <v>200</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="E126" s="21">
+        <f>IF(D126="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F126" s="22" t="str">
+        <f>IF(OR(E126="",E126="!!!"),"",IF(NOT(ISNA(VLOOKUP(E126,E$1:E125,1,FALSE()))),"OLD",IF(AND(E126&lt;&gt;"",E126&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G126" s="23" t="str">
+        <f>IF(OR(E126="",E126="!!!"),"",IF(OR(J126=0,AND(J126=1,K126=1),AND(J126=1,I126="SBJ"),AND(J126=1,I126=0)),"?IN_FOCUS",IF(J126&lt;=2,"?ACTIVATED",IF(J126&lt;&gt;"","?FAMILIAR",IF(F126="NEW",IF(ISNA(VLOOKUP(E126,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H126" s="24" t="str">
+        <f>IF(J126&lt;&gt;1,"",IF(I126="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I126" s="25" t="str">
+        <f>IF(OR(E126="",E126="!!!",F126="NEW"),"",INDEX(B125:B$2,-1+SUMPRODUCT(MAX(ROW(E125:E$2)*(E126=E125:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J126" s="25" t="str">
+        <f>IF(OR(E126="",E126="!!!",F126="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E126)*(E126=E$2:E126)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E125)*(E2=E$1:E125))))))</f>
+        <v> </v>
+      </c>
+      <c r="K126" s="25" t="str">
+        <f>IF(OR(E126="",E126="!!!",F126="NEW"),"",INDEX(J$1:J125,SUMPRODUCT(MAX(ROW(E$1:E125)*(E126=E$1:E125)))))</f>
+        <v> </v>
+      </c>
+      <c r="L126" s="26"/>
     </row>
     <row r="127" spans="1:12">
       <c r="A127" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="B127" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C127" s="27" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="E127" s="21">
         <f>IF(D127="?OLD","!!!","")</f>
@@ -6447,16 +6467,7 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="B128" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C128" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D128" s="27" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E128" s="21">
         <f>IF(D128="?OLD","!!!","")</f>
@@ -6489,76 +6500,22 @@
       <c r="L128" s="26"/>
     </row>
     <row r="129" spans="1:12">
-      <c r="A129" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="E129" s="21">
-        <f>IF(D129="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F129" s="22" t="str">
-        <f>IF(OR(E129="",E129="!!!"),"",IF(NOT(ISNA(VLOOKUP(E129,E$1:E128,1,FALSE()))),"OLD",IF(AND(E129&lt;&gt;"",E129&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G129" s="23" t="str">
-        <f>IF(OR(E129="",E129="!!!"),"",IF(OR(J129=0,AND(J129=1,K129=1),AND(J129=1,I129="SBJ"),AND(J129=1,I129=0)),"?IN_FOCUS",IF(J129&lt;=2,"?ACTIVATED",IF(J129&lt;&gt;"","?FAMILIAR",IF(F129="NEW",IF(ISNA(VLOOKUP(E129,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H129" s="24" t="str">
-        <f>IF(J129&lt;&gt;1,"",IF(I129="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I129" s="25" t="str">
-        <f>IF(OR(E129="",E129="!!!",F129="NEW"),"",INDEX(B128:B$2,-1+SUMPRODUCT(MAX(ROW(E128:E$2)*(E129=E128:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J129" s="25" t="str">
-        <f>IF(OR(E129="",E129="!!!",F129="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E129)*(E129=E$2:E129)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E128)*(E2=E$1:E128))))))</f>
-        <v> </v>
-      </c>
-      <c r="K129" s="25" t="str">
-        <f>IF(OR(E129="",E129="!!!",F129="NEW"),"",INDEX(J$1:J128,SUMPRODUCT(MAX(ROW(E$1:E128)*(E129=E$1:E128)))))</f>
-        <v> </v>
-      </c>
-      <c r="L129" s="26"/>
+      <c r="A129" s="20"/>
     </row>
     <row r="130" spans="1:12">
       <c r="A130" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="E130" s="21">
-        <f>IF(D130="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F130" s="22" t="str">
-        <f>IF(OR(E130="",E130="!!!"),"",IF(NOT(ISNA(VLOOKUP(E130,E$1:E129,1,FALSE()))),"OLD",IF(AND(E130&lt;&gt;"",E130&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G130" s="23" t="str">
-        <f>IF(OR(E130="",E130="!!!"),"",IF(OR(J130=0,AND(J130=1,K130=1),AND(J130=1,I130="SBJ"),AND(J130=1,I130=0)),"?IN_FOCUS",IF(J130&lt;=2,"?ACTIVATED",IF(J130&lt;&gt;"","?FAMILIAR",IF(F130="NEW",IF(ISNA(VLOOKUP(E130,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H130" s="24" t="str">
-        <f>IF(J130&lt;&gt;1,"",IF(I130="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I130" s="25" t="str">
-        <f>IF(OR(E130="",E130="!!!",F130="NEW"),"",INDEX(B129:B$2,-1+SUMPRODUCT(MAX(ROW(E129:E$2)*(E130=E129:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J130" s="25" t="str">
-        <f>IF(OR(E130="",E130="!!!",F130="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E130)*(E130=E$2:E130)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E129)*(E2=E$1:E129))))))</f>
-        <v> </v>
-      </c>
-      <c r="K130" s="25" t="str">
-        <f>IF(OR(E130="",E130="!!!",F130="NEW"),"",INDEX(J$1:J129,SUMPRODUCT(MAX(ROW(E$1:E129)*(E130=E$1:E129)))))</f>
-        <v> </v>
-      </c>
-      <c r="L130" s="26"/>
+        <v>208</v>
+      </c>
     </row>
     <row r="131" spans="1:12">
       <c r="A131" s="20" t="s">
-        <v>160</v>
+        <v>209</v>
+      </c>
+      <c r="B131" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C131" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="E131" s="21">
         <f>IF(D131="?OLD","!!!","")</f>
@@ -6592,16 +6549,16 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" s="20" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C132" s="27" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D132" s="27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E132" s="21">
         <f>IF(D132="?OLD","!!!","")</f>
@@ -6635,7 +6592,7 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" s="20" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E133" s="21">
         <f>IF(D133="?OLD","!!!","")</f>
@@ -6669,7 +6626,7 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" s="20" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E134" s="21">
         <f>IF(D134="?OLD","!!!","")</f>
@@ -6703,13 +6660,7 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="B135" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="C135" s="27" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="E135" s="21">
         <f>IF(D135="?OLD","!!!","")</f>
@@ -6743,7 +6694,16 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" s="20" t="s">
-        <v>211</v>
+        <v>213</v>
+      </c>
+      <c r="B136" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C136" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D136" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E136" s="21">
         <f>IF(D136="?OLD","!!!","")</f>
@@ -6777,7 +6737,7 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" s="20" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="E137" s="21">
         <f>IF(D137="?OLD","!!!","")</f>
@@ -6811,7 +6771,7 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="20" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E138" s="21">
         <f>IF(D138="?OLD","!!!","")</f>
@@ -6845,13 +6805,13 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139" s="20" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B139" s="27" t="s">
-        <v>103</v>
+        <v>217</v>
       </c>
       <c r="C139" s="27" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="E139" s="21">
         <f>IF(D139="?OLD","!!!","")</f>
@@ -6885,7 +6845,7 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="20" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="E140" s="21">
         <f>IF(D140="?OLD","!!!","")</f>
@@ -6919,16 +6879,7 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="B141" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C141" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D141" s="27" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="E141" s="21">
         <f>IF(D141="?OLD","!!!","")</f>
@@ -6962,7 +6913,7 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" s="20" t="s">
-        <v>146</v>
+        <v>220</v>
       </c>
       <c r="E142" s="21">
         <f>IF(D142="?OLD","!!!","")</f>
@@ -6996,10 +6947,13 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" s="20" t="s">
-        <v>148</v>
+        <v>221</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>114</v>
+        <v>111</v>
+      </c>
+      <c r="C143" s="27" t="s">
+        <v>176</v>
       </c>
       <c r="E143" s="21">
         <f>IF(D143="?OLD","!!!","")</f>
@@ -7033,7 +6987,7 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="20" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E144" s="21">
         <f>IF(D144="?OLD","!!!","")</f>
@@ -7067,7 +7021,16 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" s="20" t="s">
-        <v>140</v>
+        <v>222</v>
+      </c>
+      <c r="B145" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C145" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D145" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E145" s="21">
         <f>IF(D145="?OLD","!!!","")</f>
@@ -7101,16 +7064,7 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="B146" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C146" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D146" s="27" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="E146" s="21">
         <f>IF(D146="?OLD","!!!","")</f>
@@ -7144,7 +7098,10 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="20" t="s">
-        <v>216</v>
+        <v>153</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>169</v>
       </c>
       <c r="E147" s="21">
         <f>IF(D147="?OLD","!!!","")</f>
@@ -7178,7 +7135,7 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="20" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="E148" s="21">
         <f>IF(D148="?OLD","!!!","")</f>
@@ -7212,16 +7169,7 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B149" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C149" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D149" s="27" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="E149" s="21">
         <f>IF(D149="?OLD","!!!","")</f>
@@ -7255,7 +7203,16 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" s="20" t="s">
-        <v>217</v>
+        <v>223</v>
+      </c>
+      <c r="B150" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C150" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D150" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E150" s="21">
         <f>IF(D150="?OLD","!!!","")</f>
@@ -7289,7 +7246,7 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="20" t="s">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="E151" s="21">
         <f>IF(D151="?OLD","!!!","")</f>
@@ -7322,11 +7279,51 @@
       <c r="L151" s="26"/>
     </row>
     <row r="152" spans="1:12">
-      <c r="A152" s="20"/>
+      <c r="A152" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E152" s="21">
+        <f>IF(D152="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F152" s="22" t="str">
+        <f>IF(OR(E152="",E152="!!!"),"",IF(NOT(ISNA(VLOOKUP(E152,E$1:E151,1,FALSE()))),"OLD",IF(AND(E152&lt;&gt;"",E152&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G152" s="23" t="str">
+        <f>IF(OR(E152="",E152="!!!"),"",IF(OR(J152=0,AND(J152=1,K152=1),AND(J152=1,I152="SBJ"),AND(J152=1,I152=0)),"?IN_FOCUS",IF(J152&lt;=2,"?ACTIVATED",IF(J152&lt;&gt;"","?FAMILIAR",IF(F152="NEW",IF(ISNA(VLOOKUP(E152,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H152" s="24" t="str">
+        <f>IF(J152&lt;&gt;1,"",IF(I152="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I152" s="25" t="str">
+        <f>IF(OR(E152="",E152="!!!",F152="NEW"),"",INDEX(B151:B$2,-1+SUMPRODUCT(MAX(ROW(E151:E$2)*(E152=E151:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J152" s="25" t="str">
+        <f>IF(OR(E152="",E152="!!!",F152="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E152)*(E152=E$2:E152)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E151)*(E2=E$1:E151))))))</f>
+        <v> </v>
+      </c>
+      <c r="K152" s="25" t="str">
+        <f>IF(OR(E152="",E152="!!!",F152="NEW"),"",INDEX(J$1:J151,SUMPRODUCT(MAX(ROW(E$1:E151)*(E152=E$1:E151)))))</f>
+        <v> </v>
+      </c>
+      <c r="L152" s="26"/>
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="20" t="s">
-        <v>152</v>
+        <v>13</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C153" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D153" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E153" s="21">
         <f>IF(D153="?OLD","!!!","")</f>
@@ -7360,21 +7357,41 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" s="20" t="s">
-        <v>218</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="E154" s="21">
+        <f>IF(D154="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F154" s="22" t="str">
+        <f>IF(OR(E154="",E154="!!!"),"",IF(NOT(ISNA(VLOOKUP(E154,E$1:E153,1,FALSE()))),"OLD",IF(AND(E154&lt;&gt;"",E154&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G154" s="23" t="str">
+        <f>IF(OR(E154="",E154="!!!"),"",IF(OR(J154=0,AND(J154=1,K154=1),AND(J154=1,I154="SBJ"),AND(J154=1,I154=0)),"?IN_FOCUS",IF(J154&lt;=2,"?ACTIVATED",IF(J154&lt;&gt;"","?FAMILIAR",IF(F154="NEW",IF(ISNA(VLOOKUP(E154,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H154" s="24" t="str">
+        <f>IF(J154&lt;&gt;1,"",IF(I154="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I154" s="25" t="str">
+        <f>IF(OR(E154="",E154="!!!",F154="NEW"),"",INDEX(B153:B$2,-1+SUMPRODUCT(MAX(ROW(E153:E$2)*(E154=E153:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J154" s="25" t="str">
+        <f>IF(OR(E154="",E154="!!!",F154="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E154)*(E154=E$2:E154)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E153)*(E2=E$1:E153))))))</f>
+        <v> </v>
+      </c>
+      <c r="K154" s="25" t="str">
+        <f>IF(OR(E154="",E154="!!!",F154="NEW"),"",INDEX(J$1:J153,SUMPRODUCT(MAX(ROW(E$1:E153)*(E154=E$1:E153)))))</f>
+        <v> </v>
+      </c>
+      <c r="L154" s="26"/>
     </row>
     <row r="155" spans="1:12">
       <c r="A155" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="B155" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C155" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D155" s="27" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E155" s="21">
         <f>IF(D155="?OLD","!!!","")</f>
@@ -7407,42 +7424,11 @@
       <c r="L155" s="26"/>
     </row>
     <row r="156" spans="1:12">
-      <c r="A156" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="E156" s="21">
-        <f>IF(D156="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F156" s="22" t="str">
-        <f>IF(OR(E156="",E156="!!!"),"",IF(NOT(ISNA(VLOOKUP(E156,E$1:E155,1,FALSE()))),"OLD",IF(AND(E156&lt;&gt;"",E156&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G156" s="23" t="str">
-        <f>IF(OR(E156="",E156="!!!"),"",IF(OR(J156=0,AND(J156=1,K156=1),AND(J156=1,I156="SBJ"),AND(J156=1,I156=0)),"?IN_FOCUS",IF(J156&lt;=2,"?ACTIVATED",IF(J156&lt;&gt;"","?FAMILIAR",IF(F156="NEW",IF(ISNA(VLOOKUP(E156,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H156" s="24" t="str">
-        <f>IF(J156&lt;&gt;1,"",IF(I156="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I156" s="25" t="str">
-        <f>IF(OR(E156="",E156="!!!",F156="NEW"),"",INDEX(B155:B$2,-1+SUMPRODUCT(MAX(ROW(E155:E$2)*(E156=E155:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J156" s="25" t="str">
-        <f>IF(OR(E156="",E156="!!!",F156="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E156)*(E156=E$2:E156)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E155)*(E2=E$1:E155))))))</f>
-        <v> </v>
-      </c>
-      <c r="K156" s="25" t="str">
-        <f>IF(OR(E156="",E156="!!!",F156="NEW"),"",INDEX(J$1:J155,SUMPRODUCT(MAX(ROW(E$1:E155)*(E156=E$1:E155)))))</f>
-        <v> </v>
-      </c>
-      <c r="L156" s="26"/>
+      <c r="A156" s="20"/>
     </row>
     <row r="157" spans="1:12">
       <c r="A157" s="20" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="E157" s="21">
         <f>IF(D157="?OLD","!!!","")</f>
@@ -7476,50 +7462,21 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="E158" s="21">
-        <f>IF(D158="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F158" s="22" t="str">
-        <f>IF(OR(E158="",E158="!!!"),"",IF(NOT(ISNA(VLOOKUP(E158,E$1:E157,1,FALSE()))),"OLD",IF(AND(E158&lt;&gt;"",E158&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G158" s="23" t="str">
-        <f>IF(OR(E158="",E158="!!!"),"",IF(OR(J158=0,AND(J158=1,K158=1),AND(J158=1,I158="SBJ"),AND(J158=1,I158=0)),"?IN_FOCUS",IF(J158&lt;=2,"?ACTIVATED",IF(J158&lt;&gt;"","?FAMILIAR",IF(F158="NEW",IF(ISNA(VLOOKUP(E158,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H158" s="24" t="str">
-        <f>IF(J158&lt;&gt;1,"",IF(I158="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I158" s="25" t="str">
-        <f>IF(OR(E158="",E158="!!!",F158="NEW"),"",INDEX(B157:B$2,-1+SUMPRODUCT(MAX(ROW(E157:E$2)*(E158=E157:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J158" s="25" t="str">
-        <f>IF(OR(E158="",E158="!!!",F158="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E158)*(E158=E$2:E158)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E157)*(E2=E$1:E157))))))</f>
-        <v> </v>
-      </c>
-      <c r="K158" s="25" t="str">
-        <f>IF(OR(E158="",E158="!!!",F158="NEW"),"",INDEX(J$1:J157,SUMPRODUCT(MAX(ROW(E$1:E157)*(E158=E$1:E157)))))</f>
-        <v> </v>
-      </c>
-      <c r="L158" s="26"/>
+        <v>226</v>
+      </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" s="20" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="B159" s="27" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C159" s="27" t="s">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="D159" s="27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E159" s="21">
         <f>IF(D159="?OLD","!!!","")</f>
@@ -7553,7 +7510,7 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" s="20" t="s">
-        <v>151</v>
+        <v>227</v>
       </c>
       <c r="E160" s="21">
         <f>IF(D160="?OLD","!!!","")</f>
@@ -7587,7 +7544,7 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="20" t="s">
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="E161" s="21">
         <f>IF(D161="?OLD","!!!","")</f>
@@ -7621,7 +7578,7 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" s="20" t="s">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="E162" s="21">
         <f>IF(D162="?OLD","!!!","")</f>
@@ -7655,7 +7612,16 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="20" t="s">
-        <v>181</v>
+        <v>120</v>
+      </c>
+      <c r="B163" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C163" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D163" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E163" s="21">
         <f>IF(D163="?OLD","!!!","")</f>
@@ -7689,7 +7655,7 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" s="20" t="s">
-        <v>223</v>
+        <v>157</v>
       </c>
       <c r="E164" s="21">
         <f>IF(D164="?OLD","!!!","")</f>
@@ -7723,13 +7689,7 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="B165" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C165" s="27" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="E165" s="21">
         <f>IF(D165="?OLD","!!!","")</f>
@@ -7763,7 +7723,7 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166" s="20" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E166" s="21">
         <f>IF(D166="?OLD","!!!","")</f>
@@ -7797,7 +7757,7 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" s="20" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="E167" s="21">
         <f>IF(D167="?OLD","!!!","")</f>
@@ -7831,16 +7791,7 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B168" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C168" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D168" s="27" t="s">
-        <v>105</v>
+        <v>231</v>
       </c>
       <c r="E168" s="21">
         <f>IF(D168="?OLD","!!!","")</f>
@@ -7874,7 +7825,13 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169" s="20" t="s">
-        <v>138</v>
+        <v>232</v>
+      </c>
+      <c r="B169" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C169" s="27" t="s">
+        <v>218</v>
       </c>
       <c r="E169" s="21">
         <f>IF(D169="?OLD","!!!","")</f>
@@ -7908,16 +7865,7 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B170" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C170" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D170" s="27" t="s">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="E170" s="21">
         <f>IF(D170="?OLD","!!!","")</f>
@@ -7951,16 +7899,7 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B171" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C171" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D171" s="27" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="E171" s="21">
         <f>IF(D171="?OLD","!!!","")</f>
@@ -7994,7 +7933,16 @@
     </row>
     <row r="172" spans="1:12">
       <c r="A172" s="20" t="s">
-        <v>120</v>
+        <v>234</v>
+      </c>
+      <c r="B172" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C172" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D172" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E172" s="21">
         <f>IF(D172="?OLD","!!!","")</f>
@@ -8027,25 +7975,94 @@
       <c r="L172" s="26"/>
     </row>
     <row r="173" spans="1:12">
-      <c r="A173" s="20"/>
+      <c r="A173" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E173" s="21">
+        <f>IF(D173="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F173" s="22" t="str">
+        <f>IF(OR(E173="",E173="!!!"),"",IF(NOT(ISNA(VLOOKUP(E173,E$1:E172,1,FALSE()))),"OLD",IF(AND(E173&lt;&gt;"",E173&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G173" s="23" t="str">
+        <f>IF(OR(E173="",E173="!!!"),"",IF(OR(J173=0,AND(J173=1,K173=1),AND(J173=1,I173="SBJ"),AND(J173=1,I173=0)),"?IN_FOCUS",IF(J173&lt;=2,"?ACTIVATED",IF(J173&lt;&gt;"","?FAMILIAR",IF(F173="NEW",IF(ISNA(VLOOKUP(E173,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H173" s="24" t="str">
+        <f>IF(J173&lt;&gt;1,"",IF(I173="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I173" s="25" t="str">
+        <f>IF(OR(E173="",E173="!!!",F173="NEW"),"",INDEX(B172:B$2,-1+SUMPRODUCT(MAX(ROW(E172:E$2)*(E173=E172:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J173" s="25" t="str">
+        <f>IF(OR(E173="",E173="!!!",F173="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E173)*(E173=E$2:E173)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E172)*(E2=E$1:E172))))))</f>
+        <v> </v>
+      </c>
+      <c r="K173" s="25" t="str">
+        <f>IF(OR(E173="",E173="!!!",F173="NEW"),"",INDEX(J$1:J172,SUMPRODUCT(MAX(ROW(E$1:E172)*(E173=E$1:E172)))))</f>
+        <v> </v>
+      </c>
+      <c r="L173" s="26"/>
     </row>
     <row r="174" spans="1:12">
       <c r="A174" s="20" t="s">
-        <v>227</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B174" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C174" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D174" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E174" s="21">
+        <f>IF(D174="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F174" s="22" t="str">
+        <f>IF(OR(E174="",E174="!!!"),"",IF(NOT(ISNA(VLOOKUP(E174,E$1:E173,1,FALSE()))),"OLD",IF(AND(E174&lt;&gt;"",E174&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G174" s="23" t="str">
+        <f>IF(OR(E174="",E174="!!!"),"",IF(OR(J174=0,AND(J174=1,K174=1),AND(J174=1,I174="SBJ"),AND(J174=1,I174=0)),"?IN_FOCUS",IF(J174&lt;=2,"?ACTIVATED",IF(J174&lt;&gt;"","?FAMILIAR",IF(F174="NEW",IF(ISNA(VLOOKUP(E174,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H174" s="24" t="str">
+        <f>IF(J174&lt;&gt;1,"",IF(I174="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I174" s="25" t="str">
+        <f>IF(OR(E174="",E174="!!!",F174="NEW"),"",INDEX(B173:B$2,-1+SUMPRODUCT(MAX(ROW(E173:E$2)*(E174=E173:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J174" s="25" t="str">
+        <f>IF(OR(E174="",E174="!!!",F174="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E174)*(E174=E$2:E174)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E173)*(E2=E$1:E173))))))</f>
+        <v> </v>
+      </c>
+      <c r="K174" s="25" t="str">
+        <f>IF(OR(E174="",E174="!!!",F174="NEW"),"",INDEX(J$1:J173,SUMPRODUCT(MAX(ROW(E$1:E173)*(E174=E$1:E173)))))</f>
+        <v> </v>
+      </c>
+      <c r="L174" s="26"/>
     </row>
     <row r="175" spans="1:12">
       <c r="A175" s="20" t="s">
-        <v>228</v>
+        <v>144</v>
       </c>
       <c r="B175" s="27" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C175" s="27" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="D175" s="27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E175" s="21">
         <f>IF(D175="?OLD","!!!","")</f>
@@ -8079,7 +8096,7 @@
     </row>
     <row r="176" spans="1:12">
       <c r="A176" s="20" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="E176" s="21">
         <f>IF(D176="?OLD","!!!","")</f>
@@ -8112,88 +8129,25 @@
       <c r="L176" s="26"/>
     </row>
     <row r="177" spans="1:12">
-      <c r="A177" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="B177" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C177" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="E177" s="21">
-        <f>IF(D177="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F177" s="22" t="str">
-        <f>IF(OR(E177="",E177="!!!"),"",IF(NOT(ISNA(VLOOKUP(E177,E$1:E176,1,FALSE()))),"OLD",IF(AND(E177&lt;&gt;"",E177&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G177" s="23" t="str">
-        <f>IF(OR(E177="",E177="!!!"),"",IF(OR(J177=0,AND(J177=1,K177=1),AND(J177=1,I177="SBJ"),AND(J177=1,I177=0)),"?IN_FOCUS",IF(J177&lt;=2,"?ACTIVATED",IF(J177&lt;&gt;"","?FAMILIAR",IF(F177="NEW",IF(ISNA(VLOOKUP(E177,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H177" s="24" t="str">
-        <f>IF(J177&lt;&gt;1,"",IF(I177="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I177" s="25" t="str">
-        <f>IF(OR(E177="",E177="!!!",F177="NEW"),"",INDEX(B176:B$2,-1+SUMPRODUCT(MAX(ROW(E176:E$2)*(E177=E176:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J177" s="25" t="str">
-        <f>IF(OR(E177="",E177="!!!",F177="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E177)*(E177=E$2:E177)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E176)*(E2=E$1:E176))))))</f>
-        <v> </v>
-      </c>
-      <c r="K177" s="25" t="str">
-        <f>IF(OR(E177="",E177="!!!",F177="NEW"),"",INDEX(J$1:J176,SUMPRODUCT(MAX(ROW(E$1:E176)*(E177=E$1:E176)))))</f>
-        <v> </v>
-      </c>
-      <c r="L177" s="26"/>
+      <c r="A177" s="20"/>
     </row>
     <row r="178" spans="1:12">
       <c r="A178" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B178" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C178" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E178" s="21">
-        <f>IF(D178="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F178" s="22" t="str">
-        <f>IF(OR(E178="",E178="!!!"),"",IF(NOT(ISNA(VLOOKUP(E178,E$1:E177,1,FALSE()))),"OLD",IF(AND(E178&lt;&gt;"",E178&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G178" s="23" t="str">
-        <f>IF(OR(E178="",E178="!!!"),"",IF(OR(J178=0,AND(J178=1,K178=1),AND(J178=1,I178="SBJ"),AND(J178=1,I178=0)),"?IN_FOCUS",IF(J178&lt;=2,"?ACTIVATED",IF(J178&lt;&gt;"","?FAMILIAR",IF(F178="NEW",IF(ISNA(VLOOKUP(E178,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H178" s="24" t="str">
-        <f>IF(J178&lt;&gt;1,"",IF(I178="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I178" s="25" t="str">
-        <f>IF(OR(E178="",E178="!!!",F178="NEW"),"",INDEX(B177:B$2,-1+SUMPRODUCT(MAX(ROW(E177:E$2)*(E178=E177:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J178" s="25" t="str">
-        <f>IF(OR(E178="",E178="!!!",F178="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E178)*(E178=E$2:E178)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E177)*(E2=E$1:E177))))))</f>
-        <v> </v>
-      </c>
-      <c r="K178" s="25" t="str">
-        <f>IF(OR(E178="",E178="!!!",F178="NEW"),"",INDEX(J$1:J177,SUMPRODUCT(MAX(ROW(E$1:E177)*(E178=E$1:E177)))))</f>
-        <v> </v>
-      </c>
-      <c r="L178" s="26"/>
+        <v>235</v>
+      </c>
     </row>
     <row r="179" spans="1:12">
       <c r="A179" s="20" t="s">
-        <v>213</v>
+        <v>236</v>
+      </c>
+      <c r="B179" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C179" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D179" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E179" s="21">
         <f>IF(D179="?OLD","!!!","")</f>
@@ -8227,13 +8181,7 @@
     </row>
     <row r="180" spans="1:12">
       <c r="A180" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B180" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C180" s="27" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="E180" s="21">
         <f>IF(D180="?OLD","!!!","")</f>
@@ -8267,7 +8215,13 @@
     </row>
     <row r="181" spans="1:12">
       <c r="A181" s="20" t="s">
-        <v>156</v>
+        <v>238</v>
+      </c>
+      <c r="B181" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C181" s="27" t="s">
+        <v>176</v>
       </c>
       <c r="E181" s="21">
         <f>IF(D181="?OLD","!!!","")</f>
@@ -8301,7 +8255,13 @@
     </row>
     <row r="182" spans="1:12">
       <c r="A182" s="20" t="s">
-        <v>233</v>
+        <v>239</v>
+      </c>
+      <c r="B182" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C182" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E182" s="21">
         <f>IF(D182="?OLD","!!!","")</f>
@@ -8335,7 +8295,7 @@
     </row>
     <row r="183" spans="1:12">
       <c r="A183" s="20" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="E183" s="21">
         <f>IF(D183="?OLD","!!!","")</f>
@@ -8369,7 +8329,13 @@
     </row>
     <row r="184" spans="1:12">
       <c r="A184" s="20" t="s">
-        <v>235</v>
+        <v>240</v>
+      </c>
+      <c r="B184" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C184" s="27" t="s">
+        <v>218</v>
       </c>
       <c r="E184" s="21">
         <f>IF(D184="?OLD","!!!","")</f>
@@ -8403,13 +8369,7 @@
     </row>
     <row r="185" spans="1:12">
       <c r="A185" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="B185" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C185" s="27" t="s">
-        <v>210</v>
+        <v>162</v>
       </c>
       <c r="E185" s="21">
         <f>IF(D185="?OLD","!!!","")</f>
@@ -8443,7 +8403,7 @@
     </row>
     <row r="186" spans="1:12">
       <c r="A186" s="20" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="E186" s="21">
         <f>IF(D186="?OLD","!!!","")</f>
@@ -8477,16 +8437,7 @@
     </row>
     <row r="187" spans="1:12">
       <c r="A187" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="B187" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C187" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="D187" s="27" t="s">
-        <v>105</v>
+        <v>242</v>
       </c>
       <c r="E187" s="21">
         <f>IF(D187="?OLD","!!!","")</f>
@@ -8520,16 +8471,7 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="B188" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C188" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="D188" s="27" t="s">
-        <v>105</v>
+        <v>243</v>
       </c>
       <c r="E188" s="21">
         <f>IF(D188="?OLD","!!!","")</f>
@@ -8563,7 +8505,13 @@
     </row>
     <row r="189" spans="1:12">
       <c r="A189" s="20" t="s">
-        <v>107</v>
+        <v>244</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C189" s="27" t="s">
+        <v>218</v>
       </c>
       <c r="E189" s="21">
         <f>IF(D189="?OLD","!!!","")</f>
@@ -8597,7 +8545,7 @@
     </row>
     <row r="190" spans="1:12">
       <c r="A190" s="20" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="E190" s="21">
         <f>IF(D190="?OLD","!!!","")</f>
@@ -8631,7 +8579,16 @@
     </row>
     <row r="191" spans="1:12">
       <c r="A191" s="20" t="s">
-        <v>183</v>
+        <v>245</v>
+      </c>
+      <c r="B191" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C191" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D191" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E191" s="21">
         <f>IF(D191="?OLD","!!!","")</f>
@@ -8665,13 +8622,16 @@
     </row>
     <row r="192" spans="1:12">
       <c r="A192" s="20" t="s">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="B192" s="27" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="C192" s="27" t="s">
-        <v>159</v>
+        <v>246</v>
+      </c>
+      <c r="D192" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E192" s="21">
         <f>IF(D192="?OLD","!!!","")</f>
@@ -8705,13 +8665,7 @@
     </row>
     <row r="193" spans="1:12">
       <c r="A193" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="B193" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C193" s="27" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E193" s="21">
         <f>IF(D193="?OLD","!!!","")</f>
@@ -8745,7 +8699,7 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" s="20" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="E194" s="21">
         <f>IF(D194="?OLD","!!!","")</f>
@@ -8781,12 +8735,6 @@
       <c r="A195" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="B195" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C195" s="27" t="s">
-        <v>110</v>
-      </c>
       <c r="E195" s="21">
         <f>IF(D195="?OLD","!!!","")</f>
         <v/>
@@ -8819,7 +8767,13 @@
     </row>
     <row r="196" spans="1:12">
       <c r="A196" s="20" t="s">
-        <v>146</v>
+        <v>192</v>
+      </c>
+      <c r="B196" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C196" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E196" s="21">
         <f>IF(D196="?OLD","!!!","")</f>
@@ -8853,10 +8807,13 @@
     </row>
     <row r="197" spans="1:12">
       <c r="A197" s="20" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="B197" s="27" t="s">
-        <v>239</v>
+        <v>156</v>
+      </c>
+      <c r="C197" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="E197" s="21">
         <f>IF(D197="?OLD","!!!","")</f>
@@ -8890,7 +8847,7 @@
     </row>
     <row r="198" spans="1:12">
       <c r="A198" s="20" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="E198" s="21">
         <f>IF(D198="?OLD","!!!","")</f>
@@ -8924,7 +8881,13 @@
     </row>
     <row r="199" spans="1:12">
       <c r="A199" s="20" t="s">
-        <v>241</v>
+        <v>199</v>
+      </c>
+      <c r="B199" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C199" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="E199" s="21">
         <f>IF(D199="?OLD","!!!","")</f>
@@ -8958,16 +8921,7 @@
     </row>
     <row r="200" spans="1:12">
       <c r="A200" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="B200" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C200" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="D200" s="27" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="E200" s="21">
         <f>IF(D200="?OLD","!!!","")</f>
@@ -9001,16 +8955,10 @@
     </row>
     <row r="201" spans="1:12">
       <c r="A201" s="20" t="s">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="B201" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="C201" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="D201" s="27" t="s">
-        <v>105</v>
+        <v>247</v>
       </c>
       <c r="E201" s="21">
         <f>IF(D201="?OLD","!!!","")</f>
@@ -9044,7 +8992,7 @@
     </row>
     <row r="202" spans="1:12">
       <c r="A202" s="20" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E202" s="21">
         <f>IF(D202="?OLD","!!!","")</f>
@@ -9078,16 +9026,7 @@
     </row>
     <row r="203" spans="1:12">
       <c r="A203" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B203" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C203" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D203" s="27" t="s">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="E203" s="21">
         <f>IF(D203="?OLD","!!!","")</f>
@@ -9121,7 +9060,16 @@
     </row>
     <row r="204" spans="1:12">
       <c r="A204" s="20" t="s">
-        <v>244</v>
+        <v>250</v>
+      </c>
+      <c r="B204" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C204" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D204" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E204" s="21">
         <f>IF(D204="?OLD","!!!","")</f>
@@ -9155,7 +9103,16 @@
     </row>
     <row r="205" spans="1:12">
       <c r="A205" s="20" t="s">
-        <v>245</v>
+        <v>251</v>
+      </c>
+      <c r="B205" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C205" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="D205" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E205" s="21">
         <f>IF(D205="?OLD","!!!","")</f>
@@ -9189,7 +9146,7 @@
     </row>
     <row r="206" spans="1:12">
       <c r="A206" s="20" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="E206" s="21">
         <f>IF(D206="?OLD","!!!","")</f>
@@ -9222,16 +9179,85 @@
       <c r="L206" s="26"/>
     </row>
     <row r="207" spans="1:12">
-      <c r="A207" s="20"/>
+      <c r="A207" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C207" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D207" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E207" s="21">
+        <f>IF(D207="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F207" s="22" t="str">
+        <f>IF(OR(E207="",E207="!!!"),"",IF(NOT(ISNA(VLOOKUP(E207,E$1:E206,1,FALSE()))),"OLD",IF(AND(E207&lt;&gt;"",E207&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G207" s="23" t="str">
+        <f>IF(OR(E207="",E207="!!!"),"",IF(OR(J207=0,AND(J207=1,K207=1),AND(J207=1,I207="SBJ"),AND(J207=1,I207=0)),"?IN_FOCUS",IF(J207&lt;=2,"?ACTIVATED",IF(J207&lt;&gt;"","?FAMILIAR",IF(F207="NEW",IF(ISNA(VLOOKUP(E207,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H207" s="24" t="str">
+        <f>IF(J207&lt;&gt;1,"",IF(I207="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I207" s="25" t="str">
+        <f>IF(OR(E207="",E207="!!!",F207="NEW"),"",INDEX(B206:B$2,-1+SUMPRODUCT(MAX(ROW(E206:E$2)*(E207=E206:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J207" s="25" t="str">
+        <f>IF(OR(E207="",E207="!!!",F207="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E207)*(E207=E$2:E207)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E206)*(E2=E$1:E206))))))</f>
+        <v> </v>
+      </c>
+      <c r="K207" s="25" t="str">
+        <f>IF(OR(E207="",E207="!!!",F207="NEW"),"",INDEX(J$1:J206,SUMPRODUCT(MAX(ROW(E$1:E206)*(E207=E$1:E206)))))</f>
+        <v> </v>
+      </c>
+      <c r="L207" s="26"/>
     </row>
     <row r="208" spans="1:12">
       <c r="A208" s="20" t="s">
-        <v>246</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="E208" s="21">
+        <f>IF(D208="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F208" s="22" t="str">
+        <f>IF(OR(E208="",E208="!!!"),"",IF(NOT(ISNA(VLOOKUP(E208,E$1:E207,1,FALSE()))),"OLD",IF(AND(E208&lt;&gt;"",E208&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G208" s="23" t="str">
+        <f>IF(OR(E208="",E208="!!!"),"",IF(OR(J208=0,AND(J208=1,K208=1),AND(J208=1,I208="SBJ"),AND(J208=1,I208=0)),"?IN_FOCUS",IF(J208&lt;=2,"?ACTIVATED",IF(J208&lt;&gt;"","?FAMILIAR",IF(F208="NEW",IF(ISNA(VLOOKUP(E208,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H208" s="24" t="str">
+        <f>IF(J208&lt;&gt;1,"",IF(I208="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I208" s="25" t="str">
+        <f>IF(OR(E208="",E208="!!!",F208="NEW"),"",INDEX(B207:B$2,-1+SUMPRODUCT(MAX(ROW(E207:E$2)*(E208=E207:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J208" s="25" t="str">
+        <f>IF(OR(E208="",E208="!!!",F208="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E208)*(E208=E$2:E208)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E207)*(E2=E$1:E207))))))</f>
+        <v> </v>
+      </c>
+      <c r="K208" s="25" t="str">
+        <f>IF(OR(E208="",E208="!!!",F208="NEW"),"",INDEX(J$1:J207,SUMPRODUCT(MAX(ROW(E$1:E207)*(E208=E$1:E207)))))</f>
+        <v> </v>
+      </c>
+      <c r="L208" s="26"/>
     </row>
     <row r="209" spans="1:12">
       <c r="A209" s="20" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E209" s="21">
         <f>IF(D209="?OLD","!!!","")</f>
@@ -9265,7 +9291,7 @@
     </row>
     <row r="210" spans="1:12">
       <c r="A210" s="20" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="E210" s="21">
         <f>IF(D210="?OLD","!!!","")</f>
@@ -9298,85 +9324,16 @@
       <c r="L210" s="26"/>
     </row>
     <row r="211" spans="1:12">
-      <c r="A211" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="E211" s="21">
-        <f>IF(D211="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F211" s="22" t="str">
-        <f>IF(OR(E211="",E211="!!!"),"",IF(NOT(ISNA(VLOOKUP(E211,E$1:E210,1,FALSE()))),"OLD",IF(AND(E211&lt;&gt;"",E211&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G211" s="23" t="str">
-        <f>IF(OR(E211="",E211="!!!"),"",IF(OR(J211=0,AND(J211=1,K211=1),AND(J211=1,I211="SBJ"),AND(J211=1,I211=0)),"?IN_FOCUS",IF(J211&lt;=2,"?ACTIVATED",IF(J211&lt;&gt;"","?FAMILIAR",IF(F211="NEW",IF(ISNA(VLOOKUP(E211,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H211" s="24" t="str">
-        <f>IF(J211&lt;&gt;1,"",IF(I211="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I211" s="25" t="str">
-        <f>IF(OR(E211="",E211="!!!",F211="NEW"),"",INDEX(B210:B$2,-1+SUMPRODUCT(MAX(ROW(E210:E$2)*(E211=E210:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J211" s="25" t="str">
-        <f>IF(OR(E211="",E211="!!!",F211="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E211)*(E211=E$2:E211)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E210)*(E2=E$1:E210))))))</f>
-        <v> </v>
-      </c>
-      <c r="K211" s="25" t="str">
-        <f>IF(OR(E211="",E211="!!!",F211="NEW"),"",INDEX(J$1:J210,SUMPRODUCT(MAX(ROW(E$1:E210)*(E211=E$1:E210)))))</f>
-        <v> </v>
-      </c>
-      <c r="L211" s="26"/>
+      <c r="A211" s="20"/>
     </row>
     <row r="212" spans="1:12">
       <c r="A212" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="B212" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C212" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D212" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E212" s="21">
-        <f>IF(D212="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F212" s="22" t="str">
-        <f>IF(OR(E212="",E212="!!!"),"",IF(NOT(ISNA(VLOOKUP(E212,E$1:E211,1,FALSE()))),"OLD",IF(AND(E212&lt;&gt;"",E212&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G212" s="23" t="str">
-        <f>IF(OR(E212="",E212="!!!"),"",IF(OR(J212=0,AND(J212=1,K212=1),AND(J212=1,I212="SBJ"),AND(J212=1,I212=0)),"?IN_FOCUS",IF(J212&lt;=2,"?ACTIVATED",IF(J212&lt;&gt;"","?FAMILIAR",IF(F212="NEW",IF(ISNA(VLOOKUP(E212,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H212" s="24" t="str">
-        <f>IF(J212&lt;&gt;1,"",IF(I212="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I212" s="25" t="str">
-        <f>IF(OR(E212="",E212="!!!",F212="NEW"),"",INDEX(B211:B$2,-1+SUMPRODUCT(MAX(ROW(E211:E$2)*(E212=E211:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J212" s="25" t="str">
-        <f>IF(OR(E212="",E212="!!!",F212="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E212)*(E212=E$2:E212)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E211)*(E2=E$1:E211))))))</f>
-        <v> </v>
-      </c>
-      <c r="K212" s="25" t="str">
-        <f>IF(OR(E212="",E212="!!!",F212="NEW"),"",INDEX(J$1:J211,SUMPRODUCT(MAX(ROW(E$1:E211)*(E212=E$1:E211)))))</f>
-        <v> </v>
-      </c>
-      <c r="L212" s="26"/>
+        <v>254</v>
+      </c>
     </row>
     <row r="213" spans="1:12">
       <c r="A213" s="20" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="E213" s="21">
         <f>IF(D213="?OLD","!!!","")</f>
@@ -9410,13 +9367,7 @@
     </row>
     <row r="214" spans="1:12">
       <c r="A214" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="B214" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C214" s="27" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="E214" s="21">
         <f>IF(D214="?OLD","!!!","")</f>
@@ -9450,7 +9401,7 @@
     </row>
     <row r="215" spans="1:12">
       <c r="A215" s="20" t="s">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="E215" s="21">
         <f>IF(D215="?OLD","!!!","")</f>
@@ -9484,16 +9435,16 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" s="20" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="B216" s="27" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C216" s="27" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D216" s="27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E216" s="21">
         <f>IF(D216="?OLD","!!!","")</f>
@@ -9527,7 +9478,7 @@
     </row>
     <row r="217" spans="1:12">
       <c r="A217" s="20" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="E217" s="21">
         <f>IF(D217="?OLD","!!!","")</f>
@@ -9561,7 +9512,13 @@
     </row>
     <row r="218" spans="1:12">
       <c r="A218" s="20" t="s">
-        <v>151</v>
+        <v>258</v>
+      </c>
+      <c r="B218" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C218" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="E218" s="21">
         <f>IF(D218="?OLD","!!!","")</f>
@@ -9595,7 +9552,7 @@
     </row>
     <row r="219" spans="1:12">
       <c r="A219" s="20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E219" s="21">
         <f>IF(D219="?OLD","!!!","")</f>
@@ -9629,16 +9586,16 @@
     </row>
     <row r="220" spans="1:12">
       <c r="A220" s="20" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="B220" s="27" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="C220" s="27" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D220" s="27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E220" s="21">
         <f>IF(D220="?OLD","!!!","")</f>
@@ -9672,7 +9629,7 @@
     </row>
     <row r="221" spans="1:12">
       <c r="A221" s="20" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E221" s="21">
         <f>IF(D221="?OLD","!!!","")</f>
@@ -9706,16 +9663,7 @@
     </row>
     <row r="222" spans="1:12">
       <c r="A222" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="B222" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C222" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D222" s="27" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="E222" s="21">
         <f>IF(D222="?OLD","!!!","")</f>
@@ -9749,7 +9697,7 @@
     </row>
     <row r="223" spans="1:12">
       <c r="A223" s="20" t="s">
-        <v>252</v>
+        <v>153</v>
       </c>
       <c r="E223" s="21">
         <f>IF(D223="?OLD","!!!","")</f>
@@ -9783,7 +9731,16 @@
     </row>
     <row r="224" spans="1:12">
       <c r="A224" s="20" t="s">
-        <v>140</v>
+        <v>172</v>
+      </c>
+      <c r="B224" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C224" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D224" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E224" s="21">
         <f>IF(D224="?OLD","!!!","")</f>
@@ -9817,16 +9774,7 @@
     </row>
     <row r="225" spans="1:12">
       <c r="A225" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="B225" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C225" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D225" s="27" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="E225" s="21">
         <f>IF(D225="?OLD","!!!","")</f>
@@ -9860,7 +9808,16 @@
     </row>
     <row r="226" spans="1:12">
       <c r="A226" s="20" t="s">
-        <v>181</v>
+        <v>259</v>
+      </c>
+      <c r="B226" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C226" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D226" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E226" s="21">
         <f>IF(D226="?OLD","!!!","")</f>
@@ -9894,7 +9851,7 @@
     </row>
     <row r="227" spans="1:12">
       <c r="A227" s="20" t="s">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E227" s="21">
         <f>IF(D227="?OLD","!!!","")</f>
@@ -9928,16 +9885,7 @@
     </row>
     <row r="228" spans="1:12">
       <c r="A228" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="B228" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C228" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D228" s="27" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="E228" s="21">
         <f>IF(D228="?OLD","!!!","")</f>
@@ -9971,7 +9919,16 @@
     </row>
     <row r="229" spans="1:12">
       <c r="A229" s="20" t="s">
-        <v>254</v>
+        <v>146</v>
+      </c>
+      <c r="B229" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C229" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D229" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E229" s="21">
         <f>IF(D229="?OLD","!!!","")</f>
@@ -10005,7 +9962,7 @@
     </row>
     <row r="230" spans="1:12">
       <c r="A230" s="20" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
       <c r="E230" s="21">
         <f>IF(D230="?OLD","!!!","")</f>
@@ -10039,13 +9996,7 @@
     </row>
     <row r="231" spans="1:12">
       <c r="A231" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="B231" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C231" s="27" t="s">
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="E231" s="21">
         <f>IF(D231="?OLD","!!!","")</f>
@@ -10079,7 +10030,16 @@
     </row>
     <row r="232" spans="1:12">
       <c r="A232" s="20" t="s">
-        <v>146</v>
+        <v>261</v>
+      </c>
+      <c r="B232" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C232" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D232" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E232" s="21">
         <f>IF(D232="?OLD","!!!","")</f>
@@ -10113,7 +10073,7 @@
     </row>
     <row r="233" spans="1:12">
       <c r="A233" s="20" t="s">
-        <v>148</v>
+        <v>262</v>
       </c>
       <c r="E233" s="21">
         <f>IF(D233="?OLD","!!!","")</f>
@@ -10147,7 +10107,7 @@
     </row>
     <row r="234" spans="1:12">
       <c r="A234" s="20" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E234" s="21">
         <f>IF(D234="?OLD","!!!","")</f>
@@ -10181,7 +10141,13 @@
     </row>
     <row r="235" spans="1:12">
       <c r="A235" s="20" t="s">
-        <v>258</v>
+        <v>264</v>
+      </c>
+      <c r="B235" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C235" s="27" t="s">
+        <v>218</v>
       </c>
       <c r="E235" s="21">
         <f>IF(D235="?OLD","!!!","")</f>
@@ -10215,16 +10181,7 @@
     </row>
     <row r="236" spans="1:12">
       <c r="A236" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="B236" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="C236" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D236" s="27" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="E236" s="21">
         <f>IF(D236="?OLD","!!!","")</f>
@@ -10258,7 +10215,7 @@
     </row>
     <row r="237" spans="1:12">
       <c r="A237" s="20" t="s">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="E237" s="21">
         <f>IF(D237="?OLD","!!!","")</f>
@@ -10292,7 +10249,7 @@
     </row>
     <row r="238" spans="1:12">
       <c r="A238" s="20" t="s">
-        <v>148</v>
+        <v>265</v>
       </c>
       <c r="E238" s="21">
         <f>IF(D238="?OLD","!!!","")</f>
@@ -10326,16 +10283,7 @@
     </row>
     <row r="239" spans="1:12">
       <c r="A239" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="B239" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C239" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D239" s="27" t="s">
-        <v>105</v>
+        <v>266</v>
       </c>
       <c r="E239" s="21">
         <f>IF(D239="?OLD","!!!","")</f>
@@ -10369,7 +10317,16 @@
     </row>
     <row r="240" spans="1:12">
       <c r="A240" s="20" t="s">
-        <v>261</v>
+        <v>267</v>
+      </c>
+      <c r="B240" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C240" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D240" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E240" s="21">
         <f>IF(D240="?OLD","!!!","")</f>
@@ -10403,7 +10360,7 @@
     </row>
     <row r="241" spans="1:12">
       <c r="A241" s="20" t="s">
-        <v>120</v>
+        <v>249</v>
       </c>
       <c r="E241" s="21">
         <f>IF(D241="?OLD","!!!","")</f>
@@ -10436,16 +10393,85 @@
       <c r="L241" s="26"/>
     </row>
     <row r="242" spans="1:12">
-      <c r="A242" s="20"/>
+      <c r="A242" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E242" s="21">
+        <f>IF(D242="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F242" s="22" t="str">
+        <f>IF(OR(E242="",E242="!!!"),"",IF(NOT(ISNA(VLOOKUP(E242,E$1:E241,1,FALSE()))),"OLD",IF(AND(E242&lt;&gt;"",E242&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G242" s="23" t="str">
+        <f>IF(OR(E242="",E242="!!!"),"",IF(OR(J242=0,AND(J242=1,K242=1),AND(J242=1,I242="SBJ"),AND(J242=1,I242=0)),"?IN_FOCUS",IF(J242&lt;=2,"?ACTIVATED",IF(J242&lt;&gt;"","?FAMILIAR",IF(F242="NEW",IF(ISNA(VLOOKUP(E242,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H242" s="24" t="str">
+        <f>IF(J242&lt;&gt;1,"",IF(I242="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I242" s="25" t="str">
+        <f>IF(OR(E242="",E242="!!!",F242="NEW"),"",INDEX(B241:B$2,-1+SUMPRODUCT(MAX(ROW(E241:E$2)*(E242=E241:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J242" s="25" t="str">
+        <f>IF(OR(E242="",E242="!!!",F242="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E242)*(E242=E$2:E242)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E241)*(E2=E$1:E241))))))</f>
+        <v> </v>
+      </c>
+      <c r="K242" s="25" t="str">
+        <f>IF(OR(E242="",E242="!!!",F242="NEW"),"",INDEX(J$1:J241,SUMPRODUCT(MAX(ROW(E$1:E241)*(E242=E$1:E241)))))</f>
+        <v> </v>
+      </c>
+      <c r="L242" s="26"/>
     </row>
     <row r="243" spans="1:12">
       <c r="A243" s="20" t="s">
-        <v>262</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="B243" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C243" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D243" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E243" s="21">
+        <f>IF(D243="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F243" s="22" t="str">
+        <f>IF(OR(E243="",E243="!!!"),"",IF(NOT(ISNA(VLOOKUP(E243,E$1:E242,1,FALSE()))),"OLD",IF(AND(E243&lt;&gt;"",E243&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G243" s="23" t="str">
+        <f>IF(OR(E243="",E243="!!!"),"",IF(OR(J243=0,AND(J243=1,K243=1),AND(J243=1,I243="SBJ"),AND(J243=1,I243=0)),"?IN_FOCUS",IF(J243&lt;=2,"?ACTIVATED",IF(J243&lt;&gt;"","?FAMILIAR",IF(F243="NEW",IF(ISNA(VLOOKUP(E243,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H243" s="24" t="str">
+        <f>IF(J243&lt;&gt;1,"",IF(I243="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I243" s="25" t="str">
+        <f>IF(OR(E243="",E243="!!!",F243="NEW"),"",INDEX(B242:B$2,-1+SUMPRODUCT(MAX(ROW(E242:E$2)*(E243=E242:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J243" s="25" t="str">
+        <f>IF(OR(E243="",E243="!!!",F243="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E243)*(E243=E$2:E243)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E242)*(E2=E$1:E242))))))</f>
+        <v> </v>
+      </c>
+      <c r="K243" s="25" t="str">
+        <f>IF(OR(E243="",E243="!!!",F243="NEW"),"",INDEX(J$1:J242,SUMPRODUCT(MAX(ROW(E$1:E242)*(E243=E$1:E242)))))</f>
+        <v> </v>
+      </c>
+      <c r="L243" s="26"/>
     </row>
     <row r="244" spans="1:12">
       <c r="A244" s="20" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E244" s="21">
         <f>IF(D244="?OLD","!!!","")</f>
@@ -10479,7 +10505,7 @@
     </row>
     <row r="245" spans="1:12">
       <c r="A245" s="20" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="E245" s="21">
         <f>IF(D245="?OLD","!!!","")</f>
@@ -10512,82 +10538,16 @@
       <c r="L245" s="26"/>
     </row>
     <row r="246" spans="1:12">
-      <c r="A246" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="E246" s="21">
-        <f>IF(D246="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F246" s="22" t="str">
-        <f>IF(OR(E246="",E246="!!!"),"",IF(NOT(ISNA(VLOOKUP(E246,E$1:E245,1,FALSE()))),"OLD",IF(AND(E246&lt;&gt;"",E246&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G246" s="23" t="str">
-        <f>IF(OR(E246="",E246="!!!"),"",IF(OR(J246=0,AND(J246=1,K246=1),AND(J246=1,I246="SBJ"),AND(J246=1,I246=0)),"?IN_FOCUS",IF(J246&lt;=2,"?ACTIVATED",IF(J246&lt;&gt;"","?FAMILIAR",IF(F246="NEW",IF(ISNA(VLOOKUP(E246,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H246" s="24" t="str">
-        <f>IF(J246&lt;&gt;1,"",IF(I246="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I246" s="25" t="str">
-        <f>IF(OR(E246="",E246="!!!",F246="NEW"),"",INDEX(B245:B$2,-1+SUMPRODUCT(MAX(ROW(E245:E$2)*(E246=E245:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J246" s="25" t="str">
-        <f>IF(OR(E246="",E246="!!!",F246="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E246)*(E246=E$2:E246)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E245)*(E2=E$1:E245))))))</f>
-        <v> </v>
-      </c>
-      <c r="K246" s="25" t="str">
-        <f>IF(OR(E246="",E246="!!!",F246="NEW"),"",INDEX(J$1:J245,SUMPRODUCT(MAX(ROW(E$1:E245)*(E246=E$1:E245)))))</f>
-        <v> </v>
-      </c>
-      <c r="L246" s="26"/>
+      <c r="A246" s="20"/>
     </row>
     <row r="247" spans="1:12">
       <c r="A247" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="E247" s="21">
-        <f>IF(D247="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F247" s="22" t="str">
-        <f>IF(OR(E247="",E247="!!!"),"",IF(NOT(ISNA(VLOOKUP(E247,E$1:E246,1,FALSE()))),"OLD",IF(AND(E247&lt;&gt;"",E247&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G247" s="23" t="str">
-        <f>IF(OR(E247="",E247="!!!"),"",IF(OR(J247=0,AND(J247=1,K247=1),AND(J247=1,I247="SBJ"),AND(J247=1,I247=0)),"?IN_FOCUS",IF(J247&lt;=2,"?ACTIVATED",IF(J247&lt;&gt;"","?FAMILIAR",IF(F247="NEW",IF(ISNA(VLOOKUP(E247,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H247" s="24" t="str">
-        <f>IF(J247&lt;&gt;1,"",IF(I247="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I247" s="25" t="str">
-        <f>IF(OR(E247="",E247="!!!",F247="NEW"),"",INDEX(B246:B$2,-1+SUMPRODUCT(MAX(ROW(E246:E$2)*(E247=E246:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J247" s="25" t="str">
-        <f>IF(OR(E247="",E247="!!!",F247="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E247)*(E247=E$2:E247)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E246)*(E2=E$1:E246))))))</f>
-        <v> </v>
-      </c>
-      <c r="K247" s="25" t="str">
-        <f>IF(OR(E247="",E247="!!!",F247="NEW"),"",INDEX(J$1:J246,SUMPRODUCT(MAX(ROW(E$1:E246)*(E247=E$1:E246)))))</f>
-        <v> </v>
-      </c>
-      <c r="L247" s="26"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="248" spans="1:12">
       <c r="A248" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="B248" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C248" s="27" t="s">
-        <v>159</v>
+        <v>271</v>
       </c>
       <c r="E248" s="21">
         <f>IF(D248="?OLD","!!!","")</f>
@@ -10621,7 +10581,7 @@
     </row>
     <row r="249" spans="1:12">
       <c r="A249" s="20" t="s">
-        <v>160</v>
+        <v>237</v>
       </c>
       <c r="E249" s="21">
         <f>IF(D249="?OLD","!!!","")</f>
@@ -10655,7 +10615,7 @@
     </row>
     <row r="250" spans="1:12">
       <c r="A250" s="20" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E250" s="21">
         <f>IF(D250="?OLD","!!!","")</f>
@@ -10689,16 +10649,7 @@
     </row>
     <row r="251" spans="1:12">
       <c r="A251" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="B251" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C251" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D251" s="27" t="s">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="E251" s="21">
         <f>IF(D251="?OLD","!!!","")</f>
@@ -10732,7 +10683,13 @@
     </row>
     <row r="252" spans="1:12">
       <c r="A252" s="20" t="s">
-        <v>269</v>
+        <v>274</v>
+      </c>
+      <c r="B252" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C252" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E252" s="21">
         <f>IF(D252="?OLD","!!!","")</f>
@@ -10766,7 +10723,7 @@
     </row>
     <row r="253" spans="1:12">
       <c r="A253" s="20" t="s">
-        <v>270</v>
+        <v>166</v>
       </c>
       <c r="E253" s="21">
         <f>IF(D253="?OLD","!!!","")</f>
@@ -10800,13 +10757,7 @@
     </row>
     <row r="254" spans="1:12">
       <c r="A254" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="B254" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C254" s="27" t="s">
-        <v>125</v>
+        <v>275</v>
       </c>
       <c r="E254" s="21">
         <f>IF(D254="?OLD","!!!","")</f>
@@ -10840,7 +10791,16 @@
     </row>
     <row r="255" spans="1:12">
       <c r="A255" s="20" t="s">
-        <v>181</v>
+        <v>276</v>
+      </c>
+      <c r="B255" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C255" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D255" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E255" s="21">
         <f>IF(D255="?OLD","!!!","")</f>
@@ -10874,7 +10834,7 @@
     </row>
     <row r="256" spans="1:12">
       <c r="A256" s="20" t="s">
-        <v>160</v>
+        <v>277</v>
       </c>
       <c r="E256" s="21">
         <f>IF(D256="?OLD","!!!","")</f>
@@ -10908,7 +10868,7 @@
     </row>
     <row r="257" spans="1:12">
       <c r="A257" s="20" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E257" s="21">
         <f>IF(D257="?OLD","!!!","")</f>
@@ -10942,16 +10902,13 @@
     </row>
     <row r="258" spans="1:12">
       <c r="A258" s="20" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B258" s="27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C258" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D258" s="27" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="E258" s="21">
         <f>IF(D258="?OLD","!!!","")</f>
@@ -10985,7 +10942,7 @@
     </row>
     <row r="259" spans="1:12">
       <c r="A259" s="20" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="E259" s="21">
         <f>IF(D259="?OLD","!!!","")</f>
@@ -11019,16 +10976,7 @@
     </row>
     <row r="260" spans="1:12">
       <c r="A260" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="B260" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C260" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D260" s="27" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="E260" s="21">
         <f>IF(D260="?OLD","!!!","")</f>
@@ -11062,7 +11010,7 @@
     </row>
     <row r="261" spans="1:12">
       <c r="A261" s="20" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E261" s="21">
         <f>IF(D261="?OLD","!!!","")</f>
@@ -11096,7 +11044,16 @@
     </row>
     <row r="262" spans="1:12">
       <c r="A262" s="20" t="s">
-        <v>206</v>
+        <v>281</v>
+      </c>
+      <c r="B262" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C262" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D262" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E262" s="21">
         <f>IF(D262="?OLD","!!!","")</f>
@@ -11130,7 +11087,7 @@
     </row>
     <row r="263" spans="1:12">
       <c r="A263" s="20" t="s">
-        <v>276</v>
+        <v>143</v>
       </c>
       <c r="E263" s="21">
         <f>IF(D263="?OLD","!!!","")</f>
@@ -11164,16 +11121,16 @@
     </row>
     <row r="264" spans="1:12">
       <c r="A264" s="20" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B264" s="27" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="C264" s="27" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="D264" s="27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E264" s="21">
         <f>IF(D264="?OLD","!!!","")</f>
@@ -11207,7 +11164,7 @@
     </row>
     <row r="265" spans="1:12">
       <c r="A265" s="20" t="s">
-        <v>207</v>
+        <v>283</v>
       </c>
       <c r="E265" s="21">
         <f>IF(D265="?OLD","!!!","")</f>
@@ -11241,13 +11198,7 @@
     </row>
     <row r="266" spans="1:12">
       <c r="A266" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="B266" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="C266" s="27" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E266" s="21">
         <f>IF(D266="?OLD","!!!","")</f>
@@ -11281,7 +11232,7 @@
     </row>
     <row r="267" spans="1:12">
       <c r="A267" s="20" t="s">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="E267" s="21">
         <f>IF(D267="?OLD","!!!","")</f>
@@ -11315,7 +11266,16 @@
     </row>
     <row r="268" spans="1:12">
       <c r="A268" s="20" t="s">
-        <v>135</v>
+        <v>285</v>
+      </c>
+      <c r="B268" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C268" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D268" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E268" s="21">
         <f>IF(D268="?OLD","!!!","")</f>
@@ -11349,16 +11309,7 @@
     </row>
     <row r="269" spans="1:12">
       <c r="A269" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="B269" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C269" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D269" s="27" t="s">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="E269" s="21">
         <f>IF(D269="?OLD","!!!","")</f>
@@ -11392,7 +11343,13 @@
     </row>
     <row r="270" spans="1:12">
       <c r="A270" s="20" t="s">
-        <v>146</v>
+        <v>286</v>
+      </c>
+      <c r="B270" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="C270" s="27" t="s">
+        <v>218</v>
       </c>
       <c r="E270" s="21">
         <f>IF(D270="?OLD","!!!","")</f>
@@ -11426,16 +11383,7 @@
     </row>
     <row r="271" spans="1:12">
       <c r="A271" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="B271" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C271" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="D271" s="27" t="s">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="E271" s="21">
         <f>IF(D271="?OLD","!!!","")</f>
@@ -11469,7 +11417,7 @@
     </row>
     <row r="272" spans="1:12">
       <c r="A272" s="20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E272" s="21">
         <f>IF(D272="?OLD","!!!","")</f>
@@ -11503,7 +11451,16 @@
     </row>
     <row r="273" spans="1:12">
       <c r="A273" s="20" t="s">
-        <v>146</v>
+        <v>287</v>
+      </c>
+      <c r="B273" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C273" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D273" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E273" s="21">
         <f>IF(D273="?OLD","!!!","")</f>
@@ -11537,7 +11494,7 @@
     </row>
     <row r="274" spans="1:12">
       <c r="A274" s="20" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E274" s="21">
         <f>IF(D274="?OLD","!!!","")</f>
@@ -11571,7 +11528,16 @@
     </row>
     <row r="275" spans="1:12">
       <c r="A275" s="20" t="s">
-        <v>135</v>
+        <v>147</v>
+      </c>
+      <c r="B275" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C275" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D275" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E275" s="21">
         <f>IF(D275="?OLD","!!!","")</f>
@@ -11605,7 +11571,7 @@
     </row>
     <row r="276" spans="1:12">
       <c r="A276" s="20" t="s">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="E276" s="21">
         <f>IF(D276="?OLD","!!!","")</f>
@@ -11639,16 +11605,7 @@
     </row>
     <row r="277" spans="1:12">
       <c r="A277" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="B277" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C277" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D277" s="27" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="E277" s="21">
         <f>IF(D277="?OLD","!!!","")</f>
@@ -11682,7 +11639,7 @@
     </row>
     <row r="278" spans="1:12">
       <c r="A278" s="20" t="s">
-        <v>281</v>
+        <v>152</v>
       </c>
       <c r="E278" s="21">
         <f>IF(D278="?OLD","!!!","")</f>
@@ -11716,7 +11673,7 @@
     </row>
     <row r="279" spans="1:12">
       <c r="A279" s="20" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E279" s="21">
         <f>IF(D279="?OLD","!!!","")</f>
@@ -11750,7 +11707,7 @@
     </row>
     <row r="280" spans="1:12">
       <c r="A280" s="20" t="s">
-        <v>146</v>
+        <v>288</v>
       </c>
       <c r="E280" s="21">
         <f>IF(D280="?OLD","!!!","")</f>
@@ -11784,7 +11741,16 @@
     </row>
     <row r="281" spans="1:12">
       <c r="A281" s="20" t="s">
-        <v>216</v>
+        <v>287</v>
+      </c>
+      <c r="B281" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C281" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D281" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E281" s="21">
         <f>IF(D281="?OLD","!!!","")</f>
@@ -11818,7 +11784,7 @@
     </row>
     <row r="282" spans="1:12">
       <c r="A282" s="20" t="s">
-        <v>160</v>
+        <v>289</v>
       </c>
       <c r="E282" s="21">
         <f>IF(D282="?OLD","!!!","")</f>
@@ -11852,16 +11818,7 @@
     </row>
     <row r="283" spans="1:12">
       <c r="A283" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B283" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C283" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D283" s="27" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="E283" s="21">
         <f>IF(D283="?OLD","!!!","")</f>
@@ -11895,7 +11852,7 @@
     </row>
     <row r="284" spans="1:12">
       <c r="A284" s="20" t="s">
-        <v>269</v>
+        <v>151</v>
       </c>
       <c r="E284" s="21">
         <f>IF(D284="?OLD","!!!","")</f>
@@ -11929,7 +11886,7 @@
     </row>
     <row r="285" spans="1:12">
       <c r="A285" s="20" t="s">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="E285" s="21">
         <f>IF(D285="?OLD","!!!","")</f>
@@ -11963,13 +11920,7 @@
     </row>
     <row r="286" spans="1:12">
       <c r="A286" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="B286" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C286" s="27" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="E286" s="21">
         <f>IF(D286="?OLD","!!!","")</f>
@@ -12003,7 +11954,16 @@
     </row>
     <row r="287" spans="1:12">
       <c r="A287" s="20" t="s">
-        <v>283</v>
+        <v>13</v>
+      </c>
+      <c r="B287" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C287" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D287" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E287" s="21">
         <f>IF(D287="?OLD","!!!","")</f>
@@ -12037,7 +11997,7 @@
     </row>
     <row r="288" spans="1:12">
       <c r="A288" s="20" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E288" s="21">
         <f>IF(D288="?OLD","!!!","")</f>
@@ -12071,7 +12031,7 @@
     </row>
     <row r="289" spans="1:12">
       <c r="A289" s="20" t="s">
-        <v>131</v>
+        <v>290</v>
       </c>
       <c r="E289" s="21">
         <f>IF(D289="?OLD","!!!","")</f>
@@ -12105,7 +12065,13 @@
     </row>
     <row r="290" spans="1:12">
       <c r="A290" s="20" t="s">
-        <v>120</v>
+        <v>279</v>
+      </c>
+      <c r="B290" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C290" s="27" t="s">
+        <v>130</v>
       </c>
       <c r="E290" s="21">
         <f>IF(D290="?OLD","!!!","")</f>
@@ -12138,11 +12104,42 @@
       <c r="L290" s="26"/>
     </row>
     <row r="291" spans="1:12">
-      <c r="A291" s="20"/>
+      <c r="A291" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="E291" s="21">
+        <f>IF(D291="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F291" s="22" t="str">
+        <f>IF(OR(E291="",E291="!!!"),"",IF(NOT(ISNA(VLOOKUP(E291,E$1:E290,1,FALSE()))),"OLD",IF(AND(E291&lt;&gt;"",E291&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G291" s="23" t="str">
+        <f>IF(OR(E291="",E291="!!!"),"",IF(OR(J291=0,AND(J291=1,K291=1),AND(J291=1,I291="SBJ"),AND(J291=1,I291=0)),"?IN_FOCUS",IF(J291&lt;=2,"?ACTIVATED",IF(J291&lt;&gt;"","?FAMILIAR",IF(F291="NEW",IF(ISNA(VLOOKUP(E291,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H291" s="24" t="str">
+        <f>IF(J291&lt;&gt;1,"",IF(I291="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I291" s="25" t="str">
+        <f>IF(OR(E291="",E291="!!!",F291="NEW"),"",INDEX(B290:B$2,-1+SUMPRODUCT(MAX(ROW(E290:E$2)*(E291=E290:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J291" s="25" t="str">
+        <f>IF(OR(E291="",E291="!!!",F291="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E291)*(E291=E$2:E291)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E290)*(E2=E$1:E290))))))</f>
+        <v> </v>
+      </c>
+      <c r="K291" s="25" t="str">
+        <f>IF(OR(E291="",E291="!!!",F291="NEW"),"",INDEX(J$1:J290,SUMPRODUCT(MAX(ROW(E$1:E290)*(E291=E$1:E290)))))</f>
+        <v> </v>
+      </c>
+      <c r="L291" s="26"/>
     </row>
     <row r="292" spans="1:12">
       <c r="A292" s="20" t="s">
-        <v>152</v>
+        <v>292</v>
       </c>
       <c r="E292" s="21">
         <f>IF(D292="?OLD","!!!","")</f>
@@ -12176,21 +12173,41 @@
     </row>
     <row r="293" spans="1:12">
       <c r="A293" s="20" t="s">
-        <v>285</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="E293" s="21">
+        <f>IF(D293="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F293" s="22" t="str">
+        <f>IF(OR(E293="",E293="!!!"),"",IF(NOT(ISNA(VLOOKUP(E293,E$1:E292,1,FALSE()))),"OLD",IF(AND(E293&lt;&gt;"",E293&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G293" s="23" t="str">
+        <f>IF(OR(E293="",E293="!!!"),"",IF(OR(J293=0,AND(J293=1,K293=1),AND(J293=1,I293="SBJ"),AND(J293=1,I293=0)),"?IN_FOCUS",IF(J293&lt;=2,"?ACTIVATED",IF(J293&lt;&gt;"","?FAMILIAR",IF(F293="NEW",IF(ISNA(VLOOKUP(E293,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H293" s="24" t="str">
+        <f>IF(J293&lt;&gt;1,"",IF(I293="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I293" s="25" t="str">
+        <f>IF(OR(E293="",E293="!!!",F293="NEW"),"",INDEX(B292:B$2,-1+SUMPRODUCT(MAX(ROW(E292:E$2)*(E293=E292:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J293" s="25" t="str">
+        <f>IF(OR(E293="",E293="!!!",F293="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E293)*(E293=E$2:E293)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E292)*(E2=E$1:E292))))))</f>
+        <v> </v>
+      </c>
+      <c r="K293" s="25" t="str">
+        <f>IF(OR(E293="",E293="!!!",F293="NEW"),"",INDEX(J$1:J292,SUMPRODUCT(MAX(ROW(E$1:E292)*(E293=E$1:E292)))))</f>
+        <v> </v>
+      </c>
+      <c r="L293" s="26"/>
     </row>
     <row r="294" spans="1:12">
       <c r="A294" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="B294" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C294" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D294" s="27" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E294" s="21">
         <f>IF(D294="?OLD","!!!","")</f>
@@ -12223,42 +12240,11 @@
       <c r="L294" s="26"/>
     </row>
     <row r="295" spans="1:12">
-      <c r="A295" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E295" s="21">
-        <f>IF(D295="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F295" s="22" t="str">
-        <f>IF(OR(E295="",E295="!!!"),"",IF(NOT(ISNA(VLOOKUP(E295,E$1:E294,1,FALSE()))),"OLD",IF(AND(E295&lt;&gt;"",E295&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G295" s="23" t="str">
-        <f>IF(OR(E295="",E295="!!!"),"",IF(OR(J295=0,AND(J295=1,K295=1),AND(J295=1,I295="SBJ"),AND(J295=1,I295=0)),"?IN_FOCUS",IF(J295&lt;=2,"?ACTIVATED",IF(J295&lt;&gt;"","?FAMILIAR",IF(F295="NEW",IF(ISNA(VLOOKUP(E295,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H295" s="24" t="str">
-        <f>IF(J295&lt;&gt;1,"",IF(I295="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I295" s="25" t="str">
-        <f>IF(OR(E295="",E295="!!!",F295="NEW"),"",INDEX(B294:B$2,-1+SUMPRODUCT(MAX(ROW(E294:E$2)*(E295=E294:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J295" s="25" t="str">
-        <f>IF(OR(E295="",E295="!!!",F295="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E295)*(E295=E$2:E295)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E294)*(E2=E$1:E294))))))</f>
-        <v> </v>
-      </c>
-      <c r="K295" s="25" t="str">
-        <f>IF(OR(E295="",E295="!!!",F295="NEW"),"",INDEX(J$1:J294,SUMPRODUCT(MAX(ROW(E$1:E294)*(E295=E$1:E294)))))</f>
-        <v> </v>
-      </c>
-      <c r="L295" s="26"/>
+      <c r="A295" s="20"/>
     </row>
     <row r="296" spans="1:12">
       <c r="A296" s="20" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E296" s="21">
         <f>IF(D296="?OLD","!!!","")</f>
@@ -12292,41 +12278,21 @@
     </row>
     <row r="297" spans="1:12">
       <c r="A297" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E297" s="21">
-        <f>IF(D297="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F297" s="22" t="str">
-        <f>IF(OR(E297="",E297="!!!"),"",IF(NOT(ISNA(VLOOKUP(E297,E$1:E296,1,FALSE()))),"OLD",IF(AND(E297&lt;&gt;"",E297&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G297" s="23" t="str">
-        <f>IF(OR(E297="",E297="!!!"),"",IF(OR(J297=0,AND(J297=1,K297=1),AND(J297=1,I297="SBJ"),AND(J297=1,I297=0)),"?IN_FOCUS",IF(J297&lt;=2,"?ACTIVATED",IF(J297&lt;&gt;"","?FAMILIAR",IF(F297="NEW",IF(ISNA(VLOOKUP(E297,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H297" s="24" t="str">
-        <f>IF(J297&lt;&gt;1,"",IF(I297="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I297" s="25" t="str">
-        <f>IF(OR(E297="",E297="!!!",F297="NEW"),"",INDEX(B296:B$2,-1+SUMPRODUCT(MAX(ROW(E296:E$2)*(E297=E296:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J297" s="25" t="str">
-        <f>IF(OR(E297="",E297="!!!",F297="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E297)*(E297=E$2:E297)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E296)*(E2=E$1:E296))))))</f>
-        <v> </v>
-      </c>
-      <c r="K297" s="25" t="str">
-        <f>IF(OR(E297="",E297="!!!",F297="NEW"),"",INDEX(J$1:J296,SUMPRODUCT(MAX(ROW(E$1:E296)*(E297=E$1:E296)))))</f>
-        <v> </v>
-      </c>
-      <c r="L297" s="26"/>
+        <v>293</v>
+      </c>
     </row>
     <row r="298" spans="1:12">
       <c r="A298" s="20" t="s">
-        <v>156</v>
+        <v>294</v>
+      </c>
+      <c r="B298" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C298" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D298" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E298" s="21">
         <f>IF(D298="?OLD","!!!","")</f>
@@ -12360,16 +12326,7 @@
     </row>
     <row r="299" spans="1:12">
       <c r="A299" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="B299" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C299" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D299" s="27" t="s">
-        <v>105</v>
+        <v>295</v>
       </c>
       <c r="E299" s="21">
         <f>IF(D299="?OLD","!!!","")</f>
@@ -12403,7 +12360,7 @@
     </row>
     <row r="300" spans="1:12">
       <c r="A300" s="20" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="E300" s="21">
         <f>IF(D300="?OLD","!!!","")</f>
@@ -12437,7 +12394,7 @@
     </row>
     <row r="301" spans="1:12">
       <c r="A301" s="20" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E301" s="21">
         <f>IF(D301="?OLD","!!!","")</f>
@@ -12471,7 +12428,7 @@
     </row>
     <row r="302" spans="1:12">
       <c r="A302" s="20" t="s">
-        <v>291</v>
+        <v>162</v>
       </c>
       <c r="E302" s="21">
         <f>IF(D302="?OLD","!!!","")</f>
@@ -12505,7 +12462,16 @@
     </row>
     <row r="303" spans="1:12">
       <c r="A303" s="20" t="s">
-        <v>219</v>
+        <v>297</v>
+      </c>
+      <c r="B303" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C303" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D303" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E303" s="21">
         <f>IF(D303="?OLD","!!!","")</f>
@@ -12539,7 +12505,7 @@
     </row>
     <row r="304" spans="1:12">
       <c r="A304" s="20" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E304" s="21">
         <f>IF(D304="?OLD","!!!","")</f>
@@ -12573,7 +12539,7 @@
     </row>
     <row r="305" spans="1:12">
       <c r="A305" s="20" t="s">
-        <v>161</v>
+        <v>298</v>
       </c>
       <c r="E305" s="21">
         <f>IF(D305="?OLD","!!!","")</f>
@@ -12607,7 +12573,7 @@
     </row>
     <row r="306" spans="1:12">
       <c r="A306" s="20" t="s">
-        <v>176</v>
+        <v>299</v>
       </c>
       <c r="E306" s="21">
         <f>IF(D306="?OLD","!!!","")</f>
@@ -12641,7 +12607,7 @@
     </row>
     <row r="307" spans="1:12">
       <c r="A307" s="20" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="E307" s="21">
         <f>IF(D307="?OLD","!!!","")</f>
@@ -12675,16 +12641,7 @@
     </row>
     <row r="308" spans="1:12">
       <c r="A308" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B308" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C308" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D308" s="27" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E308" s="21">
         <f>IF(D308="?OLD","!!!","")</f>
@@ -12718,7 +12675,7 @@
     </row>
     <row r="309" spans="1:12">
       <c r="A309" s="20" t="s">
-        <v>293</v>
+        <v>167</v>
       </c>
       <c r="E309" s="21">
         <f>IF(D309="?OLD","!!!","")</f>
@@ -12752,7 +12709,7 @@
     </row>
     <row r="310" spans="1:12">
       <c r="A310" s="20" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="E310" s="21">
         <f>IF(D310="?OLD","!!!","")</f>
@@ -12786,13 +12743,7 @@
     </row>
     <row r="311" spans="1:12">
       <c r="A311" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="B311" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C311" s="27" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E311" s="21">
         <f>IF(D311="?OLD","!!!","")</f>
@@ -12826,13 +12777,16 @@
     </row>
     <row r="312" spans="1:12">
       <c r="A312" s="20" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B312" s="27" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="C312" s="27" t="s">
-        <v>110</v>
+        <v>123</v>
+      </c>
+      <c r="D312" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E312" s="21">
         <f>IF(D312="?OLD","!!!","")</f>
@@ -12866,7 +12820,7 @@
     </row>
     <row r="313" spans="1:12">
       <c r="A313" s="20" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="E313" s="21">
         <f>IF(D313="?OLD","!!!","")</f>
@@ -12900,7 +12854,7 @@
     </row>
     <row r="314" spans="1:12">
       <c r="A314" s="20" t="s">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="E314" s="21">
         <f>IF(D314="?OLD","!!!","")</f>
@@ -12934,13 +12888,13 @@
     </row>
     <row r="315" spans="1:12">
       <c r="A315" s="20" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B315" s="27" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C315" s="27" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="E315" s="21">
         <f>IF(D315="?OLD","!!!","")</f>
@@ -12974,7 +12928,13 @@
     </row>
     <row r="316" spans="1:12">
       <c r="A316" s="20" t="s">
-        <v>298</v>
+        <v>303</v>
+      </c>
+      <c r="B316" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C316" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="E316" s="21">
         <f>IF(D316="?OLD","!!!","")</f>
@@ -13008,7 +12968,7 @@
     </row>
     <row r="317" spans="1:12">
       <c r="A317" s="20" t="s">
-        <v>120</v>
+        <v>215</v>
       </c>
       <c r="E317" s="21">
         <f>IF(D317="?OLD","!!!","")</f>
@@ -13041,16 +13001,82 @@
       <c r="L317" s="26"/>
     </row>
     <row r="318" spans="1:12">
-      <c r="A318" s="20"/>
+      <c r="A318" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="E318" s="21">
+        <f>IF(D318="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F318" s="22" t="str">
+        <f>IF(OR(E318="",E318="!!!"),"",IF(NOT(ISNA(VLOOKUP(E318,E$1:E317,1,FALSE()))),"OLD",IF(AND(E318&lt;&gt;"",E318&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G318" s="23" t="str">
+        <f>IF(OR(E318="",E318="!!!"),"",IF(OR(J318=0,AND(J318=1,K318=1),AND(J318=1,I318="SBJ"),AND(J318=1,I318=0)),"?IN_FOCUS",IF(J318&lt;=2,"?ACTIVATED",IF(J318&lt;&gt;"","?FAMILIAR",IF(F318="NEW",IF(ISNA(VLOOKUP(E318,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H318" s="24" t="str">
+        <f>IF(J318&lt;&gt;1,"",IF(I318="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I318" s="25" t="str">
+        <f>IF(OR(E318="",E318="!!!",F318="NEW"),"",INDEX(B317:B$2,-1+SUMPRODUCT(MAX(ROW(E317:E$2)*(E318=E317:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J318" s="25" t="str">
+        <f>IF(OR(E318="",E318="!!!",F318="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E318)*(E318=E$2:E318)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E317)*(E2=E$1:E317))))))</f>
+        <v> </v>
+      </c>
+      <c r="K318" s="25" t="str">
+        <f>IF(OR(E318="",E318="!!!",F318="NEW"),"",INDEX(J$1:J317,SUMPRODUCT(MAX(ROW(E$1:E317)*(E318=E$1:E317)))))</f>
+        <v> </v>
+      </c>
+      <c r="L318" s="26"/>
     </row>
     <row r="319" spans="1:12">
       <c r="A319" s="20" t="s">
-        <v>299</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="B319" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C319" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="E319" s="21">
+        <f>IF(D319="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F319" s="22" t="str">
+        <f>IF(OR(E319="",E319="!!!"),"",IF(NOT(ISNA(VLOOKUP(E319,E$1:E318,1,FALSE()))),"OLD",IF(AND(E319&lt;&gt;"",E319&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G319" s="23" t="str">
+        <f>IF(OR(E319="",E319="!!!"),"",IF(OR(J319=0,AND(J319=1,K319=1),AND(J319=1,I319="SBJ"),AND(J319=1,I319=0)),"?IN_FOCUS",IF(J319&lt;=2,"?ACTIVATED",IF(J319&lt;&gt;"","?FAMILIAR",IF(F319="NEW",IF(ISNA(VLOOKUP(E319,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H319" s="24" t="str">
+        <f>IF(J319&lt;&gt;1,"",IF(I319="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I319" s="25" t="str">
+        <f>IF(OR(E319="",E319="!!!",F319="NEW"),"",INDEX(B318:B$2,-1+SUMPRODUCT(MAX(ROW(E318:E$2)*(E319=E318:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J319" s="25" t="str">
+        <f>IF(OR(E319="",E319="!!!",F319="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E319)*(E319=E$2:E319)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E318)*(E2=E$1:E318))))))</f>
+        <v> </v>
+      </c>
+      <c r="K319" s="25" t="str">
+        <f>IF(OR(E319="",E319="!!!",F319="NEW"),"",INDEX(J$1:J318,SUMPRODUCT(MAX(ROW(E$1:E318)*(E319=E$1:E318)))))</f>
+        <v> </v>
+      </c>
+      <c r="L319" s="26"/>
     </row>
     <row r="320" spans="1:12">
       <c r="A320" s="20" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E320" s="21">
         <f>IF(D320="?OLD","!!!","")</f>
@@ -13084,16 +13110,7 @@
     </row>
     <row r="321" spans="1:12">
       <c r="A321" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="B321" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C321" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="D321" s="27" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E321" s="21">
         <f>IF(D321="?OLD","!!!","")</f>
@@ -13126,85 +13143,16 @@
       <c r="L321" s="26"/>
     </row>
     <row r="322" spans="1:12">
-      <c r="A322" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="E322" s="21">
-        <f>IF(D322="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F322" s="22" t="str">
-        <f>IF(OR(E322="",E322="!!!"),"",IF(NOT(ISNA(VLOOKUP(E322,E$1:E321,1,FALSE()))),"OLD",IF(AND(E322&lt;&gt;"",E322&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G322" s="23" t="str">
-        <f>IF(OR(E322="",E322="!!!"),"",IF(OR(J322=0,AND(J322=1,K322=1),AND(J322=1,I322="SBJ"),AND(J322=1,I322=0)),"?IN_FOCUS",IF(J322&lt;=2,"?ACTIVATED",IF(J322&lt;&gt;"","?FAMILIAR",IF(F322="NEW",IF(ISNA(VLOOKUP(E322,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H322" s="24" t="str">
-        <f>IF(J322&lt;&gt;1,"",IF(I322="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I322" s="25" t="str">
-        <f>IF(OR(E322="",E322="!!!",F322="NEW"),"",INDEX(B321:B$2,-1+SUMPRODUCT(MAX(ROW(E321:E$2)*(E322=E321:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J322" s="25" t="str">
-        <f>IF(OR(E322="",E322="!!!",F322="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E322)*(E322=E$2:E322)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E321)*(E2=E$1:E321))))))</f>
-        <v> </v>
-      </c>
-      <c r="K322" s="25" t="str">
-        <f>IF(OR(E322="",E322="!!!",F322="NEW"),"",INDEX(J$1:J321,SUMPRODUCT(MAX(ROW(E$1:E321)*(E322=E$1:E321)))))</f>
-        <v> </v>
-      </c>
-      <c r="L322" s="26"/>
+      <c r="A322" s="20"/>
     </row>
     <row r="323" spans="1:12">
       <c r="A323" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="B323" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C323" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="D323" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E323" s="21">
-        <f>IF(D323="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F323" s="22" t="str">
-        <f>IF(OR(E323="",E323="!!!"),"",IF(NOT(ISNA(VLOOKUP(E323,E$1:E322,1,FALSE()))),"OLD",IF(AND(E323&lt;&gt;"",E323&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G323" s="23" t="str">
-        <f>IF(OR(E323="",E323="!!!"),"",IF(OR(J323=0,AND(J323=1,K323=1),AND(J323=1,I323="SBJ"),AND(J323=1,I323=0)),"?IN_FOCUS",IF(J323&lt;=2,"?ACTIVATED",IF(J323&lt;&gt;"","?FAMILIAR",IF(F323="NEW",IF(ISNA(VLOOKUP(E323,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H323" s="24" t="str">
-        <f>IF(J323&lt;&gt;1,"",IF(I323="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I323" s="25" t="str">
-        <f>IF(OR(E323="",E323="!!!",F323="NEW"),"",INDEX(B322:B$2,-1+SUMPRODUCT(MAX(ROW(E322:E$2)*(E323=E322:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J323" s="25" t="str">
-        <f>IF(OR(E323="",E323="!!!",F323="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E323)*(E323=E$2:E323)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E322)*(E2=E$1:E322))))))</f>
-        <v> </v>
-      </c>
-      <c r="K323" s="25" t="str">
-        <f>IF(OR(E323="",E323="!!!",F323="NEW"),"",INDEX(J$1:J322,SUMPRODUCT(MAX(ROW(E$1:E322)*(E323=E$1:E322)))))</f>
-        <v> </v>
-      </c>
-      <c r="L323" s="26"/>
+        <v>307</v>
+      </c>
     </row>
     <row r="324" spans="1:12">
       <c r="A324" s="20" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="E324" s="21">
         <f>IF(D324="?OLD","!!!","")</f>
@@ -13238,7 +13186,16 @@
     </row>
     <row r="325" spans="1:12">
       <c r="A325" s="20" t="s">
-        <v>160</v>
+        <v>245</v>
+      </c>
+      <c r="B325" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C325" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D325" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E325" s="21">
         <f>IF(D325="?OLD","!!!","")</f>
@@ -13272,16 +13229,7 @@
     </row>
     <row r="326" spans="1:12">
       <c r="A326" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B326" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C326" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D326" s="27" t="s">
-        <v>105</v>
+        <v>309</v>
       </c>
       <c r="E326" s="21">
         <f>IF(D326="?OLD","!!!","")</f>
@@ -13315,7 +13263,16 @@
     </row>
     <row r="327" spans="1:12">
       <c r="A327" s="20" t="s">
-        <v>302</v>
+        <v>129</v>
+      </c>
+      <c r="B327" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C327" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="D327" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E327" s="21">
         <f>IF(D327="?OLD","!!!","")</f>
@@ -13349,13 +13306,7 @@
     </row>
     <row r="328" spans="1:12">
       <c r="A328" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="B328" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="C328" s="27" t="s">
-        <v>110</v>
+        <v>301</v>
       </c>
       <c r="E328" s="21">
         <f>IF(D328="?OLD","!!!","")</f>
@@ -13389,7 +13340,7 @@
     </row>
     <row r="329" spans="1:12">
       <c r="A329" s="20" t="s">
-        <v>12</v>
+        <v>166</v>
       </c>
       <c r="E329" s="21">
         <f>IF(D329="?OLD","!!!","")</f>
@@ -13423,7 +13374,16 @@
     </row>
     <row r="330" spans="1:12">
       <c r="A330" s="20" t="s">
-        <v>181</v>
+        <v>300</v>
+      </c>
+      <c r="B330" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C330" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D330" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E330" s="21">
         <f>IF(D330="?OLD","!!!","")</f>
@@ -13457,13 +13417,7 @@
     </row>
     <row r="331" spans="1:12">
       <c r="A331" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="B331" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C331" s="27" t="s">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="E331" s="21">
         <f>IF(D331="?OLD","!!!","")</f>
@@ -13497,7 +13451,13 @@
     </row>
     <row r="332" spans="1:12">
       <c r="A332" s="20" t="s">
-        <v>298</v>
+        <v>311</v>
+      </c>
+      <c r="B332" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="C332" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="E332" s="21">
         <f>IF(D332="?OLD","!!!","")</f>
@@ -13531,7 +13491,7 @@
     </row>
     <row r="333" spans="1:12">
       <c r="A333" s="20" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="E333" s="21">
         <f>IF(D333="?OLD","!!!","")</f>
@@ -13564,12 +13524,78 @@
       <c r="L333" s="26"/>
     </row>
     <row r="334" spans="1:12">
-      <c r="A334" s="20"/>
+      <c r="A334" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E334" s="21">
+        <f>IF(D334="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F334" s="22" t="str">
+        <f>IF(OR(E334="",E334="!!!"),"",IF(NOT(ISNA(VLOOKUP(E334,E$1:E333,1,FALSE()))),"OLD",IF(AND(E334&lt;&gt;"",E334&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G334" s="23" t="str">
+        <f>IF(OR(E334="",E334="!!!"),"",IF(OR(J334=0,AND(J334=1,K334=1),AND(J334=1,I334="SBJ"),AND(J334=1,I334=0)),"?IN_FOCUS",IF(J334&lt;=2,"?ACTIVATED",IF(J334&lt;&gt;"","?FAMILIAR",IF(F334="NEW",IF(ISNA(VLOOKUP(E334,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H334" s="24" t="str">
+        <f>IF(J334&lt;&gt;1,"",IF(I334="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I334" s="25" t="str">
+        <f>IF(OR(E334="",E334="!!!",F334="NEW"),"",INDEX(B333:B$2,-1+SUMPRODUCT(MAX(ROW(E333:E$2)*(E334=E333:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J334" s="25" t="str">
+        <f>IF(OR(E334="",E334="!!!",F334="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E334)*(E334=E$2:E334)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E333)*(E2=E$1:E333))))))</f>
+        <v> </v>
+      </c>
+      <c r="K334" s="25" t="str">
+        <f>IF(OR(E334="",E334="!!!",F334="NEW"),"",INDEX(J$1:J333,SUMPRODUCT(MAX(ROW(E$1:E333)*(E334=E$1:E333)))))</f>
+        <v> </v>
+      </c>
+      <c r="L334" s="26"/>
     </row>
     <row r="335" spans="1:12">
       <c r="A335" s="20" t="s">
-        <v>305</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="B335" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C335" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="E335" s="21">
+        <f>IF(D335="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F335" s="22" t="str">
+        <f>IF(OR(E335="",E335="!!!"),"",IF(NOT(ISNA(VLOOKUP(E335,E$1:E334,1,FALSE()))),"OLD",IF(AND(E335&lt;&gt;"",E335&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G335" s="23" t="str">
+        <f>IF(OR(E335="",E335="!!!"),"",IF(OR(J335=0,AND(J335=1,K335=1),AND(J335=1,I335="SBJ"),AND(J335=1,I335=0)),"?IN_FOCUS",IF(J335&lt;=2,"?ACTIVATED",IF(J335&lt;&gt;"","?FAMILIAR",IF(F335="NEW",IF(ISNA(VLOOKUP(E335,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H335" s="24" t="str">
+        <f>IF(J335&lt;&gt;1,"",IF(I335="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I335" s="25" t="str">
+        <f>IF(OR(E335="",E335="!!!",F335="NEW"),"",INDEX(B334:B$2,-1+SUMPRODUCT(MAX(ROW(E334:E$2)*(E335=E334:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J335" s="25" t="str">
+        <f>IF(OR(E335="",E335="!!!",F335="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E335)*(E335=E$2:E335)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E334)*(E2=E$1:E334))))))</f>
+        <v> </v>
+      </c>
+      <c r="K335" s="25" t="str">
+        <f>IF(OR(E335="",E335="!!!",F335="NEW"),"",INDEX(J$1:J334,SUMPRODUCT(MAX(ROW(E$1:E334)*(E335=E$1:E334)))))</f>
+        <v> </v>
+      </c>
+      <c r="L335" s="26"/>
     </row>
     <row r="336" spans="1:12">
       <c r="A336" s="20" t="s">
@@ -13607,7 +13633,7 @@
     </row>
     <row r="337" spans="1:12">
       <c r="A337" s="20" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="E337" s="21">
         <f>IF(D337="?OLD","!!!","")</f>
@@ -13640,85 +13666,16 @@
       <c r="L337" s="26"/>
     </row>
     <row r="338" spans="1:12">
-      <c r="A338" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="B338" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C338" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D338" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E338" s="21">
-        <f>IF(D338="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F338" s="22" t="str">
-        <f>IF(OR(E338="",E338="!!!"),"",IF(NOT(ISNA(VLOOKUP(E338,E$1:E337,1,FALSE()))),"OLD",IF(AND(E338&lt;&gt;"",E338&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G338" s="23" t="str">
-        <f>IF(OR(E338="",E338="!!!"),"",IF(OR(J338=0,AND(J338=1,K338=1),AND(J338=1,I338="SBJ"),AND(J338=1,I338=0)),"?IN_FOCUS",IF(J338&lt;=2,"?ACTIVATED",IF(J338&lt;&gt;"","?FAMILIAR",IF(F338="NEW",IF(ISNA(VLOOKUP(E338,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H338" s="24" t="str">
-        <f>IF(J338&lt;&gt;1,"",IF(I338="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I338" s="25" t="str">
-        <f>IF(OR(E338="",E338="!!!",F338="NEW"),"",INDEX(B337:B$2,-1+SUMPRODUCT(MAX(ROW(E337:E$2)*(E338=E337:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J338" s="25" t="str">
-        <f>IF(OR(E338="",E338="!!!",F338="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E338)*(E338=E$2:E338)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E337)*(E2=E$1:E337))))))</f>
-        <v> </v>
-      </c>
-      <c r="K338" s="25" t="str">
-        <f>IF(OR(E338="",E338="!!!",F338="NEW"),"",INDEX(J$1:J337,SUMPRODUCT(MAX(ROW(E$1:E337)*(E338=E$1:E337)))))</f>
-        <v> </v>
-      </c>
-      <c r="L338" s="26"/>
+      <c r="A338" s="20"/>
     </row>
     <row r="339" spans="1:12">
       <c r="A339" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="E339" s="21">
-        <f>IF(D339="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F339" s="22" t="str">
-        <f>IF(OR(E339="",E339="!!!"),"",IF(NOT(ISNA(VLOOKUP(E339,E$1:E338,1,FALSE()))),"OLD",IF(AND(E339&lt;&gt;"",E339&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G339" s="23" t="str">
-        <f>IF(OR(E339="",E339="!!!"),"",IF(OR(J339=0,AND(J339=1,K339=1),AND(J339=1,I339="SBJ"),AND(J339=1,I339=0)),"?IN_FOCUS",IF(J339&lt;=2,"?ACTIVATED",IF(J339&lt;&gt;"","?FAMILIAR",IF(F339="NEW",IF(ISNA(VLOOKUP(E339,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H339" s="24" t="str">
-        <f>IF(J339&lt;&gt;1,"",IF(I339="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I339" s="25" t="str">
-        <f>IF(OR(E339="",E339="!!!",F339="NEW"),"",INDEX(B338:B$2,-1+SUMPRODUCT(MAX(ROW(E338:E$2)*(E339=E338:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J339" s="25" t="str">
-        <f>IF(OR(E339="",E339="!!!",F339="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E339)*(E339=E$2:E339)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E338)*(E2=E$1:E338))))))</f>
-        <v> </v>
-      </c>
-      <c r="K339" s="25" t="str">
-        <f>IF(OR(E339="",E339="!!!",F339="NEW"),"",INDEX(J$1:J338,SUMPRODUCT(MAX(ROW(E$1:E338)*(E339=E$1:E338)))))</f>
-        <v> </v>
-      </c>
-      <c r="L339" s="26"/>
+        <v>313</v>
+      </c>
     </row>
     <row r="340" spans="1:12">
       <c r="A340" s="20" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E340" s="21">
         <f>IF(D340="?OLD","!!!","")</f>
@@ -13752,16 +13709,7 @@
     </row>
     <row r="341" spans="1:12">
       <c r="A341" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="B341" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C341" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D341" s="27" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="E341" s="21">
         <f>IF(D341="?OLD","!!!","")</f>
@@ -13795,7 +13743,16 @@
     </row>
     <row r="342" spans="1:12">
       <c r="A342" s="20" t="s">
-        <v>181</v>
+        <v>315</v>
+      </c>
+      <c r="B342" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C342" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D342" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E342" s="21">
         <f>IF(D342="?OLD","!!!","")</f>
@@ -13829,7 +13786,7 @@
     </row>
     <row r="343" spans="1:12">
       <c r="A343" s="20" t="s">
-        <v>310</v>
+        <v>143</v>
       </c>
       <c r="E343" s="21">
         <f>IF(D343="?OLD","!!!","")</f>
@@ -13863,16 +13820,7 @@
     </row>
     <row r="344" spans="1:12">
       <c r="A344" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B344" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C344" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="D344" s="27" t="s">
-        <v>105</v>
+        <v>316</v>
       </c>
       <c r="E344" s="21">
         <f>IF(D344="?OLD","!!!","")</f>
@@ -13906,7 +13854,16 @@
     </row>
     <row r="345" spans="1:12">
       <c r="A345" s="20" t="s">
-        <v>107</v>
+        <v>317</v>
+      </c>
+      <c r="B345" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C345" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D345" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E345" s="21">
         <f>IF(D345="?OLD","!!!","")</f>
@@ -13940,7 +13897,7 @@
     </row>
     <row r="346" spans="1:12">
       <c r="A346" s="20" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="E346" s="21">
         <f>IF(D346="?OLD","!!!","")</f>
@@ -13974,7 +13931,7 @@
     </row>
     <row r="347" spans="1:12">
       <c r="A347" s="20" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="E347" s="21">
         <f>IF(D347="?OLD","!!!","")</f>
@@ -14008,7 +13965,16 @@
     </row>
     <row r="348" spans="1:12">
       <c r="A348" s="20" t="s">
-        <v>140</v>
+        <v>319</v>
+      </c>
+      <c r="B348" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C348" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="D348" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E348" s="21">
         <f>IF(D348="?OLD","!!!","")</f>
@@ -14042,16 +14008,7 @@
     </row>
     <row r="349" spans="1:12">
       <c r="A349" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="B349" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C349" s="27" t="s">
         <v>115</v>
-      </c>
-      <c r="D349" s="27" t="s">
-        <v>105</v>
       </c>
       <c r="E349" s="21">
         <f>IF(D349="?OLD","!!!","")</f>
@@ -14085,7 +14042,7 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" s="20" t="s">
-        <v>313</v>
+        <v>145</v>
       </c>
       <c r="E350" s="21">
         <f>IF(D350="?OLD","!!!","")</f>
@@ -14119,16 +14076,7 @@
     </row>
     <row r="351" spans="1:12">
       <c r="A351" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="B351" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C351" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="D351" s="27" t="s">
-        <v>105</v>
+        <v>284</v>
       </c>
       <c r="E351" s="21">
         <f>IF(D351="?OLD","!!!","")</f>
@@ -14162,7 +14110,7 @@
     </row>
     <row r="352" spans="1:12">
       <c r="A352" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E352" s="21">
         <f>IF(D352="?OLD","!!!","")</f>
@@ -14196,7 +14144,16 @@
     </row>
     <row r="353" spans="1:12">
       <c r="A353" s="20" t="s">
-        <v>315</v>
+        <v>320</v>
+      </c>
+      <c r="B353" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C353" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D353" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E353" s="21">
         <f>IF(D353="?OLD","!!!","")</f>
@@ -14230,16 +14187,7 @@
     </row>
     <row r="354" spans="1:12">
       <c r="A354" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="B354" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C354" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="D354" s="27" t="s">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="E354" s="21">
         <f>IF(D354="?OLD","!!!","")</f>
@@ -14273,7 +14221,16 @@
     </row>
     <row r="355" spans="1:12">
       <c r="A355" s="20" t="s">
-        <v>317</v>
+        <v>322</v>
+      </c>
+      <c r="B355" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C355" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="D355" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E355" s="21">
         <f>IF(D355="?OLD","!!!","")</f>
@@ -14307,7 +14264,7 @@
     </row>
     <row r="356" spans="1:12">
       <c r="A356" s="20" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E356" s="21">
         <f>IF(D356="?OLD","!!!","")</f>
@@ -14341,7 +14298,7 @@
     </row>
     <row r="357" spans="1:12">
       <c r="A357" s="20" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E357" s="21">
         <f>IF(D357="?OLD","!!!","")</f>
@@ -14375,7 +14332,16 @@
     </row>
     <row r="358" spans="1:12">
       <c r="A358" s="20" t="s">
-        <v>319</v>
+        <v>324</v>
+      </c>
+      <c r="B358" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C358" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D358" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E358" s="21">
         <f>IF(D358="?OLD","!!!","")</f>
@@ -14409,16 +14375,7 @@
     </row>
     <row r="359" spans="1:12">
       <c r="A359" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="B359" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C359" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D359" s="27" t="s">
-        <v>105</v>
+        <v>325</v>
       </c>
       <c r="E359" s="21">
         <f>IF(D359="?OLD","!!!","")</f>
@@ -14452,7 +14409,7 @@
     </row>
     <row r="360" spans="1:12">
       <c r="A360" s="20" t="s">
-        <v>216</v>
+        <v>153</v>
       </c>
       <c r="E360" s="21">
         <f>IF(D360="?OLD","!!!","")</f>
@@ -14486,7 +14443,7 @@
     </row>
     <row r="361" spans="1:12">
       <c r="A361" s="20" t="s">
-        <v>160</v>
+        <v>326</v>
       </c>
       <c r="E361" s="21">
         <f>IF(D361="?OLD","!!!","")</f>
@@ -14520,16 +14477,7 @@
     </row>
     <row r="362" spans="1:12">
       <c r="A362" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="B362" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C362" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D362" s="27" t="s">
-        <v>105</v>
+        <v>327</v>
       </c>
       <c r="E362" s="21">
         <f>IF(D362="?OLD","!!!","")</f>
@@ -14563,7 +14511,16 @@
     </row>
     <row r="363" spans="1:12">
       <c r="A363" s="20" t="s">
-        <v>12</v>
+        <v>328</v>
+      </c>
+      <c r="B363" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C363" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D363" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E363" s="21">
         <f>IF(D363="?OLD","!!!","")</f>
@@ -14597,7 +14554,7 @@
     </row>
     <row r="364" spans="1:12">
       <c r="A364" s="20" t="s">
-        <v>322</v>
+        <v>224</v>
       </c>
       <c r="E364" s="21">
         <f>IF(D364="?OLD","!!!","")</f>
@@ -14631,13 +14588,7 @@
     </row>
     <row r="365" spans="1:12">
       <c r="A365" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="B365" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C365" s="27" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="E365" s="21">
         <f>IF(D365="?OLD","!!!","")</f>
@@ -14671,7 +14622,16 @@
     </row>
     <row r="366" spans="1:12">
       <c r="A366" s="20" t="s">
-        <v>65</v>
+        <v>329</v>
+      </c>
+      <c r="B366" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C366" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D366" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E366" s="21">
         <f>IF(D366="?OLD","!!!","")</f>
@@ -14705,7 +14665,7 @@
     </row>
     <row r="367" spans="1:12">
       <c r="A367" s="20" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="E367" s="21">
         <f>IF(D367="?OLD","!!!","")</f>
@@ -14738,25 +14698,82 @@
       <c r="L367" s="26"/>
     </row>
     <row r="368" spans="1:12">
-      <c r="A368" s="20"/>
+      <c r="A368" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="E368" s="21">
+        <f>IF(D368="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F368" s="22" t="str">
+        <f>IF(OR(E368="",E368="!!!"),"",IF(NOT(ISNA(VLOOKUP(E368,E$1:E367,1,FALSE()))),"OLD",IF(AND(E368&lt;&gt;"",E368&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G368" s="23" t="str">
+        <f>IF(OR(E368="",E368="!!!"),"",IF(OR(J368=0,AND(J368=1,K368=1),AND(J368=1,I368="SBJ"),AND(J368=1,I368=0)),"?IN_FOCUS",IF(J368&lt;=2,"?ACTIVATED",IF(J368&lt;&gt;"","?FAMILIAR",IF(F368="NEW",IF(ISNA(VLOOKUP(E368,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H368" s="24" t="str">
+        <f>IF(J368&lt;&gt;1,"",IF(I368="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I368" s="25" t="str">
+        <f>IF(OR(E368="",E368="!!!",F368="NEW"),"",INDEX(B367:B$2,-1+SUMPRODUCT(MAX(ROW(E367:E$2)*(E368=E367:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J368" s="25" t="str">
+        <f>IF(OR(E368="",E368="!!!",F368="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E368)*(E368=E$2:E368)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E367)*(E2=E$1:E367))))))</f>
+        <v> </v>
+      </c>
+      <c r="K368" s="25" t="str">
+        <f>IF(OR(E368="",E368="!!!",F368="NEW"),"",INDEX(J$1:J367,SUMPRODUCT(MAX(ROW(E$1:E367)*(E368=E$1:E367)))))</f>
+        <v> </v>
+      </c>
+      <c r="L368" s="26"/>
     </row>
     <row r="369" spans="1:12">
       <c r="A369" s="20" t="s">
-        <v>324</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="B369" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C369" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="E369" s="21">
+        <f>IF(D369="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F369" s="22" t="str">
+        <f>IF(OR(E369="",E369="!!!"),"",IF(NOT(ISNA(VLOOKUP(E369,E$1:E368,1,FALSE()))),"OLD",IF(AND(E369&lt;&gt;"",E369&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G369" s="23" t="str">
+        <f>IF(OR(E369="",E369="!!!"),"",IF(OR(J369=0,AND(J369=1,K369=1),AND(J369=1,I369="SBJ"),AND(J369=1,I369=0)),"?IN_FOCUS",IF(J369&lt;=2,"?ACTIVATED",IF(J369&lt;&gt;"","?FAMILIAR",IF(F369="NEW",IF(ISNA(VLOOKUP(E369,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H369" s="24" t="str">
+        <f>IF(J369&lt;&gt;1,"",IF(I369="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I369" s="25" t="str">
+        <f>IF(OR(E369="",E369="!!!",F369="NEW"),"",INDEX(B368:B$2,-1+SUMPRODUCT(MAX(ROW(E368:E$2)*(E369=E368:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J369" s="25" t="str">
+        <f>IF(OR(E369="",E369="!!!",F369="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E369)*(E369=E$2:E369)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E368)*(E2=E$1:E368))))))</f>
+        <v> </v>
+      </c>
+      <c r="K369" s="25" t="str">
+        <f>IF(OR(E369="",E369="!!!",F369="NEW"),"",INDEX(J$1:J368,SUMPRODUCT(MAX(ROW(E$1:E368)*(E369=E$1:E368)))))</f>
+        <v> </v>
+      </c>
+      <c r="L369" s="26"/>
     </row>
     <row r="370" spans="1:12">
       <c r="A370" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="B370" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C370" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="D370" s="27" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="E370" s="21">
         <f>IF(D370="?OLD","!!!","")</f>
@@ -14790,7 +14807,7 @@
     </row>
     <row r="371" spans="1:12">
       <c r="A371" s="20" t="s">
-        <v>326</v>
+        <v>126</v>
       </c>
       <c r="E371" s="21">
         <f>IF(D371="?OLD","!!!","")</f>
@@ -14823,82 +14840,25 @@
       <c r="L371" s="26"/>
     </row>
     <row r="372" spans="1:12">
-      <c r="A372" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="E372" s="21">
-        <f>IF(D372="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F372" s="22" t="str">
-        <f>IF(OR(E372="",E372="!!!"),"",IF(NOT(ISNA(VLOOKUP(E372,E$1:E371,1,FALSE()))),"OLD",IF(AND(E372&lt;&gt;"",E372&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G372" s="23" t="str">
-        <f>IF(OR(E372="",E372="!!!"),"",IF(OR(J372=0,AND(J372=1,K372=1),AND(J372=1,I372="SBJ"),AND(J372=1,I372=0)),"?IN_FOCUS",IF(J372&lt;=2,"?ACTIVATED",IF(J372&lt;&gt;"","?FAMILIAR",IF(F372="NEW",IF(ISNA(VLOOKUP(E372,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H372" s="24" t="str">
-        <f>IF(J372&lt;&gt;1,"",IF(I372="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I372" s="25" t="str">
-        <f>IF(OR(E372="",E372="!!!",F372="NEW"),"",INDEX(B371:B$2,-1+SUMPRODUCT(MAX(ROW(E371:E$2)*(E372=E371:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J372" s="25" t="str">
-        <f>IF(OR(E372="",E372="!!!",F372="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E372)*(E372=E$2:E372)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E371)*(E2=E$1:E371))))))</f>
-        <v> </v>
-      </c>
-      <c r="K372" s="25" t="str">
-        <f>IF(OR(E372="",E372="!!!",F372="NEW"),"",INDEX(J$1:J371,SUMPRODUCT(MAX(ROW(E$1:E371)*(E372=E$1:E371)))))</f>
-        <v> </v>
-      </c>
-      <c r="L372" s="26"/>
+      <c r="A372" s="20"/>
     </row>
     <row r="373" spans="1:12">
       <c r="A373" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="B373" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C373" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E373" s="21">
-        <f>IF(D373="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F373" s="22" t="str">
-        <f>IF(OR(E373="",E373="!!!"),"",IF(NOT(ISNA(VLOOKUP(E373,E$1:E372,1,FALSE()))),"OLD",IF(AND(E373&lt;&gt;"",E373&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G373" s="23" t="str">
-        <f>IF(OR(E373="",E373="!!!"),"",IF(OR(J373=0,AND(J373=1,K373=1),AND(J373=1,I373="SBJ"),AND(J373=1,I373=0)),"?IN_FOCUS",IF(J373&lt;=2,"?ACTIVATED",IF(J373&lt;&gt;"","?FAMILIAR",IF(F373="NEW",IF(ISNA(VLOOKUP(E373,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H373" s="24" t="str">
-        <f>IF(J373&lt;&gt;1,"",IF(I373="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I373" s="25" t="str">
-        <f>IF(OR(E373="",E373="!!!",F373="NEW"),"",INDEX(B372:B$2,-1+SUMPRODUCT(MAX(ROW(E372:E$2)*(E373=E372:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J373" s="25" t="str">
-        <f>IF(OR(E373="",E373="!!!",F373="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E373)*(E373=E$2:E373)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E372)*(E2=E$1:E372))))))</f>
-        <v> </v>
-      </c>
-      <c r="K373" s="25" t="str">
-        <f>IF(OR(E373="",E373="!!!",F373="NEW"),"",INDEX(J$1:J372,SUMPRODUCT(MAX(ROW(E$1:E372)*(E373=E$1:E372)))))</f>
-        <v> </v>
-      </c>
-      <c r="L373" s="26"/>
+        <v>332</v>
+      </c>
     </row>
     <row r="374" spans="1:12">
       <c r="A374" s="20" t="s">
-        <v>160</v>
+        <v>333</v>
+      </c>
+      <c r="B374" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C374" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D374" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E374" s="21">
         <f>IF(D374="?OLD","!!!","")</f>
@@ -14932,7 +14892,7 @@
     </row>
     <row r="375" spans="1:12">
       <c r="A375" s="20" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E375" s="21">
         <f>IF(D375="?OLD","!!!","")</f>
@@ -14966,16 +14926,7 @@
     </row>
     <row r="376" spans="1:12">
       <c r="A376" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="B376" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C376" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D376" s="27" t="s">
-        <v>105</v>
+        <v>335</v>
       </c>
       <c r="E376" s="21">
         <f>IF(D376="?OLD","!!!","")</f>
@@ -15009,7 +14960,13 @@
     </row>
     <row r="377" spans="1:12">
       <c r="A377" s="20" t="s">
-        <v>331</v>
+        <v>336</v>
+      </c>
+      <c r="B377" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C377" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="E377" s="21">
         <f>IF(D377="?OLD","!!!","")</f>
@@ -15043,13 +15000,7 @@
     </row>
     <row r="378" spans="1:12">
       <c r="A378" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="B378" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C378" s="27" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E378" s="21">
         <f>IF(D378="?OLD","!!!","")</f>
@@ -15083,7 +15034,7 @@
     </row>
     <row r="379" spans="1:12">
       <c r="A379" s="20" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E379" s="21">
         <f>IF(D379="?OLD","!!!","")</f>
@@ -15117,7 +15068,16 @@
     </row>
     <row r="380" spans="1:12">
       <c r="A380" s="20" t="s">
-        <v>334</v>
+        <v>338</v>
+      </c>
+      <c r="B380" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C380" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D380" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E380" s="21">
         <f>IF(D380="?OLD","!!!","")</f>
@@ -15151,7 +15111,7 @@
     </row>
     <row r="381" spans="1:12">
       <c r="A381" s="20" t="s">
-        <v>120</v>
+        <v>339</v>
       </c>
       <c r="E381" s="21">
         <f>IF(D381="?OLD","!!!","")</f>
@@ -15184,25 +15144,82 @@
       <c r="L381" s="26"/>
     </row>
     <row r="382" spans="1:12">
-      <c r="A382" s="20"/>
+      <c r="A382" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="B382" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C382" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E382" s="21">
+        <f>IF(D382="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F382" s="22" t="str">
+        <f>IF(OR(E382="",E382="!!!"),"",IF(NOT(ISNA(VLOOKUP(E382,E$1:E381,1,FALSE()))),"OLD",IF(AND(E382&lt;&gt;"",E382&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G382" s="23" t="str">
+        <f>IF(OR(E382="",E382="!!!"),"",IF(OR(J382=0,AND(J382=1,K382=1),AND(J382=1,I382="SBJ"),AND(J382=1,I382=0)),"?IN_FOCUS",IF(J382&lt;=2,"?ACTIVATED",IF(J382&lt;&gt;"","?FAMILIAR",IF(F382="NEW",IF(ISNA(VLOOKUP(E382,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H382" s="24" t="str">
+        <f>IF(J382&lt;&gt;1,"",IF(I382="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I382" s="25" t="str">
+        <f>IF(OR(E382="",E382="!!!",F382="NEW"),"",INDEX(B381:B$2,-1+SUMPRODUCT(MAX(ROW(E381:E$2)*(E382=E381:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J382" s="25" t="str">
+        <f>IF(OR(E382="",E382="!!!",F382="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E382)*(E382=E$2:E382)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E381)*(E2=E$1:E381))))))</f>
+        <v> </v>
+      </c>
+      <c r="K382" s="25" t="str">
+        <f>IF(OR(E382="",E382="!!!",F382="NEW"),"",INDEX(J$1:J381,SUMPRODUCT(MAX(ROW(E$1:E381)*(E382=E$1:E381)))))</f>
+        <v> </v>
+      </c>
+      <c r="L382" s="26"/>
     </row>
     <row r="383" spans="1:12">
       <c r="A383" s="20" t="s">
-        <v>335</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="E383" s="21">
+        <f>IF(D383="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F383" s="22" t="str">
+        <f>IF(OR(E383="",E383="!!!"),"",IF(NOT(ISNA(VLOOKUP(E383,E$1:E382,1,FALSE()))),"OLD",IF(AND(E383&lt;&gt;"",E383&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G383" s="23" t="str">
+        <f>IF(OR(E383="",E383="!!!"),"",IF(OR(J383=0,AND(J383=1,K383=1),AND(J383=1,I383="SBJ"),AND(J383=1,I383=0)),"?IN_FOCUS",IF(J383&lt;=2,"?ACTIVATED",IF(J383&lt;&gt;"","?FAMILIAR",IF(F383="NEW",IF(ISNA(VLOOKUP(E383,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H383" s="24" t="str">
+        <f>IF(J383&lt;&gt;1,"",IF(I383="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I383" s="25" t="str">
+        <f>IF(OR(E383="",E383="!!!",F383="NEW"),"",INDEX(B382:B$2,-1+SUMPRODUCT(MAX(ROW(E382:E$2)*(E383=E382:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J383" s="25" t="str">
+        <f>IF(OR(E383="",E383="!!!",F383="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E383)*(E383=E$2:E383)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E382)*(E2=E$1:E382))))))</f>
+        <v> </v>
+      </c>
+      <c r="K383" s="25" t="str">
+        <f>IF(OR(E383="",E383="!!!",F383="NEW"),"",INDEX(J$1:J382,SUMPRODUCT(MAX(ROW(E$1:E382)*(E383=E$1:E382)))))</f>
+        <v> </v>
+      </c>
+      <c r="L383" s="26"/>
     </row>
     <row r="384" spans="1:12">
       <c r="A384" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="B384" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C384" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="D384" s="27" t="s">
-        <v>105</v>
+        <v>342</v>
       </c>
       <c r="E384" s="21">
         <f>IF(D384="?OLD","!!!","")</f>
@@ -15236,7 +15253,7 @@
     </row>
     <row r="385" spans="1:12">
       <c r="A385" s="20" t="s">
-        <v>212</v>
+        <v>126</v>
       </c>
       <c r="E385" s="21">
         <f>IF(D385="?OLD","!!!","")</f>
@@ -15269,76 +15286,25 @@
       <c r="L385" s="26"/>
     </row>
     <row r="386" spans="1:12">
-      <c r="A386" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="E386" s="21">
-        <f>IF(D386="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F386" s="22" t="str">
-        <f>IF(OR(E386="",E386="!!!"),"",IF(NOT(ISNA(VLOOKUP(E386,E$1:E385,1,FALSE()))),"OLD",IF(AND(E386&lt;&gt;"",E386&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G386" s="23" t="str">
-        <f>IF(OR(E386="",E386="!!!"),"",IF(OR(J386=0,AND(J386=1,K386=1),AND(J386=1,I386="SBJ"),AND(J386=1,I386=0)),"?IN_FOCUS",IF(J386&lt;=2,"?ACTIVATED",IF(J386&lt;&gt;"","?FAMILIAR",IF(F386="NEW",IF(ISNA(VLOOKUP(E386,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H386" s="24" t="str">
-        <f>IF(J386&lt;&gt;1,"",IF(I386="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I386" s="25" t="str">
-        <f>IF(OR(E386="",E386="!!!",F386="NEW"),"",INDEX(B385:B$2,-1+SUMPRODUCT(MAX(ROW(E385:E$2)*(E386=E385:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J386" s="25" t="str">
-        <f>IF(OR(E386="",E386="!!!",F386="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E386)*(E386=E$2:E386)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E385)*(E2=E$1:E385))))))</f>
-        <v> </v>
-      </c>
-      <c r="K386" s="25" t="str">
-        <f>IF(OR(E386="",E386="!!!",F386="NEW"),"",INDEX(J$1:J385,SUMPRODUCT(MAX(ROW(E$1:E385)*(E386=E$1:E385)))))</f>
-        <v> </v>
-      </c>
-      <c r="L386" s="26"/>
+      <c r="A386" s="20"/>
     </row>
     <row r="387" spans="1:12">
       <c r="A387" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="E387" s="21">
-        <f>IF(D387="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F387" s="22" t="str">
-        <f>IF(OR(E387="",E387="!!!"),"",IF(NOT(ISNA(VLOOKUP(E387,E$1:E386,1,FALSE()))),"OLD",IF(AND(E387&lt;&gt;"",E387&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G387" s="23" t="str">
-        <f>IF(OR(E387="",E387="!!!"),"",IF(OR(J387=0,AND(J387=1,K387=1),AND(J387=1,I387="SBJ"),AND(J387=1,I387=0)),"?IN_FOCUS",IF(J387&lt;=2,"?ACTIVATED",IF(J387&lt;&gt;"","?FAMILIAR",IF(F387="NEW",IF(ISNA(VLOOKUP(E387,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H387" s="24" t="str">
-        <f>IF(J387&lt;&gt;1,"",IF(I387="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I387" s="25" t="str">
-        <f>IF(OR(E387="",E387="!!!",F387="NEW"),"",INDEX(B386:B$2,-1+SUMPRODUCT(MAX(ROW(E386:E$2)*(E387=E386:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J387" s="25" t="str">
-        <f>IF(OR(E387="",E387="!!!",F387="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E387)*(E387=E$2:E387)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E386)*(E2=E$1:E386))))))</f>
-        <v> </v>
-      </c>
-      <c r="K387" s="25" t="str">
-        <f>IF(OR(E387="",E387="!!!",F387="NEW"),"",INDEX(J$1:J386,SUMPRODUCT(MAX(ROW(E$1:E386)*(E387=E$1:E386)))))</f>
-        <v> </v>
-      </c>
-      <c r="L387" s="26"/>
+        <v>343</v>
+      </c>
     </row>
     <row r="388" spans="1:12">
       <c r="A388" s="20" t="s">
-        <v>181</v>
+        <v>333</v>
+      </c>
+      <c r="B388" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C388" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D388" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E388" s="21">
         <f>IF(D388="?OLD","!!!","")</f>
@@ -15372,7 +15338,7 @@
     </row>
     <row r="389" spans="1:12">
       <c r="A389" s="20" t="s">
-        <v>337</v>
+        <v>220</v>
       </c>
       <c r="E389" s="21">
         <f>IF(D389="?OLD","!!!","")</f>
@@ -15406,7 +15372,7 @@
     </row>
     <row r="390" spans="1:12">
       <c r="A390" s="20" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="E390" s="21">
         <f>IF(D390="?OLD","!!!","")</f>
@@ -15440,7 +15406,7 @@
     </row>
     <row r="391" spans="1:12">
       <c r="A391" s="20" t="s">
-        <v>255</v>
+        <v>344</v>
       </c>
       <c r="E391" s="21">
         <f>IF(D391="?OLD","!!!","")</f>
@@ -15474,13 +15440,7 @@
     </row>
     <row r="392" spans="1:12">
       <c r="A392" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="B392" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C392" s="27" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="E392" s="21">
         <f>IF(D392="?OLD","!!!","")</f>
@@ -15514,7 +15474,7 @@
     </row>
     <row r="393" spans="1:12">
       <c r="A393" s="20" t="s">
-        <v>120</v>
+        <v>345</v>
       </c>
       <c r="E393" s="21">
         <f>IF(D393="?OLD","!!!","")</f>
@@ -15547,22 +15507,82 @@
       <c r="L393" s="26"/>
     </row>
     <row r="394" spans="1:12">
-      <c r="A394" s="20"/>
+      <c r="A394" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="E394" s="21">
+        <f>IF(D394="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F394" s="22" t="str">
+        <f>IF(OR(E394="",E394="!!!"),"",IF(NOT(ISNA(VLOOKUP(E394,E$1:E393,1,FALSE()))),"OLD",IF(AND(E394&lt;&gt;"",E394&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G394" s="23" t="str">
+        <f>IF(OR(E394="",E394="!!!"),"",IF(OR(J394=0,AND(J394=1,K394=1),AND(J394=1,I394="SBJ"),AND(J394=1,I394=0)),"?IN_FOCUS",IF(J394&lt;=2,"?ACTIVATED",IF(J394&lt;&gt;"","?FAMILIAR",IF(F394="NEW",IF(ISNA(VLOOKUP(E394,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H394" s="24" t="str">
+        <f>IF(J394&lt;&gt;1,"",IF(I394="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I394" s="25" t="str">
+        <f>IF(OR(E394="",E394="!!!",F394="NEW"),"",INDEX(B393:B$2,-1+SUMPRODUCT(MAX(ROW(E393:E$2)*(E394=E393:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J394" s="25" t="str">
+        <f>IF(OR(E394="",E394="!!!",F394="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E394)*(E394=E$2:E394)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E393)*(E2=E$1:E393))))))</f>
+        <v> </v>
+      </c>
+      <c r="K394" s="25" t="str">
+        <f>IF(OR(E394="",E394="!!!",F394="NEW"),"",INDEX(J$1:J393,SUMPRODUCT(MAX(ROW(E$1:E393)*(E394=E$1:E393)))))</f>
+        <v> </v>
+      </c>
+      <c r="L394" s="26"/>
     </row>
     <row r="395" spans="1:12">
       <c r="A395" s="20" t="s">
-        <v>339</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="E395" s="21">
+        <f>IF(D395="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F395" s="22" t="str">
+        <f>IF(OR(E395="",E395="!!!"),"",IF(NOT(ISNA(VLOOKUP(E395,E$1:E394,1,FALSE()))),"OLD",IF(AND(E395&lt;&gt;"",E395&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G395" s="23" t="str">
+        <f>IF(OR(E395="",E395="!!!"),"",IF(OR(J395=0,AND(J395=1,K395=1),AND(J395=1,I395="SBJ"),AND(J395=1,I395=0)),"?IN_FOCUS",IF(J395&lt;=2,"?ACTIVATED",IF(J395&lt;&gt;"","?FAMILIAR",IF(F395="NEW",IF(ISNA(VLOOKUP(E395,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H395" s="24" t="str">
+        <f>IF(J395&lt;&gt;1,"",IF(I395="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I395" s="25" t="str">
+        <f>IF(OR(E395="",E395="!!!",F395="NEW"),"",INDEX(B394:B$2,-1+SUMPRODUCT(MAX(ROW(E394:E$2)*(E395=E394:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J395" s="25" t="str">
+        <f>IF(OR(E395="",E395="!!!",F395="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E395)*(E395=E$2:E395)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E394)*(E2=E$1:E394))))))</f>
+        <v> </v>
+      </c>
+      <c r="K395" s="25" t="str">
+        <f>IF(OR(E395="",E395="!!!",F395="NEW"),"",INDEX(J$1:J394,SUMPRODUCT(MAX(ROW(E$1:E394)*(E395=E$1:E394)))))</f>
+        <v> </v>
+      </c>
+      <c r="L395" s="26"/>
     </row>
     <row r="396" spans="1:12">
       <c r="A396" s="20" t="s">
-        <v>340</v>
+        <v>264</v>
       </c>
       <c r="B396" s="27" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C396" s="27" t="s">
-        <v>110</v>
+        <v>218</v>
       </c>
       <c r="E396" s="21">
         <f>IF(D396="?OLD","!!!","")</f>
@@ -15596,7 +15616,7 @@
     </row>
     <row r="397" spans="1:12">
       <c r="A397" s="20" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="E397" s="21">
         <f>IF(D397="?OLD","!!!","")</f>
@@ -15629,85 +15649,22 @@
       <c r="L397" s="26"/>
     </row>
     <row r="398" spans="1:12">
-      <c r="A398" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="E398" s="21">
-        <f>IF(D398="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F398" s="22" t="str">
-        <f>IF(OR(E398="",E398="!!!"),"",IF(NOT(ISNA(VLOOKUP(E398,E$1:E397,1,FALSE()))),"OLD",IF(AND(E398&lt;&gt;"",E398&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G398" s="23" t="str">
-        <f>IF(OR(E398="",E398="!!!"),"",IF(OR(J398=0,AND(J398=1,K398=1),AND(J398=1,I398="SBJ"),AND(J398=1,I398=0)),"?IN_FOCUS",IF(J398&lt;=2,"?ACTIVATED",IF(J398&lt;&gt;"","?FAMILIAR",IF(F398="NEW",IF(ISNA(VLOOKUP(E398,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H398" s="24" t="str">
-        <f>IF(J398&lt;&gt;1,"",IF(I398="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I398" s="25" t="str">
-        <f>IF(OR(E398="",E398="!!!",F398="NEW"),"",INDEX(B397:B$2,-1+SUMPRODUCT(MAX(ROW(E397:E$2)*(E398=E397:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J398" s="25" t="str">
-        <f>IF(OR(E398="",E398="!!!",F398="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E398)*(E398=E$2:E398)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E397)*(E2=E$1:E397))))))</f>
-        <v> </v>
-      </c>
-      <c r="K398" s="25" t="str">
-        <f>IF(OR(E398="",E398="!!!",F398="NEW"),"",INDEX(J$1:J397,SUMPRODUCT(MAX(ROW(E$1:E397)*(E398=E$1:E397)))))</f>
-        <v> </v>
-      </c>
-      <c r="L398" s="26"/>
+      <c r="A398" s="20"/>
     </row>
     <row r="399" spans="1:12">
       <c r="A399" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E399" s="21">
-        <f>IF(D399="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F399" s="22" t="str">
-        <f>IF(OR(E399="",E399="!!!"),"",IF(NOT(ISNA(VLOOKUP(E399,E$1:E398,1,FALSE()))),"OLD",IF(AND(E399&lt;&gt;"",E399&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G399" s="23" t="str">
-        <f>IF(OR(E399="",E399="!!!"),"",IF(OR(J399=0,AND(J399=1,K399=1),AND(J399=1,I399="SBJ"),AND(J399=1,I399=0)),"?IN_FOCUS",IF(J399&lt;=2,"?ACTIVATED",IF(J399&lt;&gt;"","?FAMILIAR",IF(F399="NEW",IF(ISNA(VLOOKUP(E399,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H399" s="24" t="str">
-        <f>IF(J399&lt;&gt;1,"",IF(I399="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I399" s="25" t="str">
-        <f>IF(OR(E399="",E399="!!!",F399="NEW"),"",INDEX(B398:B$2,-1+SUMPRODUCT(MAX(ROW(E398:E$2)*(E399=E398:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J399" s="25" t="str">
-        <f>IF(OR(E399="",E399="!!!",F399="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E399)*(E399=E$2:E399)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E398)*(E2=E$1:E398))))))</f>
-        <v> </v>
-      </c>
-      <c r="K399" s="25" t="str">
-        <f>IF(OR(E399="",E399="!!!",F399="NEW"),"",INDEX(J$1:J398,SUMPRODUCT(MAX(ROW(E$1:E398)*(E399=E$1:E398)))))</f>
-        <v> </v>
-      </c>
-      <c r="L399" s="26"/>
+        <v>347</v>
+      </c>
     </row>
     <row r="400" spans="1:12">
       <c r="A400" s="20" t="s">
-        <v>141</v>
+        <v>348</v>
       </c>
       <c r="B400" s="27" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="C400" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D400" s="27" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E400" s="21">
         <f>IF(D400="?OLD","!!!","")</f>
@@ -15741,7 +15698,7 @@
     </row>
     <row r="401" spans="1:12">
       <c r="A401" s="20" t="s">
-        <v>342</v>
+        <v>151</v>
       </c>
       <c r="E401" s="21">
         <f>IF(D401="?OLD","!!!","")</f>
@@ -15775,13 +15732,7 @@
     </row>
     <row r="402" spans="1:12">
       <c r="A402" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="B402" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C402" s="27" t="s">
-        <v>159</v>
+        <v>349</v>
       </c>
       <c r="E402" s="21">
         <f>IF(D402="?OLD","!!!","")</f>
@@ -15815,7 +15766,7 @@
     </row>
     <row r="403" spans="1:12">
       <c r="A403" s="20" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="E403" s="21">
         <f>IF(D403="?OLD","!!!","")</f>
@@ -15849,7 +15800,16 @@
     </row>
     <row r="404" spans="1:12">
       <c r="A404" s="20" t="s">
-        <v>151</v>
+        <v>146</v>
+      </c>
+      <c r="B404" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C404" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D404" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E404" s="21">
         <f>IF(D404="?OLD","!!!","")</f>
@@ -15883,7 +15843,7 @@
     </row>
     <row r="405" spans="1:12">
       <c r="A405" s="20" t="s">
-        <v>146</v>
+        <v>350</v>
       </c>
       <c r="E405" s="21">
         <f>IF(D405="?OLD","!!!","")</f>
@@ -15917,7 +15877,13 @@
     </row>
     <row r="406" spans="1:12">
       <c r="A406" s="20" t="s">
-        <v>343</v>
+        <v>187</v>
+      </c>
+      <c r="B406" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C406" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E406" s="21">
         <f>IF(D406="?OLD","!!!","")</f>
@@ -15951,7 +15917,7 @@
     </row>
     <row r="407" spans="1:12">
       <c r="A407" s="20" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="E407" s="21">
         <f>IF(D407="?OLD","!!!","")</f>
@@ -15985,7 +15951,7 @@
     </row>
     <row r="408" spans="1:12">
       <c r="A408" s="20" t="s">
-        <v>344</v>
+        <v>157</v>
       </c>
       <c r="E408" s="21">
         <f>IF(D408="?OLD","!!!","")</f>
@@ -16019,13 +15985,7 @@
     </row>
     <row r="409" spans="1:12">
       <c r="A409" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="B409" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C409" s="27" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E409" s="21">
         <f>IF(D409="?OLD","!!!","")</f>
@@ -16059,7 +16019,7 @@
     </row>
     <row r="410" spans="1:12">
       <c r="A410" s="20" t="s">
-        <v>182</v>
+        <v>351</v>
       </c>
       <c r="E410" s="21">
         <f>IF(D410="?OLD","!!!","")</f>
@@ -16093,7 +16053,7 @@
     </row>
     <row r="411" spans="1:12">
       <c r="A411" s="20" t="s">
-        <v>181</v>
+        <v>126</v>
       </c>
       <c r="E411" s="21">
         <f>IF(D411="?OLD","!!!","")</f>
@@ -16127,7 +16087,7 @@
     </row>
     <row r="412" spans="1:12">
       <c r="A412" s="20" t="s">
-        <v>225</v>
+        <v>352</v>
       </c>
       <c r="E412" s="21">
         <f>IF(D412="?OLD","!!!","")</f>
@@ -16161,7 +16121,13 @@
     </row>
     <row r="413" spans="1:12">
       <c r="A413" s="20" t="s">
-        <v>213</v>
+        <v>192</v>
+      </c>
+      <c r="B413" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C413" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E413" s="21">
         <f>IF(D413="?OLD","!!!","")</f>
@@ -16195,13 +16161,7 @@
     </row>
     <row r="414" spans="1:12">
       <c r="A414" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="B414" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C414" s="27" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="E414" s="21">
         <f>IF(D414="?OLD","!!!","")</f>
@@ -16235,7 +16195,7 @@
     </row>
     <row r="415" spans="1:12">
       <c r="A415" s="20" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="E415" s="21">
         <f>IF(D415="?OLD","!!!","")</f>
@@ -16269,7 +16229,7 @@
     </row>
     <row r="416" spans="1:12">
       <c r="A416" s="20" t="s">
-        <v>343</v>
+        <v>233</v>
       </c>
       <c r="E416" s="21">
         <f>IF(D416="?OLD","!!!","")</f>
@@ -16303,7 +16263,7 @@
     </row>
     <row r="417" spans="1:12">
       <c r="A417" s="20" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="E417" s="21">
         <f>IF(D417="?OLD","!!!","")</f>
@@ -16337,7 +16297,13 @@
     </row>
     <row r="418" spans="1:12">
       <c r="A418" s="20" t="s">
-        <v>21</v>
+        <v>353</v>
+      </c>
+      <c r="B418" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C418" s="27" t="s">
+        <v>218</v>
       </c>
       <c r="E418" s="21">
         <f>IF(D418="?OLD","!!!","")</f>
@@ -16371,13 +16337,7 @@
     </row>
     <row r="419" spans="1:12">
       <c r="A419" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="B419" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C419" s="27" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E419" s="21">
         <f>IF(D419="?OLD","!!!","")</f>
@@ -16411,7 +16371,7 @@
     </row>
     <row r="420" spans="1:12">
       <c r="A420" s="20" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E420" s="21">
         <f>IF(D420="?OLD","!!!","")</f>
@@ -16445,7 +16405,7 @@
     </row>
     <row r="421" spans="1:12">
       <c r="A421" s="20" t="s">
-        <v>347</v>
+        <v>126</v>
       </c>
       <c r="E421" s="21">
         <f>IF(D421="?OLD","!!!","")</f>
@@ -16479,7 +16439,7 @@
     </row>
     <row r="422" spans="1:12">
       <c r="A422" s="20" t="s">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="E422" s="21">
         <f>IF(D422="?OLD","!!!","")</f>
@@ -16513,7 +16473,13 @@
     </row>
     <row r="423" spans="1:12">
       <c r="A423" s="20" t="s">
-        <v>131</v>
+        <v>274</v>
+      </c>
+      <c r="B423" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C423" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E423" s="21">
         <f>IF(D423="?OLD","!!!","")</f>
@@ -16547,7 +16513,7 @@
     </row>
     <row r="424" spans="1:12">
       <c r="A424" s="20" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E424" s="21">
         <f>IF(D424="?OLD","!!!","")</f>
@@ -16581,7 +16547,7 @@
     </row>
     <row r="425" spans="1:12">
       <c r="A425" s="20" t="s">
-        <v>120</v>
+        <v>355</v>
       </c>
       <c r="E425" s="21">
         <f>IF(D425="?OLD","!!!","")</f>
@@ -16614,22 +16580,76 @@
       <c r="L425" s="26"/>
     </row>
     <row r="426" spans="1:12">
-      <c r="A426" s="20"/>
+      <c r="A426" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="E426" s="21">
+        <f>IF(D426="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F426" s="22" t="str">
+        <f>IF(OR(E426="",E426="!!!"),"",IF(NOT(ISNA(VLOOKUP(E426,E$1:E425,1,FALSE()))),"OLD",IF(AND(E426&lt;&gt;"",E426&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G426" s="23" t="str">
+        <f>IF(OR(E426="",E426="!!!"),"",IF(OR(J426=0,AND(J426=1,K426=1),AND(J426=1,I426="SBJ"),AND(J426=1,I426=0)),"?IN_FOCUS",IF(J426&lt;=2,"?ACTIVATED",IF(J426&lt;&gt;"","?FAMILIAR",IF(F426="NEW",IF(ISNA(VLOOKUP(E426,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H426" s="24" t="str">
+        <f>IF(J426&lt;&gt;1,"",IF(I426="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I426" s="25" t="str">
+        <f>IF(OR(E426="",E426="!!!",F426="NEW"),"",INDEX(B425:B$2,-1+SUMPRODUCT(MAX(ROW(E425:E$2)*(E426=E425:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J426" s="25" t="str">
+        <f>IF(OR(E426="",E426="!!!",F426="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E426)*(E426=E$2:E426)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E425)*(E2=E$1:E425))))))</f>
+        <v> </v>
+      </c>
+      <c r="K426" s="25" t="str">
+        <f>IF(OR(E426="",E426="!!!",F426="NEW"),"",INDEX(J$1:J425,SUMPRODUCT(MAX(ROW(E$1:E425)*(E426=E$1:E425)))))</f>
+        <v> </v>
+      </c>
+      <c r="L426" s="26"/>
     </row>
     <row r="427" spans="1:12">
       <c r="A427" s="20" t="s">
-        <v>350</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="E427" s="21">
+        <f>IF(D427="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F427" s="22" t="str">
+        <f>IF(OR(E427="",E427="!!!"),"",IF(NOT(ISNA(VLOOKUP(E427,E$1:E426,1,FALSE()))),"OLD",IF(AND(E427&lt;&gt;"",E427&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G427" s="23" t="str">
+        <f>IF(OR(E427="",E427="!!!"),"",IF(OR(J427=0,AND(J427=1,K427=1),AND(J427=1,I427="SBJ"),AND(J427=1,I427=0)),"?IN_FOCUS",IF(J427&lt;=2,"?ACTIVATED",IF(J427&lt;&gt;"","?FAMILIAR",IF(F427="NEW",IF(ISNA(VLOOKUP(E427,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H427" s="24" t="str">
+        <f>IF(J427&lt;&gt;1,"",IF(I427="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I427" s="25" t="str">
+        <f>IF(OR(E427="",E427="!!!",F427="NEW"),"",INDEX(B426:B$2,-1+SUMPRODUCT(MAX(ROW(E426:E$2)*(E427=E426:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J427" s="25" t="str">
+        <f>IF(OR(E427="",E427="!!!",F427="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E427)*(E427=E$2:E427)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E426)*(E2=E$1:E426))))))</f>
+        <v> </v>
+      </c>
+      <c r="K427" s="25" t="str">
+        <f>IF(OR(E427="",E427="!!!",F427="NEW"),"",INDEX(J$1:J426,SUMPRODUCT(MAX(ROW(E$1:E426)*(E427=E$1:E426)))))</f>
+        <v> </v>
+      </c>
+      <c r="L427" s="26"/>
     </row>
     <row r="428" spans="1:12">
       <c r="A428" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="B428" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C428" s="27" t="s">
-        <v>110</v>
+        <v>357</v>
       </c>
       <c r="E428" s="21">
         <f>IF(D428="?OLD","!!!","")</f>
@@ -16663,7 +16683,7 @@
     </row>
     <row r="429" spans="1:12">
       <c r="A429" s="20" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="E429" s="21">
         <f>IF(D429="?OLD","!!!","")</f>
@@ -16696,85 +16716,22 @@
       <c r="L429" s="26"/>
     </row>
     <row r="430" spans="1:12">
-      <c r="A430" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="E430" s="21">
-        <f>IF(D430="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F430" s="22" t="str">
-        <f>IF(OR(E430="",E430="!!!"),"",IF(NOT(ISNA(VLOOKUP(E430,E$1:E429,1,FALSE()))),"OLD",IF(AND(E430&lt;&gt;"",E430&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G430" s="23" t="str">
-        <f>IF(OR(E430="",E430="!!!"),"",IF(OR(J430=0,AND(J430=1,K430=1),AND(J430=1,I430="SBJ"),AND(J430=1,I430=0)),"?IN_FOCUS",IF(J430&lt;=2,"?ACTIVATED",IF(J430&lt;&gt;"","?FAMILIAR",IF(F430="NEW",IF(ISNA(VLOOKUP(E430,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H430" s="24" t="str">
-        <f>IF(J430&lt;&gt;1,"",IF(I430="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I430" s="25" t="str">
-        <f>IF(OR(E430="",E430="!!!",F430="NEW"),"",INDEX(B429:B$2,-1+SUMPRODUCT(MAX(ROW(E429:E$2)*(E430=E429:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J430" s="25" t="str">
-        <f>IF(OR(E430="",E430="!!!",F430="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E430)*(E430=E$2:E430)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E429)*(E2=E$1:E429))))))</f>
-        <v> </v>
-      </c>
-      <c r="K430" s="25" t="str">
-        <f>IF(OR(E430="",E430="!!!",F430="NEW"),"",INDEX(J$1:J429,SUMPRODUCT(MAX(ROW(E$1:E429)*(E430=E$1:E429)))))</f>
-        <v> </v>
-      </c>
-      <c r="L430" s="26"/>
+      <c r="A430" s="20"/>
     </row>
     <row r="431" spans="1:12">
       <c r="A431" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="E431" s="21">
-        <f>IF(D431="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F431" s="22" t="str">
-        <f>IF(OR(E431="",E431="!!!"),"",IF(NOT(ISNA(VLOOKUP(E431,E$1:E430,1,FALSE()))),"OLD",IF(AND(E431&lt;&gt;"",E431&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G431" s="23" t="str">
-        <f>IF(OR(E431="",E431="!!!"),"",IF(OR(J431=0,AND(J431=1,K431=1),AND(J431=1,I431="SBJ"),AND(J431=1,I431=0)),"?IN_FOCUS",IF(J431&lt;=2,"?ACTIVATED",IF(J431&lt;&gt;"","?FAMILIAR",IF(F431="NEW",IF(ISNA(VLOOKUP(E431,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H431" s="24" t="str">
-        <f>IF(J431&lt;&gt;1,"",IF(I431="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I431" s="25" t="str">
-        <f>IF(OR(E431="",E431="!!!",F431="NEW"),"",INDEX(B430:B$2,-1+SUMPRODUCT(MAX(ROW(E430:E$2)*(E431=E430:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J431" s="25" t="str">
-        <f>IF(OR(E431="",E431="!!!",F431="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E431)*(E431=E$2:E431)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E430)*(E2=E$1:E430))))))</f>
-        <v> </v>
-      </c>
-      <c r="K431" s="25" t="str">
-        <f>IF(OR(E431="",E431="!!!",F431="NEW"),"",INDEX(J$1:J430,SUMPRODUCT(MAX(ROW(E$1:E430)*(E431=E$1:E430)))))</f>
-        <v> </v>
-      </c>
-      <c r="L431" s="26"/>
+        <v>358</v>
+      </c>
     </row>
     <row r="432" spans="1:12">
       <c r="A432" s="20" t="s">
-        <v>259</v>
+        <v>359</v>
       </c>
       <c r="B432" s="27" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C432" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D432" s="27" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E432" s="21">
         <f>IF(D432="?OLD","!!!","")</f>
@@ -16808,7 +16765,7 @@
     </row>
     <row r="433" spans="1:12">
       <c r="A433" s="20" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E433" s="21">
         <f>IF(D433="?OLD","!!!","")</f>
@@ -16842,7 +16799,7 @@
     </row>
     <row r="434" spans="1:12">
       <c r="A434" s="20" t="s">
-        <v>216</v>
+        <v>349</v>
       </c>
       <c r="E434" s="21">
         <f>IF(D434="?OLD","!!!","")</f>
@@ -16876,7 +16833,7 @@
     </row>
     <row r="435" spans="1:12">
       <c r="A435" s="20" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E435" s="21">
         <f>IF(D435="?OLD","!!!","")</f>
@@ -16910,7 +16867,16 @@
     </row>
     <row r="436" spans="1:12">
       <c r="A436" s="20" t="s">
-        <v>135</v>
+        <v>267</v>
+      </c>
+      <c r="B436" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C436" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D436" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E436" s="21">
         <f>IF(D436="?OLD","!!!","")</f>
@@ -16944,16 +16910,7 @@
     </row>
     <row r="437" spans="1:12">
       <c r="A437" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="B437" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C437" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D437" s="27" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="E437" s="21">
         <f>IF(D437="?OLD","!!!","")</f>
@@ -16987,7 +16944,7 @@
     </row>
     <row r="438" spans="1:12">
       <c r="A438" s="20" t="s">
-        <v>353</v>
+        <v>224</v>
       </c>
       <c r="E438" s="21">
         <f>IF(D438="?OLD","!!!","")</f>
@@ -17021,7 +16978,7 @@
     </row>
     <row r="439" spans="1:12">
       <c r="A439" s="20" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E439" s="21">
         <f>IF(D439="?OLD","!!!","")</f>
@@ -17055,7 +17012,7 @@
     </row>
     <row r="440" spans="1:12">
       <c r="A440" s="20" t="s">
-        <v>354</v>
+        <v>140</v>
       </c>
       <c r="E440" s="21">
         <f>IF(D440="?OLD","!!!","")</f>
@@ -17089,7 +17046,16 @@
     </row>
     <row r="441" spans="1:12">
       <c r="A441" s="20" t="s">
-        <v>355</v>
+        <v>360</v>
+      </c>
+      <c r="B441" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="C441" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D441" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E441" s="21">
         <f>IF(D441="?OLD","!!!","")</f>
@@ -17123,7 +17089,7 @@
     </row>
     <row r="442" spans="1:12">
       <c r="A442" s="20" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="E442" s="21">
         <f>IF(D442="?OLD","!!!","")</f>
@@ -17157,7 +17123,7 @@
     </row>
     <row r="443" spans="1:12">
       <c r="A443" s="20" t="s">
-        <v>216</v>
+        <v>151</v>
       </c>
       <c r="E443" s="21">
         <f>IF(D443="?OLD","!!!","")</f>
@@ -17191,13 +17157,7 @@
     </row>
     <row r="444" spans="1:12">
       <c r="A444" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="B444" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C444" s="27" t="s">
-        <v>168</v>
+        <v>362</v>
       </c>
       <c r="E444" s="21">
         <f>IF(D444="?OLD","!!!","")</f>
@@ -17231,13 +17191,7 @@
     </row>
     <row r="445" spans="1:12">
       <c r="A445" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="B445" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C445" s="27" t="s">
-        <v>110</v>
+        <v>363</v>
       </c>
       <c r="E445" s="21">
         <f>IF(D445="?OLD","!!!","")</f>
@@ -17271,7 +17225,7 @@
     </row>
     <row r="446" spans="1:12">
       <c r="A446" s="20" t="s">
-        <v>358</v>
+        <v>12</v>
       </c>
       <c r="E446" s="21">
         <f>IF(D446="?OLD","!!!","")</f>
@@ -17305,16 +17259,7 @@
     </row>
     <row r="447" spans="1:12">
       <c r="A447" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="B447" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C447" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="D447" s="27" t="s">
-        <v>105</v>
+        <v>224</v>
       </c>
       <c r="E447" s="21">
         <f>IF(D447="?OLD","!!!","")</f>
@@ -17348,7 +17293,13 @@
     </row>
     <row r="448" spans="1:12">
       <c r="A448" s="20" t="s">
-        <v>360</v>
+        <v>364</v>
+      </c>
+      <c r="B448" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C448" s="27" t="s">
+        <v>176</v>
       </c>
       <c r="E448" s="21">
         <f>IF(D448="?OLD","!!!","")</f>
@@ -17382,13 +17333,13 @@
     </row>
     <row r="449" spans="1:12">
       <c r="A449" s="20" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B449" s="27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C449" s="27" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="E449" s="21">
         <f>IF(D449="?OLD","!!!","")</f>
@@ -17422,13 +17373,7 @@
     </row>
     <row r="450" spans="1:12">
       <c r="A450" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="B450" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="C450" s="27" t="s">
-        <v>159</v>
+        <v>366</v>
       </c>
       <c r="E450" s="21">
         <f>IF(D450="?OLD","!!!","")</f>
@@ -17462,7 +17407,16 @@
     </row>
     <row r="451" spans="1:12">
       <c r="A451" s="20" t="s">
-        <v>120</v>
+        <v>367</v>
+      </c>
+      <c r="B451" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C451" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D451" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E451" s="21">
         <f>IF(D451="?OLD","!!!","")</f>
@@ -17495,16 +17449,88 @@
       <c r="L451" s="26"/>
     </row>
     <row r="452" spans="1:12">
-      <c r="A452" s="20"/>
+      <c r="A452" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="E452" s="21">
+        <f>IF(D452="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F452" s="22" t="str">
+        <f>IF(OR(E452="",E452="!!!"),"",IF(NOT(ISNA(VLOOKUP(E452,E$1:E451,1,FALSE()))),"OLD",IF(AND(E452&lt;&gt;"",E452&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G452" s="23" t="str">
+        <f>IF(OR(E452="",E452="!!!"),"",IF(OR(J452=0,AND(J452=1,K452=1),AND(J452=1,I452="SBJ"),AND(J452=1,I452=0)),"?IN_FOCUS",IF(J452&lt;=2,"?ACTIVATED",IF(J452&lt;&gt;"","?FAMILIAR",IF(F452="NEW",IF(ISNA(VLOOKUP(E452,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H452" s="24" t="str">
+        <f>IF(J452&lt;&gt;1,"",IF(I452="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I452" s="25" t="str">
+        <f>IF(OR(E452="",E452="!!!",F452="NEW"),"",INDEX(B451:B$2,-1+SUMPRODUCT(MAX(ROW(E451:E$2)*(E452=E451:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J452" s="25" t="str">
+        <f>IF(OR(E452="",E452="!!!",F452="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E452)*(E452=E$2:E452)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E451)*(E2=E$1:E451))))))</f>
+        <v> </v>
+      </c>
+      <c r="K452" s="25" t="str">
+        <f>IF(OR(E452="",E452="!!!",F452="NEW"),"",INDEX(J$1:J451,SUMPRODUCT(MAX(ROW(E$1:E451)*(E452=E$1:E451)))))</f>
+        <v> </v>
+      </c>
+      <c r="L452" s="26"/>
     </row>
     <row r="453" spans="1:12">
       <c r="A453" s="20" t="s">
-        <v>362</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="B453" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C453" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E453" s="21">
+        <f>IF(D453="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F453" s="22" t="str">
+        <f>IF(OR(E453="",E453="!!!"),"",IF(NOT(ISNA(VLOOKUP(E453,E$1:E452,1,FALSE()))),"OLD",IF(AND(E453&lt;&gt;"",E453&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G453" s="23" t="str">
+        <f>IF(OR(E453="",E453="!!!"),"",IF(OR(J453=0,AND(J453=1,K453=1),AND(J453=1,I453="SBJ"),AND(J453=1,I453=0)),"?IN_FOCUS",IF(J453&lt;=2,"?ACTIVATED",IF(J453&lt;&gt;"","?FAMILIAR",IF(F453="NEW",IF(ISNA(VLOOKUP(E453,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H453" s="24" t="str">
+        <f>IF(J453&lt;&gt;1,"",IF(I453="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I453" s="25" t="str">
+        <f>IF(OR(E453="",E453="!!!",F453="NEW"),"",INDEX(B452:B$2,-1+SUMPRODUCT(MAX(ROW(E452:E$2)*(E453=E452:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J453" s="25" t="str">
+        <f>IF(OR(E453="",E453="!!!",F453="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E453)*(E453=E$2:E453)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E452)*(E2=E$1:E452))))))</f>
+        <v> </v>
+      </c>
+      <c r="K453" s="25" t="str">
+        <f>IF(OR(E453="",E453="!!!",F453="NEW"),"",INDEX(J$1:J452,SUMPRODUCT(MAX(ROW(E$1:E452)*(E453=E$1:E452)))))</f>
+        <v> </v>
+      </c>
+      <c r="L453" s="26"/>
     </row>
     <row r="454" spans="1:12">
       <c r="A454" s="20" t="s">
-        <v>363</v>
+        <v>340</v>
+      </c>
+      <c r="B454" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="C454" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="E454" s="21">
         <f>IF(D454="?OLD","!!!","")</f>
@@ -17538,7 +17564,7 @@
     </row>
     <row r="455" spans="1:12">
       <c r="A455" s="20" t="s">
-        <v>364</v>
+        <v>126</v>
       </c>
       <c r="E455" s="21">
         <f>IF(D455="?OLD","!!!","")</f>
@@ -17571,82 +17597,16 @@
       <c r="L455" s="26"/>
     </row>
     <row r="456" spans="1:12">
-      <c r="A456" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="B456" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C456" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="E456" s="21">
-        <f>IF(D456="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F456" s="22" t="str">
-        <f>IF(OR(E456="",E456="!!!"),"",IF(NOT(ISNA(VLOOKUP(E456,E$1:E455,1,FALSE()))),"OLD",IF(AND(E456&lt;&gt;"",E456&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G456" s="23" t="str">
-        <f>IF(OR(E456="",E456="!!!"),"",IF(OR(J456=0,AND(J456=1,K456=1),AND(J456=1,I456="SBJ"),AND(J456=1,I456=0)),"?IN_FOCUS",IF(J456&lt;=2,"?ACTIVATED",IF(J456&lt;&gt;"","?FAMILIAR",IF(F456="NEW",IF(ISNA(VLOOKUP(E456,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H456" s="24" t="str">
-        <f>IF(J456&lt;&gt;1,"",IF(I456="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I456" s="25" t="str">
-        <f>IF(OR(E456="",E456="!!!",F456="NEW"),"",INDEX(B455:B$2,-1+SUMPRODUCT(MAX(ROW(E455:E$2)*(E456=E455:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J456" s="25" t="str">
-        <f>IF(OR(E456="",E456="!!!",F456="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E456)*(E456=E$2:E456)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E455)*(E2=E$1:E455))))))</f>
-        <v> </v>
-      </c>
-      <c r="K456" s="25" t="str">
-        <f>IF(OR(E456="",E456="!!!",F456="NEW"),"",INDEX(J$1:J455,SUMPRODUCT(MAX(ROW(E$1:E455)*(E456=E$1:E455)))))</f>
-        <v> </v>
-      </c>
-      <c r="L456" s="26"/>
+      <c r="A456" s="20"/>
     </row>
     <row r="457" spans="1:12">
       <c r="A457" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="E457" s="21">
-        <f>IF(D457="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F457" s="22" t="str">
-        <f>IF(OR(E457="",E457="!!!"),"",IF(NOT(ISNA(VLOOKUP(E457,E$1:E456,1,FALSE()))),"OLD",IF(AND(E457&lt;&gt;"",E457&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G457" s="23" t="str">
-        <f>IF(OR(E457="",E457="!!!"),"",IF(OR(J457=0,AND(J457=1,K457=1),AND(J457=1,I457="SBJ"),AND(J457=1,I457=0)),"?IN_FOCUS",IF(J457&lt;=2,"?ACTIVATED",IF(J457&lt;&gt;"","?FAMILIAR",IF(F457="NEW",IF(ISNA(VLOOKUP(E457,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H457" s="24" t="str">
-        <f>IF(J457&lt;&gt;1,"",IF(I457="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I457" s="25" t="str">
-        <f>IF(OR(E457="",E457="!!!",F457="NEW"),"",INDEX(B456:B$2,-1+SUMPRODUCT(MAX(ROW(E456:E$2)*(E457=E456:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J457" s="25" t="str">
-        <f>IF(OR(E457="",E457="!!!",F457="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E457)*(E457=E$2:E457)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E456)*(E2=E$1:E456))))))</f>
-        <v> </v>
-      </c>
-      <c r="K457" s="25" t="str">
-        <f>IF(OR(E457="",E457="!!!",F457="NEW"),"",INDEX(J$1:J456,SUMPRODUCT(MAX(ROW(E$1:E456)*(E457=E$1:E456)))))</f>
-        <v> </v>
-      </c>
-      <c r="L457" s="26"/>
+        <v>370</v>
+      </c>
     </row>
     <row r="458" spans="1:12">
       <c r="A458" s="20" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E458" s="21">
         <f>IF(D458="?OLD","!!!","")</f>
@@ -17680,7 +17640,7 @@
     </row>
     <row r="459" spans="1:12">
       <c r="A459" s="20" t="s">
-        <v>120</v>
+        <v>372</v>
       </c>
       <c r="E459" s="21">
         <f>IF(D459="?OLD","!!!","")</f>
@@ -17713,7 +17673,149 @@
       <c r="L459" s="26"/>
     </row>
     <row r="460" spans="1:12">
-      <c r="A460" s="20"/>
+      <c r="A460" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="B460" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C460" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E460" s="21">
+        <f>IF(D460="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F460" s="22" t="str">
+        <f>IF(OR(E460="",E460="!!!"),"",IF(NOT(ISNA(VLOOKUP(E460,E$1:E459,1,FALSE()))),"OLD",IF(AND(E460&lt;&gt;"",E460&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G460" s="23" t="str">
+        <f>IF(OR(E460="",E460="!!!"),"",IF(OR(J460=0,AND(J460=1,K460=1),AND(J460=1,I460="SBJ"),AND(J460=1,I460=0)),"?IN_FOCUS",IF(J460&lt;=2,"?ACTIVATED",IF(J460&lt;&gt;"","?FAMILIAR",IF(F460="NEW",IF(ISNA(VLOOKUP(E460,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H460" s="24" t="str">
+        <f>IF(J460&lt;&gt;1,"",IF(I460="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I460" s="25" t="str">
+        <f>IF(OR(E460="",E460="!!!",F460="NEW"),"",INDEX(B459:B$2,-1+SUMPRODUCT(MAX(ROW(E459:E$2)*(E460=E459:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J460" s="25" t="str">
+        <f>IF(OR(E460="",E460="!!!",F460="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E460)*(E460=E$2:E460)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E459)*(E2=E$1:E459))))))</f>
+        <v> </v>
+      </c>
+      <c r="K460" s="25" t="str">
+        <f>IF(OR(E460="",E460="!!!",F460="NEW"),"",INDEX(J$1:J459,SUMPRODUCT(MAX(ROW(E$1:E459)*(E460=E$1:E459)))))</f>
+        <v> </v>
+      </c>
+      <c r="L460" s="26"/>
+    </row>
+    <row r="461" spans="1:12">
+      <c r="A461" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="E461" s="21">
+        <f>IF(D461="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F461" s="22" t="str">
+        <f>IF(OR(E461="",E461="!!!"),"",IF(NOT(ISNA(VLOOKUP(E461,E$1:E460,1,FALSE()))),"OLD",IF(AND(E461&lt;&gt;"",E461&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G461" s="23" t="str">
+        <f>IF(OR(E461="",E461="!!!"),"",IF(OR(J461=0,AND(J461=1,K461=1),AND(J461=1,I461="SBJ"),AND(J461=1,I461=0)),"?IN_FOCUS",IF(J461&lt;=2,"?ACTIVATED",IF(J461&lt;&gt;"","?FAMILIAR",IF(F461="NEW",IF(ISNA(VLOOKUP(E461,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H461" s="24" t="str">
+        <f>IF(J461&lt;&gt;1,"",IF(I461="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I461" s="25" t="str">
+        <f>IF(OR(E461="",E461="!!!",F461="NEW"),"",INDEX(B460:B$2,-1+SUMPRODUCT(MAX(ROW(E460:E$2)*(E461=E460:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J461" s="25" t="str">
+        <f>IF(OR(E461="",E461="!!!",F461="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E461)*(E461=E$2:E461)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E460)*(E2=E$1:E460))))))</f>
+        <v> </v>
+      </c>
+      <c r="K461" s="25" t="str">
+        <f>IF(OR(E461="",E461="!!!",F461="NEW"),"",INDEX(J$1:J460,SUMPRODUCT(MAX(ROW(E$1:E460)*(E461=E$1:E460)))))</f>
+        <v> </v>
+      </c>
+      <c r="L461" s="26"/>
+    </row>
+    <row r="462" spans="1:12">
+      <c r="A462" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="E462" s="21">
+        <f>IF(D462="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F462" s="22" t="str">
+        <f>IF(OR(E462="",E462="!!!"),"",IF(NOT(ISNA(VLOOKUP(E462,E$1:E461,1,FALSE()))),"OLD",IF(AND(E462&lt;&gt;"",E462&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G462" s="23" t="str">
+        <f>IF(OR(E462="",E462="!!!"),"",IF(OR(J462=0,AND(J462=1,K462=1),AND(J462=1,I462="SBJ"),AND(J462=1,I462=0)),"?IN_FOCUS",IF(J462&lt;=2,"?ACTIVATED",IF(J462&lt;&gt;"","?FAMILIAR",IF(F462="NEW",IF(ISNA(VLOOKUP(E462,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H462" s="24" t="str">
+        <f>IF(J462&lt;&gt;1,"",IF(I462="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I462" s="25" t="str">
+        <f>IF(OR(E462="",E462="!!!",F462="NEW"),"",INDEX(B461:B$2,-1+SUMPRODUCT(MAX(ROW(E461:E$2)*(E462=E461:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J462" s="25" t="str">
+        <f>IF(OR(E462="",E462="!!!",F462="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E462)*(E462=E$2:E462)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E461)*(E2=E$1:E461))))))</f>
+        <v> </v>
+      </c>
+      <c r="K462" s="25" t="str">
+        <f>IF(OR(E462="",E462="!!!",F462="NEW"),"",INDEX(J$1:J461,SUMPRODUCT(MAX(ROW(E$1:E461)*(E462=E$1:E461)))))</f>
+        <v> </v>
+      </c>
+      <c r="L462" s="26"/>
+    </row>
+    <row r="463" spans="1:12">
+      <c r="A463" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E463" s="21">
+        <f>IF(D463="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F463" s="22" t="str">
+        <f>IF(OR(E463="",E463="!!!"),"",IF(NOT(ISNA(VLOOKUP(E463,E$1:E462,1,FALSE()))),"OLD",IF(AND(E463&lt;&gt;"",E463&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G463" s="23" t="str">
+        <f>IF(OR(E463="",E463="!!!"),"",IF(OR(J463=0,AND(J463=1,K463=1),AND(J463=1,I463="SBJ"),AND(J463=1,I463=0)),"?IN_FOCUS",IF(J463&lt;=2,"?ACTIVATED",IF(J463&lt;&gt;"","?FAMILIAR",IF(F463="NEW",IF(ISNA(VLOOKUP(E463,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H463" s="24" t="str">
+        <f>IF(J463&lt;&gt;1,"",IF(I463="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I463" s="25" t="str">
+        <f>IF(OR(E463="",E463="!!!",F463="NEW"),"",INDEX(B462:B$2,-1+SUMPRODUCT(MAX(ROW(E462:E$2)*(E463=E462:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J463" s="25" t="str">
+        <f>IF(OR(E463="",E463="!!!",F463="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E463)*(E463=E$2:E463)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E462)*(E2=E$1:E462))))))</f>
+        <v> </v>
+      </c>
+      <c r="K463" s="25" t="str">
+        <f>IF(OR(E463="",E463="!!!",F463="NEW"),"",INDEX(J$1:J462,SUMPRODUCT(MAX(ROW(E$1:E462)*(E463=E$1:E462)))))</f>
+        <v> </v>
+      </c>
+      <c r="L463" s="26"/>
+    </row>
+    <row r="464" spans="1:12">
+      <c r="A464" s="20"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
